--- a/design/tables/VisualSkin.xlsx
+++ b/design/tables/VisualSkin.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisualSkin" sheetId="1" r:id="Rfc49fb7bc3454019"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisualSkin" sheetId="1" r:id="R4393256eb0ea4d88"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3928,6 +3928,1523 @@
         <x:v>第21关，路线来自Map/MapPoint/Spot/Theme</x:v>
       </x:c>
     </x:row>
+    <x:row r="90">
+      <x:c r="A90" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B90" t="str">
+        <x:v>home_city</x:v>
+      </x:c>
+      <x:c r="C90" t="str">
+        <x:v>ui/backgrounds/home_city/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D90" t="str">
+        <x:v>ui/backgrounds</x:v>
+      </x:c>
+      <x:c r="E90" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F90" t="n">
+        <x:v>941</x:v>
+      </x:c>
+      <x:c r="G90" t="n">
+        <x:v>1672</x:v>
+      </x:c>
+      <x:c r="H90" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I90" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J90" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K90" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L90" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M90" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B91" t="str">
+        <x:v>loading_blue</x:v>
+      </x:c>
+      <x:c r="C91" t="str">
+        <x:v>ui/backgrounds/loading_blue/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D91" t="str">
+        <x:v>ui/backgrounds</x:v>
+      </x:c>
+      <x:c r="E91" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F91" t="n">
+        <x:v>941</x:v>
+      </x:c>
+      <x:c r="G91" t="n">
+        <x:v>1672</x:v>
+      </x:c>
+      <x:c r="H91" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I91" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J91" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K91" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L91" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M91" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" t="n">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B92" t="str">
+        <x:v>window_cream</x:v>
+      </x:c>
+      <x:c r="C92" t="str">
+        <x:v>ui/skins/redesign/window_cream/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D92" t="str">
+        <x:v>ui/skins/redesign</x:v>
+      </x:c>
+      <x:c r="E92" t="str">
+        <x:v>sliced</x:v>
+      </x:c>
+      <x:c r="F92" t="n">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G92" t="n">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="H92" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I92" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J92" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K92" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L92" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M92" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B93" t="str">
+        <x:v>button_gold</x:v>
+      </x:c>
+      <x:c r="C93" t="str">
+        <x:v>ui/skins/redesign/button_gold/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D93" t="str">
+        <x:v>ui/skins/redesign</x:v>
+      </x:c>
+      <x:c r="E93" t="str">
+        <x:v>sliced</x:v>
+      </x:c>
+      <x:c r="F93" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G93" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H93" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="I93" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J93" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K93" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="L93" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M93" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B94" t="str">
+        <x:v>button_green</x:v>
+      </x:c>
+      <x:c r="C94" t="str">
+        <x:v>ui/skins/redesign/button_green/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D94" t="str">
+        <x:v>ui/skins/redesign</x:v>
+      </x:c>
+      <x:c r="E94" t="str">
+        <x:v>sliced</x:v>
+      </x:c>
+      <x:c r="F94" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G94" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H94" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="I94" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J94" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K94" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="L94" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M94" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B95" t="str">
+        <x:v>circle_cream</x:v>
+      </x:c>
+      <x:c r="C95" t="str">
+        <x:v>ui/skins/redesign/circle_cream/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D95" t="str">
+        <x:v>ui/skins/redesign</x:v>
+      </x:c>
+      <x:c r="E95" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F95" t="n">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="G95" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="H95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M95" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B96" t="str">
+        <x:v>tab_normal</x:v>
+      </x:c>
+      <x:c r="C96" t="str">
+        <x:v>ui/skins/redesign/tab_normal/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D96" t="str">
+        <x:v>ui/skins/redesign</x:v>
+      </x:c>
+      <x:c r="E96" t="str">
+        <x:v>sliced</x:v>
+      </x:c>
+      <x:c r="F96" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G96" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H96" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I96" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J96" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K96" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="L96" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M96" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B97" t="str">
+        <x:v>tab_selected</x:v>
+      </x:c>
+      <x:c r="C97" t="str">
+        <x:v>ui/skins/redesign/tab_selected/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D97" t="str">
+        <x:v>ui/skins/redesign</x:v>
+      </x:c>
+      <x:c r="E97" t="str">
+        <x:v>sliced</x:v>
+      </x:c>
+      <x:c r="F97" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G97" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H97" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I97" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J97" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K97" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="L97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M97" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" t="n">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B98" t="str">
+        <x:v>close_red</x:v>
+      </x:c>
+      <x:c r="C98" t="str">
+        <x:v>ui/skins/redesign/close_red/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D98" t="str">
+        <x:v>ui/skins/redesign</x:v>
+      </x:c>
+      <x:c r="E98" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F98" t="n">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="G98" t="n">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="H98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M98" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B99" t="str">
+        <x:v>shelf</x:v>
+      </x:c>
+      <x:c r="C99" t="str">
+        <x:v>ui/skins/redesign/shelf/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D99" t="str">
+        <x:v>ui/skins/redesign</x:v>
+      </x:c>
+      <x:c r="E99" t="str">
+        <x:v>sliced</x:v>
+      </x:c>
+      <x:c r="F99" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G99" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H99" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I99" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J99" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K99" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L99" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M99" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B100" t="str">
+        <x:v>name_tag</x:v>
+      </x:c>
+      <x:c r="C100" t="str">
+        <x:v>ui/skins/redesign/name_tag/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D100" t="str">
+        <x:v>ui/skins/redesign</x:v>
+      </x:c>
+      <x:c r="E100" t="str">
+        <x:v>sliced</x:v>
+      </x:c>
+      <x:c r="F100" t="n">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G100" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H100" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I100" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J100" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K100" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L100" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M100" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B101" t="str">
+        <x:v>night_banner</x:v>
+      </x:c>
+      <x:c r="C101" t="str">
+        <x:v>ui/skins/redesign/night_banner/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D101" t="str">
+        <x:v>ui/skins/redesign</x:v>
+      </x:c>
+      <x:c r="E101" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F101" t="n">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="G101" t="n">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="H101" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I101" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J101" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K101" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L101" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M101" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" t="n">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B102" t="str">
+        <x:v>window_mint</x:v>
+      </x:c>
+      <x:c r="C102" t="str">
+        <x:v>ui/skins/redesign/window_mint/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D102" t="str">
+        <x:v>ui/skins/redesign</x:v>
+      </x:c>
+      <x:c r="E102" t="str">
+        <x:v>sliced</x:v>
+      </x:c>
+      <x:c r="F102" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G102" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H102" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I102" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J102" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K102" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="L102" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M102" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>button_disabled</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>ui/skins/redesign/button_disabled/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D103" t="str">
+        <x:v>ui/skins/redesign</x:v>
+      </x:c>
+      <x:c r="E103" t="str">
+        <x:v>sliced</x:v>
+      </x:c>
+      <x:c r="F103" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G103" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H103" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="I103" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J103" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K103" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="L103" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M103" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="n">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>book_frame</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>ui/windows/book_frame/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D104" t="str">
+        <x:v>ui/windows</x:v>
+      </x:c>
+      <x:c r="E104" t="str">
+        <x:v>sliced</x:v>
+      </x:c>
+      <x:c r="F104" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="G104" t="n">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="H104" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="I104" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J104" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="K104" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L104" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M104" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B105" t="str">
+        <x:v>icon_heart</x:v>
+      </x:c>
+      <x:c r="C105" t="str">
+        <x:v>ui/icons/common/icon_heart/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D105" t="str">
+        <x:v>ui/icons/common</x:v>
+      </x:c>
+      <x:c r="E105" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F105" t="n">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="G105" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="H105" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I105" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J105" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K105" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L105" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M105" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B106" t="str">
+        <x:v>icon_coin</x:v>
+      </x:c>
+      <x:c r="C106" t="str">
+        <x:v>ui/icons/common/icon_coin/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D106" t="str">
+        <x:v>ui/icons/common</x:v>
+      </x:c>
+      <x:c r="E106" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F106" t="n">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="G106" t="n">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="H106" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I106" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J106" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K106" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L106" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M106" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" t="n">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B107" t="str">
+        <x:v>icon_book</x:v>
+      </x:c>
+      <x:c r="C107" t="str">
+        <x:v>ui/icons/common/icon_book/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D107" t="str">
+        <x:v>ui/icons/common</x:v>
+      </x:c>
+      <x:c r="E107" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F107" t="n">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="G107" t="n">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="H107" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I107" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J107" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K107" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L107" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M107" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" t="n">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B108" t="str">
+        <x:v>icon_gear</x:v>
+      </x:c>
+      <x:c r="C108" t="str">
+        <x:v>ui/icons/common/icon_gear/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D108" t="str">
+        <x:v>ui/icons/common</x:v>
+      </x:c>
+      <x:c r="E108" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F108" t="n">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="G108" t="n">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="H108" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I108" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J108" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K108" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L108" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M108" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B109" t="str">
+        <x:v>icon_store</x:v>
+      </x:c>
+      <x:c r="C109" t="str">
+        <x:v>ui/icons/common/icon_store/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D109" t="str">
+        <x:v>ui/icons/common</x:v>
+      </x:c>
+      <x:c r="E109" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F109" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="G109" t="n">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="H109" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I109" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J109" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K109" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L109" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M109" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" t="n">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B110" t="str">
+        <x:v>icon_trophy</x:v>
+      </x:c>
+      <x:c r="C110" t="str">
+        <x:v>ui/icons/common/icon_trophy/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D110" t="str">
+        <x:v>ui/icons/common</x:v>
+      </x:c>
+      <x:c r="E110" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F110" t="n">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="G110" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="H110" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I110" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J110" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K110" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L110" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M110" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" t="n">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B111" t="str">
+        <x:v>icon_avatar</x:v>
+      </x:c>
+      <x:c r="C111" t="str">
+        <x:v>ui/icons/common/icon_avatar/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D111" t="str">
+        <x:v>ui/icons/common</x:v>
+      </x:c>
+      <x:c r="E111" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F111" t="n">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="G111" t="n">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="H111" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I111" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J111" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K111" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L111" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M111" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" t="n">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B112" t="str">
+        <x:v>icon_check</x:v>
+      </x:c>
+      <x:c r="C112" t="str">
+        <x:v>ui/icons/common/icon_check/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D112" t="str">
+        <x:v>ui/icons/common</x:v>
+      </x:c>
+      <x:c r="E112" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F112" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="G112" t="n">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="H112" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I112" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J112" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K112" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L112" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M112" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" t="n">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B113" t="str">
+        <x:v>icon_freeze</x:v>
+      </x:c>
+      <x:c r="C113" t="str">
+        <x:v>ui/icons/common/icon_freeze/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D113" t="str">
+        <x:v>ui/icons/common</x:v>
+      </x:c>
+      <x:c r="E113" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F113" t="n">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="G113" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="H113" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I113" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J113" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K113" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L113" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M113" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" t="n">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B114" t="str">
+        <x:v>icon_broom</x:v>
+      </x:c>
+      <x:c r="C114" t="str">
+        <x:v>ui/icons/common/icon_broom/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D114" t="str">
+        <x:v>ui/icons/common</x:v>
+      </x:c>
+      <x:c r="E114" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F114" t="n">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="G114" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="H114" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I114" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J114" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K114" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L114" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M114" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B115" t="str">
+        <x:v>icon_menu</x:v>
+      </x:c>
+      <x:c r="C115" t="str">
+        <x:v>ui/icons/common/icon_menu/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D115" t="str">
+        <x:v>ui/icons/common</x:v>
+      </x:c>
+      <x:c r="E115" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F115" t="n">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="G115" t="n">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="H115" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I115" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J115" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K115" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L115" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M115" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" t="n">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B116" t="str">
+        <x:v>icon_pause</x:v>
+      </x:c>
+      <x:c r="C116" t="str">
+        <x:v>ui/icons/common/icon_pause/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D116" t="str">
+        <x:v>ui/icons/common</x:v>
+      </x:c>
+      <x:c r="E116" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F116" t="n">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="G116" t="n">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="H116" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I116" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J116" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K116" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L116" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M116" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" t="n">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B117" t="str">
+        <x:v>goods_cola</x:v>
+      </x:c>
+      <x:c r="C117" t="str">
+        <x:v>ui/icons/goods/goods_cola/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D117" t="str">
+        <x:v>ui/icons/goods</x:v>
+      </x:c>
+      <x:c r="E117" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F117" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G117" t="n">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="H117" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I117" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J117" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K117" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L117" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M117" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" t="n">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B118" t="str">
+        <x:v>goods_bread</x:v>
+      </x:c>
+      <x:c r="C118" t="str">
+        <x:v>ui/icons/goods/goods_bread/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D118" t="str">
+        <x:v>ui/icons/goods</x:v>
+      </x:c>
+      <x:c r="E118" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F118" t="n">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="G118" t="n">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="H118" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I118" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J118" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K118" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L118" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M118" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" t="n">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B119" t="str">
+        <x:v>goods_noodles</x:v>
+      </x:c>
+      <x:c r="C119" t="str">
+        <x:v>ui/icons/goods/goods_noodles/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D119" t="str">
+        <x:v>ui/icons/goods</x:v>
+      </x:c>
+      <x:c r="E119" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F119" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="G119" t="n">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="H119" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I119" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J119" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K119" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L119" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M119" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" t="n">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B120" t="str">
+        <x:v>goods_milk</x:v>
+      </x:c>
+      <x:c r="C120" t="str">
+        <x:v>ui/icons/goods/goods_milk/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D120" t="str">
+        <x:v>ui/icons/goods</x:v>
+      </x:c>
+      <x:c r="E120" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F120" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="G120" t="n">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="H120" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I120" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J120" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K120" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L120" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M120" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" t="n">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B121" t="str">
+        <x:v>goods_chips</x:v>
+      </x:c>
+      <x:c r="C121" t="str">
+        <x:v>ui/icons/goods/goods_chips/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D121" t="str">
+        <x:v>ui/icons/goods</x:v>
+      </x:c>
+      <x:c r="E121" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F121" t="n">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="G121" t="n">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="H121" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I121" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J121" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K121" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L121" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M121" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" t="n">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B122" t="str">
+        <x:v>goods_cookies</x:v>
+      </x:c>
+      <x:c r="C122" t="str">
+        <x:v>ui/icons/goods/goods_cookies/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D122" t="str">
+        <x:v>ui/icons/goods</x:v>
+      </x:c>
+      <x:c r="E122" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F122" t="n">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="G122" t="n">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="H122" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I122" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J122" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K122" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L122" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M122" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" t="n">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B123" t="str">
+        <x:v>goods_jelly</x:v>
+      </x:c>
+      <x:c r="C123" t="str">
+        <x:v>ui/icons/goods/goods_jelly/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D123" t="str">
+        <x:v>ui/icons/goods</x:v>
+      </x:c>
+      <x:c r="E123" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F123" t="n">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="G123" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="H123" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I123" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J123" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K123" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L123" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M123" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" t="n">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B124" t="str">
+        <x:v>goods_water</x:v>
+      </x:c>
+      <x:c r="C124" t="str">
+        <x:v>ui/icons/goods/goods_water/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D124" t="str">
+        <x:v>ui/icons/goods</x:v>
+      </x:c>
+      <x:c r="E124" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F124" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="G124" t="n">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="H124" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I124" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J124" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K124" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L124" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M124" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B125" t="str">
+        <x:v>goods_rice</x:v>
+      </x:c>
+      <x:c r="C125" t="str">
+        <x:v>ui/icons/goods/goods_rice/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D125" t="str">
+        <x:v>ui/icons/goods</x:v>
+      </x:c>
+      <x:c r="E125" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F125" t="n">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="G125" t="n">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="H125" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I125" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J125" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K125" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L125" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M125" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" ht="28" customHeight="1">
+      <x:c r="A126" t="n">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B126" t="str">
+        <x:v>courtyard_ground</x:v>
+      </x:c>
+      <x:c r="C126" t="str">
+        <x:v>gameplay/maps/courtyard_ground/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D126" t="str">
+        <x:v>gameplay/maps</x:v>
+      </x:c>
+      <x:c r="E126" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F126" t="n">
+        <x:v>1254</x:v>
+      </x:c>
+      <x:c r="G126" t="n">
+        <x:v>1254</x:v>
+      </x:c>
+      <x:c r="H126" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I126" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J126" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K126" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L126" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M126" t="str">
+        <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/VisualSkin.xlsx
+++ b/design/tables/VisualSkin.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisualSkin" sheetId="1" r:id="R4393256eb0ea4d88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisualSkin" sheetId="1" r:id="R7a9478e3e2c847a5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -319,6 +319,9 @@
       <x:c r="M1" s="5" t="str">
         <x:v>用途</x:v>
       </x:c>
+      <x:c r="N1" t="str">
+        <x:v>适配方式</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="5" t="str">
@@ -360,6 +363,9 @@
       <x:c r="M2" s="5" t="str">
         <x:v>client</x:v>
       </x:c>
+      <x:c r="N2" t="str">
+        <x:v>client</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="36" customHeight="1">
       <x:c r="A3" s="5" t="str">
@@ -401,6 +407,9 @@
       <x:c r="M3" s="5" t="str">
         <x:v>string</x:v>
       </x:c>
+      <x:c r="N3" t="str">
+        <x:v>string</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="36" customHeight="1">
       <x:c r="A4" s="5" t="str">
@@ -442,6 +451,9 @@
       <x:c r="M4" s="5" t="str">
         <x:v>用途</x:v>
       </x:c>
+      <x:c r="N4" t="str">
+        <x:v>适配方式</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="36" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -483,9 +495,12 @@
       <x:c r="M5" s="5" t="str">
         <x:v>note</x:v>
       </x:c>
+      <x:c r="N5" t="str">
+        <x:v>resizeMode</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="28" customHeight="1">
-      <x:c r="A6" s="3" t="n">
+      <x:c r="A6" s="3" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="3" t="str">
@@ -500,33 +515,36 @@
       <x:c r="E6" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F6" s="3" t="n">
+      <x:c r="F6" s="3" t="str">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="G6" s="3" t="n">
+      <x:c r="G6" s="3" t="str">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="H6" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I6" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J6" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K6" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L6" s="3" t="n">
+      <x:c r="H6" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I6" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J6" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K6" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L6" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M6" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N6" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="28" customHeight="1">
-      <x:c r="A7" s="3" t="n">
+      <x:c r="A7" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B7" s="3" t="str">
@@ -541,33 +559,36 @@
       <x:c r="E7" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F7" s="3" t="n">
+      <x:c r="F7" s="3" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G7" s="3" t="n">
+      <x:c r="G7" s="3" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H7" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I7" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J7" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K7" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L7" s="3" t="n">
+      <x:c r="H7" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I7" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J7" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K7" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L7" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M7" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N7" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="28" customHeight="1">
-      <x:c r="A8" s="3" t="n">
+      <x:c r="A8" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B8" s="3" t="str">
@@ -582,33 +603,36 @@
       <x:c r="E8" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F8" s="3" t="n">
+      <x:c r="F8" s="3" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G8" s="3" t="n">
+      <x:c r="G8" s="3" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H8" s="3" t="n">
+      <x:c r="H8" s="3" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I8" s="3" t="n">
+      <x:c r="I8" s="3" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J8" s="3" t="n">
+      <x:c r="J8" s="3" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K8" s="3" t="n">
+      <x:c r="K8" s="3" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L8" s="3" t="n">
+      <x:c r="L8" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M8" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N8" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="28" customHeight="1">
-      <x:c r="A9" s="3" t="n">
+      <x:c r="A9" s="3" t="str">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B9" s="3" t="str">
@@ -623,33 +647,36 @@
       <x:c r="E9" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F9" s="3" t="n">
+      <x:c r="F9" s="3" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G9" s="3" t="n">
+      <x:c r="G9" s="3" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H9" s="3" t="n">
+      <x:c r="H9" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I9" s="3" t="n">
+      <x:c r="I9" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J9" s="3" t="n">
+      <x:c r="J9" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K9" s="3" t="n">
+      <x:c r="K9" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L9" s="3" t="n">
+      <x:c r="L9" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M9" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N9" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="28" customHeight="1">
-      <x:c r="A10" s="3" t="n">
+      <x:c r="A10" s="3" t="str">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B10" s="3" t="str">
@@ -664,33 +691,36 @@
       <x:c r="E10" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F10" s="3" t="n">
+      <x:c r="F10" s="3" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G10" s="3" t="n">
+      <x:c r="G10" s="3" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H10" s="3" t="n">
+      <x:c r="H10" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I10" s="3" t="n">
+      <x:c r="I10" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J10" s="3" t="n">
+      <x:c r="J10" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K10" s="3" t="n">
+      <x:c r="K10" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L10" s="3" t="n">
+      <x:c r="L10" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M10" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N10" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="28" customHeight="1">
-      <x:c r="A11" s="3" t="n">
+      <x:c r="A11" s="3" t="str">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B11" s="3" t="str">
@@ -705,33 +735,36 @@
       <x:c r="E11" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F11" s="3" t="n">
+      <x:c r="F11" s="3" t="str">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G11" s="3" t="n">
+      <x:c r="G11" s="3" t="str">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H11" s="3" t="n">
+      <x:c r="H11" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I11" s="3" t="n">
+      <x:c r="I11" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J11" s="3" t="n">
+      <x:c r="J11" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K11" s="3" t="n">
+      <x:c r="K11" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L11" s="3" t="n">
+      <x:c r="L11" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M11" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N11" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="28" customHeight="1">
-      <x:c r="A12" s="3" t="n">
+      <x:c r="A12" s="3" t="str">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B12" s="3" t="str">
@@ -746,33 +779,36 @@
       <x:c r="E12" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F12" s="3" t="n">
+      <x:c r="F12" s="3" t="str">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G12" s="3" t="n">
+      <x:c r="G12" s="3" t="str">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H12" s="3" t="n">
+      <x:c r="H12" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I12" s="3" t="n">
+      <x:c r="I12" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J12" s="3" t="n">
+      <x:c r="J12" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K12" s="3" t="n">
+      <x:c r="K12" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L12" s="3" t="n">
+      <x:c r="L12" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M12" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N12" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="28" customHeight="1">
-      <x:c r="A13" s="3" t="n">
+      <x:c r="A13" s="3" t="str">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B13" s="3" t="str">
@@ -787,33 +823,36 @@
       <x:c r="E13" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F13" s="3" t="n">
+      <x:c r="F13" s="3" t="str">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G13" s="3" t="n">
+      <x:c r="G13" s="3" t="str">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H13" s="3" t="n">
+      <x:c r="H13" s="3" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I13" s="3" t="n">
+      <x:c r="I13" s="3" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J13" s="3" t="n">
+      <x:c r="J13" s="3" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K13" s="3" t="n">
+      <x:c r="K13" s="3" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L13" s="3" t="n">
+      <x:c r="L13" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M13" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N13" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="28" customHeight="1">
-      <x:c r="A14" s="3" t="n">
+      <x:c r="A14" s="3" t="str">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B14" s="3" t="str">
@@ -828,33 +867,36 @@
       <x:c r="E14" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F14" s="3" t="n">
+      <x:c r="F14" s="3" t="str">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="G14" s="3" t="n">
+      <x:c r="G14" s="3" t="str">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="H14" s="3" t="n">
+      <x:c r="H14" s="3" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I14" s="3" t="n">
+      <x:c r="I14" s="3" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J14" s="3" t="n">
+      <x:c r="J14" s="3" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K14" s="3" t="n">
+      <x:c r="K14" s="3" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="L14" s="3" t="n">
+      <x:c r="L14" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M14" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N14" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="28" customHeight="1">
-      <x:c r="A15" s="3" t="n">
+      <x:c r="A15" s="3" t="str">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B15" s="3" t="str">
@@ -869,33 +911,36 @@
       <x:c r="E15" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F15" s="3" t="n">
+      <x:c r="F15" s="3" t="str">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="G15" s="3" t="n">
+      <x:c r="G15" s="3" t="str">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="H15" s="3" t="n">
+      <x:c r="H15" s="3" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I15" s="3" t="n">
+      <x:c r="I15" s="3" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J15" s="3" t="n">
+      <x:c r="J15" s="3" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K15" s="3" t="n">
+      <x:c r="K15" s="3" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L15" s="3" t="n">
+      <x:c r="L15" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M15" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N15" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="28" customHeight="1">
-      <x:c r="A16" s="3" t="n">
+      <x:c r="A16" s="3" t="str">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B16" s="3" t="str">
@@ -910,33 +955,36 @@
       <x:c r="E16" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F16" s="3" t="n">
+      <x:c r="F16" s="3" t="str">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G16" s="3" t="n">
+      <x:c r="G16" s="3" t="str">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H16" s="3" t="n">
+      <x:c r="H16" s="3" t="str">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I16" s="3" t="n">
+      <x:c r="I16" s="3" t="str">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J16" s="3" t="n">
+      <x:c r="J16" s="3" t="str">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="K16" s="3" t="n">
+      <x:c r="K16" s="3" t="str">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="L16" s="3" t="n">
+      <x:c r="L16" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M16" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N16" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="28" customHeight="1">
-      <x:c r="A17" s="3" t="n">
+      <x:c r="A17" s="3" t="str">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B17" s="3" t="str">
@@ -951,33 +999,36 @@
       <x:c r="E17" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F17" s="3" t="n">
+      <x:c r="F17" s="3" t="str">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G17" s="3" t="n">
+      <x:c r="G17" s="3" t="str">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H17" s="3" t="n">
+      <x:c r="H17" s="3" t="str">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I17" s="3" t="n">
+      <x:c r="I17" s="3" t="str">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J17" s="3" t="n">
+      <x:c r="J17" s="3" t="str">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K17" s="3" t="n">
+      <x:c r="K17" s="3" t="str">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L17" s="3" t="n">
+      <x:c r="L17" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M17" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N17" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="28" customHeight="1">
-      <x:c r="A18" s="3" t="n">
+      <x:c r="A18" s="3" t="str">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B18" s="3" t="str">
@@ -992,33 +1043,36 @@
       <x:c r="E18" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F18" s="3" t="n">
+      <x:c r="F18" s="3" t="str">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G18" s="3" t="n">
+      <x:c r="G18" s="3" t="str">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="H18" s="3" t="n">
+      <x:c r="H18" s="3" t="str">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="I18" s="3" t="n">
+      <x:c r="I18" s="3" t="str">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="J18" s="3" t="n">
+      <x:c r="J18" s="3" t="str">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="K18" s="3" t="n">
+      <x:c r="K18" s="3" t="str">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="L18" s="3" t="n">
+      <x:c r="L18" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M18" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N18" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="28" customHeight="1">
-      <x:c r="A19" s="3" t="n">
+      <x:c r="A19" s="3" t="str">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B19" s="3" t="str">
@@ -1033,33 +1087,36 @@
       <x:c r="E19" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F19" s="3" t="n">
+      <x:c r="F19" s="3" t="str">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G19" s="3" t="n">
+      <x:c r="G19" s="3" t="str">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H19" s="3" t="n">
+      <x:c r="H19" s="3" t="str">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="I19" s="3" t="n">
+      <x:c r="I19" s="3" t="str">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="J19" s="3" t="n">
+      <x:c r="J19" s="3" t="str">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="K19" s="3" t="n">
+      <x:c r="K19" s="3" t="str">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="L19" s="3" t="n">
+      <x:c r="L19" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M19" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N19" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="28" customHeight="1">
-      <x:c r="A20" s="3" t="n">
+      <x:c r="A20" s="3" t="str">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B20" s="3" t="str">
@@ -1074,33 +1131,36 @@
       <x:c r="E20" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F20" s="3" t="n">
+      <x:c r="F20" s="3" t="str">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="G20" s="3" t="n">
+      <x:c r="G20" s="3" t="str">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="H20" s="3" t="n">
+      <x:c r="H20" s="3" t="str">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="I20" s="3" t="n">
+      <x:c r="I20" s="3" t="str">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="J20" s="3" t="n">
+      <x:c r="J20" s="3" t="str">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="K20" s="3" t="n">
+      <x:c r="K20" s="3" t="str">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="L20" s="3" t="n">
+      <x:c r="L20" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M20" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N20" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="28" customHeight="1">
-      <x:c r="A21" s="3" t="n">
+      <x:c r="A21" s="3" t="str">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B21" s="3" t="str">
@@ -1115,33 +1175,36 @@
       <x:c r="E21" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F21" s="3" t="n">
+      <x:c r="F21" s="3" t="str">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G21" s="3" t="n">
+      <x:c r="G21" s="3" t="str">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="H21" s="3" t="n">
+      <x:c r="H21" s="3" t="str">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I21" s="3" t="n">
+      <x:c r="I21" s="3" t="str">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="J21" s="3" t="n">
+      <x:c r="J21" s="3" t="str">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K21" s="3" t="n">
+      <x:c r="K21" s="3" t="str">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="L21" s="3" t="n">
+      <x:c r="L21" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M21" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N21" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="28" customHeight="1">
-      <x:c r="A22" s="3" t="n">
+      <x:c r="A22" s="3" t="str">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B22" s="3" t="str">
@@ -1156,33 +1219,36 @@
       <x:c r="E22" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F22" s="3" t="n">
+      <x:c r="F22" s="3" t="str">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G22" s="3" t="n">
+      <x:c r="G22" s="3" t="str">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H22" s="3" t="n">
+      <x:c r="H22" s="3" t="str">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I22" s="3" t="n">
+      <x:c r="I22" s="3" t="str">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J22" s="3" t="n">
+      <x:c r="J22" s="3" t="str">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K22" s="3" t="n">
+      <x:c r="K22" s="3" t="str">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L22" s="3" t="n">
+      <x:c r="L22" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="M22" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N22" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="28" customHeight="1">
-      <x:c r="A23" s="3" t="n">
+      <x:c r="A23" s="3" t="str">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B23" s="3" t="str">
@@ -1197,33 +1263,36 @@
       <x:c r="E23" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F23" s="3" t="n">
+      <x:c r="F23" s="3" t="str">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G23" s="3" t="n">
+      <x:c r="G23" s="3" t="str">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="H23" s="3" t="n">
+      <x:c r="H23" s="3" t="str">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="I23" s="3" t="n">
+      <x:c r="I23" s="3" t="str">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J23" s="3" t="n">
+      <x:c r="J23" s="3" t="str">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="K23" s="3" t="n">
+      <x:c r="K23" s="3" t="str">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L23" s="3" t="n">
+      <x:c r="L23" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="M23" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N23" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="28" customHeight="1">
-      <x:c r="A24" s="3" t="n">
+      <x:c r="A24" s="3" t="str">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B24" s="3" t="str">
@@ -1238,33 +1307,36 @@
       <x:c r="E24" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F24" s="3" t="n">
+      <x:c r="F24" s="3" t="str">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G24" s="3" t="n">
+      <x:c r="G24" s="3" t="str">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="H24" s="3" t="n">
+      <x:c r="H24" s="3" t="str">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="I24" s="3" t="n">
+      <x:c r="I24" s="3" t="str">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="J24" s="3" t="n">
+      <x:c r="J24" s="3" t="str">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="K24" s="3" t="n">
+      <x:c r="K24" s="3" t="str">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="L24" s="3" t="n">
+      <x:c r="L24" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="M24" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N24" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="28" customHeight="1">
-      <x:c r="A25" s="3" t="n">
+      <x:c r="A25" s="3" t="str">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B25" s="3" t="str">
@@ -1279,33 +1351,36 @@
       <x:c r="E25" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F25" s="3" t="n">
+      <x:c r="F25" s="3" t="str">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="G25" s="3" t="n">
+      <x:c r="G25" s="3" t="str">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H25" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I25" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J25" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K25" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L25" s="3" t="n">
+      <x:c r="H25" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I25" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J25" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K25" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L25" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M25" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N25" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="28" customHeight="1">
-      <x:c r="A26" s="3" t="n">
+      <x:c r="A26" s="3" t="str">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B26" s="3" t="str">
@@ -1320,33 +1395,36 @@
       <x:c r="E26" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F26" s="3" t="n">
+      <x:c r="F26" s="3" t="str">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="G26" s="3" t="n">
+      <x:c r="G26" s="3" t="str">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H26" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I26" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J26" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K26" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L26" s="3" t="n">
+      <x:c r="H26" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I26" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J26" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K26" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L26" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M26" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N26" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="28" customHeight="1">
-      <x:c r="A27" s="3" t="n">
+      <x:c r="A27" s="3" t="str">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B27" s="3" t="str">
@@ -1361,33 +1439,36 @@
       <x:c r="E27" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F27" s="3" t="n">
+      <x:c r="F27" s="3" t="str">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="G27" s="3" t="n">
+      <x:c r="G27" s="3" t="str">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H27" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I27" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J27" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K27" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L27" s="3" t="n">
+      <x:c r="H27" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I27" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J27" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K27" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L27" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M27" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N27" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="28" customHeight="1">
-      <x:c r="A28" s="3" t="n">
+      <x:c r="A28" s="3" t="str">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B28" s="3" t="str">
@@ -1402,33 +1483,36 @@
       <x:c r="E28" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F28" s="3" t="n">
+      <x:c r="F28" s="3" t="str">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="G28" s="3" t="n">
+      <x:c r="G28" s="3" t="str">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="H28" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I28" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J28" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K28" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L28" s="3" t="n">
+      <x:c r="H28" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I28" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J28" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K28" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L28" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M28" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N28" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="28" customHeight="1">
-      <x:c r="A29" s="3" t="n">
+      <x:c r="A29" s="3" t="str">
         <x:v>24</x:v>
       </x:c>
       <x:c r="B29" s="3" t="str">
@@ -1443,33 +1527,36 @@
       <x:c r="E29" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F29" s="3" t="n">
+      <x:c r="F29" s="3" t="str">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="G29" s="3" t="n">
+      <x:c r="G29" s="3" t="str">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="H29" s="3" t="n">
+      <x:c r="H29" s="3" t="str">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="I29" s="3" t="n">
+      <x:c r="I29" s="3" t="str">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="J29" s="3" t="n">
+      <x:c r="J29" s="3" t="str">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="K29" s="3" t="n">
+      <x:c r="K29" s="3" t="str">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="L29" s="3" t="n">
+      <x:c r="L29" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="M29" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N29" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="28" customHeight="1">
-      <x:c r="A30" s="3" t="n">
+      <x:c r="A30" s="3" t="str">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B30" s="3" t="str">
@@ -1484,33 +1571,36 @@
       <x:c r="E30" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F30" s="3" t="n">
+      <x:c r="F30" s="3" t="str">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="G30" s="3" t="n">
+      <x:c r="G30" s="3" t="str">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H30" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I30" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J30" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K30" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L30" s="3" t="n">
+      <x:c r="H30" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I30" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J30" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K30" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L30" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
       <x:c r="M30" s="3" t="str">
         <x:v>Highlight，原预制体 battle_hud.prefab</x:v>
       </x:c>
+      <x:c r="N30" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="28" customHeight="1">
-      <x:c r="A31" s="3" t="n">
+      <x:c r="A31" s="3" t="str">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B31" s="3" t="str">
@@ -1525,33 +1615,36 @@
       <x:c r="E31" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F31" s="3" t="n">
+      <x:c r="F31" s="3" t="str">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G31" s="3" t="n">
+      <x:c r="G31" s="3" t="str">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H31" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I31" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J31" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K31" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L31" s="3" t="n">
+      <x:c r="H31" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I31" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J31" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K31" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L31" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
       <x:c r="M31" s="3" t="str">
         <x:v>Highlight，原预制体 battle_hud.prefab</x:v>
       </x:c>
+      <x:c r="N31" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="28" customHeight="1">
-      <x:c r="A32" s="3" t="n">
+      <x:c r="A32" s="3" t="str">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B32" s="3" t="str">
@@ -1566,33 +1659,36 @@
       <x:c r="E32" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F32" s="3" t="n">
+      <x:c r="F32" s="3" t="str">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G32" s="3" t="n">
+      <x:c r="G32" s="3" t="str">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H32" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I32" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J32" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K32" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L32" s="3" t="n">
+      <x:c r="H32" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I32" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J32" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K32" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L32" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
       <x:c r="M32" s="3" t="str">
         <x:v>Highlight，原预制体 battle_hud.prefab</x:v>
       </x:c>
+      <x:c r="N32" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="28" customHeight="1">
-      <x:c r="A33" s="3" t="n">
+      <x:c r="A33" s="3" t="str">
         <x:v>28</x:v>
       </x:c>
       <x:c r="B33" s="3" t="str">
@@ -1607,33 +1703,36 @@
       <x:c r="E33" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F33" s="3" t="n">
+      <x:c r="F33" s="3" t="str">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="G33" s="3" t="n">
+      <x:c r="G33" s="3" t="str">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="H33" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I33" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J33" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K33" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L33" s="3" t="n">
+      <x:c r="H33" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I33" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J33" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K33" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L33" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
       <x:c r="M33" s="3" t="str">
         <x:v>Heart，原预制体 battle_hud.prefab</x:v>
       </x:c>
+      <x:c r="N33" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="28" customHeight="1">
-      <x:c r="A34" s="3" t="n">
+      <x:c r="A34" s="3" t="str">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B34" s="3" t="str">
@@ -1648,33 +1747,36 @@
       <x:c r="E34" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F34" s="3" t="n">
+      <x:c r="F34" s="3" t="str">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G34" s="3" t="n">
+      <x:c r="G34" s="3" t="str">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="H34" s="3" t="n">
+      <x:c r="H34" s="3" t="str">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="I34" s="3" t="n">
+      <x:c r="I34" s="3" t="str">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="J34" s="3" t="n">
+      <x:c r="J34" s="3" t="str">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="K34" s="3" t="n">
+      <x:c r="K34" s="3" t="str">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="L34" s="3" t="n">
+      <x:c r="L34" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M34" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N34" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="28" customHeight="1">
-      <x:c r="A35" s="3" t="n">
+      <x:c r="A35" s="3" t="str">
         <x:v>30</x:v>
       </x:c>
       <x:c r="B35" s="3" t="str">
@@ -1689,33 +1791,36 @@
       <x:c r="E35" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F35" s="3" t="n">
+      <x:c r="F35" s="3" t="str">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G35" s="3" t="n">
+      <x:c r="G35" s="3" t="str">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H35" s="3" t="n">
+      <x:c r="H35" s="3" t="str">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="I35" s="3" t="n">
+      <x:c r="I35" s="3" t="str">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="J35" s="3" t="n">
+      <x:c r="J35" s="3" t="str">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="K35" s="3" t="n">
+      <x:c r="K35" s="3" t="str">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="L35" s="3" t="n">
+      <x:c r="L35" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M35" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N35" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="28" customHeight="1">
-      <x:c r="A36" s="3" t="n">
+      <x:c r="A36" s="3" t="str">
         <x:v>31</x:v>
       </x:c>
       <x:c r="B36" s="3" t="str">
@@ -1730,33 +1835,36 @@
       <x:c r="E36" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F36" s="3" t="n">
+      <x:c r="F36" s="3" t="str">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G36" s="3" t="n">
+      <x:c r="G36" s="3" t="str">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H36" s="3" t="n">
+      <x:c r="H36" s="3" t="str">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I36" s="3" t="n">
+      <x:c r="I36" s="3" t="str">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="J36" s="3" t="n">
+      <x:c r="J36" s="3" t="str">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="K36" s="3" t="n">
+      <x:c r="K36" s="3" t="str">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="L36" s="3" t="n">
+      <x:c r="L36" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="M36" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N36" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="28" customHeight="1">
-      <x:c r="A37" s="3" t="n">
+      <x:c r="A37" s="3" t="str">
         <x:v>32</x:v>
       </x:c>
       <x:c r="B37" s="3" t="str">
@@ -1771,33 +1879,36 @@
       <x:c r="E37" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F37" s="3" t="n">
+      <x:c r="F37" s="3" t="str">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G37" s="3" t="n">
+      <x:c r="G37" s="3" t="str">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H37" s="3" t="n">
+      <x:c r="H37" s="3" t="str">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="I37" s="3" t="n">
+      <x:c r="I37" s="3" t="str">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="J37" s="3" t="n">
+      <x:c r="J37" s="3" t="str">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="K37" s="3" t="n">
+      <x:c r="K37" s="3" t="str">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="L37" s="3" t="n">
+      <x:c r="L37" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="M37" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N37" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="28" customHeight="1">
-      <x:c r="A38" s="3" t="n">
+      <x:c r="A38" s="3" t="str">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B38" s="3" t="str">
@@ -1812,33 +1923,36 @@
       <x:c r="E38" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F38" s="3" t="n">
+      <x:c r="F38" s="3" t="str">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="G38" s="3" t="n">
+      <x:c r="G38" s="3" t="str">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H38" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I38" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J38" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K38" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L38" s="3" t="n">
+      <x:c r="H38" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I38" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J38" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K38" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L38" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
       <x:c r="M38" s="3" t="str">
         <x:v>Highlight，原预制体 battle_hud.prefab</x:v>
       </x:c>
+      <x:c r="N38" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="28" customHeight="1">
-      <x:c r="A39" s="3" t="n">
+      <x:c r="A39" s="3" t="str">
         <x:v>34</x:v>
       </x:c>
       <x:c r="B39" s="3" t="str">
@@ -1853,33 +1967,36 @@
       <x:c r="E39" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F39" s="3" t="n">
+      <x:c r="F39" s="3" t="str">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G39" s="3" t="n">
+      <x:c r="G39" s="3" t="str">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H39" s="3" t="n">
+      <x:c r="H39" s="3" t="str">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I39" s="3" t="n">
+      <x:c r="I39" s="3" t="str">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J39" s="3" t="n">
+      <x:c r="J39" s="3" t="str">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K39" s="3" t="n">
+      <x:c r="K39" s="3" t="str">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="L39" s="3" t="n">
+      <x:c r="L39" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M39" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N39" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="28" customHeight="1">
-      <x:c r="A40" s="3" t="n">
+      <x:c r="A40" s="3" t="str">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B40" s="3" t="str">
@@ -1894,33 +2011,36 @@
       <x:c r="E40" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F40" s="3" t="n">
+      <x:c r="F40" s="3" t="str">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G40" s="3" t="n">
+      <x:c r="G40" s="3" t="str">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="H40" s="3" t="n">
+      <x:c r="H40" s="3" t="str">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="I40" s="3" t="n">
+      <x:c r="I40" s="3" t="str">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="J40" s="3" t="n">
+      <x:c r="J40" s="3" t="str">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="K40" s="3" t="n">
+      <x:c r="K40" s="3" t="str">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="L40" s="3" t="n">
+      <x:c r="L40" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="M40" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N40" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="28" customHeight="1">
-      <x:c r="A41" s="3" t="n">
+      <x:c r="A41" s="3" t="str">
         <x:v>36</x:v>
       </x:c>
       <x:c r="B41" s="3" t="str">
@@ -1935,33 +2055,36 @@
       <x:c r="E41" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F41" s="3" t="n">
+      <x:c r="F41" s="3" t="str">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="G41" s="3" t="n">
+      <x:c r="G41" s="3" t="str">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H41" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I41" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J41" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K41" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L41" s="3" t="n">
+      <x:c r="H41" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I41" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J41" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K41" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L41" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
       <x:c r="M41" s="3" t="str">
         <x:v>Highlight，原预制体 build_card.prefab</x:v>
       </x:c>
+      <x:c r="N41" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="28" customHeight="1">
-      <x:c r="A42" s="3" t="n">
+      <x:c r="A42" s="3" t="str">
         <x:v>37</x:v>
       </x:c>
       <x:c r="B42" s="3" t="str">
@@ -1976,33 +2099,36 @@
       <x:c r="E42" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F42" s="3" t="n">
+      <x:c r="F42" s="3" t="str">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="G42" s="3" t="n">
+      <x:c r="G42" s="3" t="str">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H42" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I42" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J42" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K42" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L42" s="3" t="n">
+      <x:c r="H42" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I42" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J42" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K42" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L42" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
       <x:c r="M42" s="3" t="str">
         <x:v>Highlight，原预制体 button.prefab</x:v>
       </x:c>
+      <x:c r="N42" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="28" customHeight="1">
-      <x:c r="A43" s="3" t="n">
+      <x:c r="A43" s="3" t="str">
         <x:v>38</x:v>
       </x:c>
       <x:c r="B43" s="3" t="str">
@@ -2017,33 +2143,36 @@
       <x:c r="E43" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F43" s="3" t="n">
+      <x:c r="F43" s="3" t="str">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G43" s="3" t="n">
+      <x:c r="G43" s="3" t="str">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="H43" s="3" t="n">
+      <x:c r="H43" s="3" t="str">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I43" s="3" t="n">
+      <x:c r="I43" s="3" t="str">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="J43" s="3" t="n">
+      <x:c r="J43" s="3" t="str">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="K43" s="3" t="n">
+      <x:c r="K43" s="3" t="str">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="L43" s="3" t="n">
+      <x:c r="L43" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M43" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N43" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="28" customHeight="1">
-      <x:c r="A44" s="3" t="n">
+      <x:c r="A44" s="3" t="str">
         <x:v>39</x:v>
       </x:c>
       <x:c r="B44" s="3" t="str">
@@ -2058,33 +2187,36 @@
       <x:c r="E44" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F44" s="3" t="n">
+      <x:c r="F44" s="3" t="str">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G44" s="3" t="n">
+      <x:c r="G44" s="3" t="str">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="H44" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I44" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J44" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K44" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L44" s="3" t="n">
+      <x:c r="H44" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I44" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J44" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K44" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L44" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="M44" s="3" t="str">
         <x:v>Play，原预制体 challenge_pick.prefab</x:v>
       </x:c>
+      <x:c r="N44" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="28" customHeight="1">
-      <x:c r="A45" s="3" t="n">
+      <x:c r="A45" s="3" t="str">
         <x:v>40</x:v>
       </x:c>
       <x:c r="B45" s="3" t="str">
@@ -2099,33 +2231,36 @@
       <x:c r="E45" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F45" s="3" t="n">
+      <x:c r="F45" s="3" t="str">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G45" s="3" t="n">
+      <x:c r="G45" s="3" t="str">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="H45" s="3" t="n">
+      <x:c r="H45" s="3" t="str">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="I45" s="3" t="n">
+      <x:c r="I45" s="3" t="str">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="J45" s="3" t="n">
+      <x:c r="J45" s="3" t="str">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="K45" s="3" t="n">
+      <x:c r="K45" s="3" t="str">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="L45" s="3" t="n">
+      <x:c r="L45" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M45" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N45" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="28" customHeight="1">
-      <x:c r="A46" s="3" t="n">
+      <x:c r="A46" s="3" t="str">
         <x:v>41</x:v>
       </x:c>
       <x:c r="B46" s="3" t="str">
@@ -2140,33 +2275,36 @@
       <x:c r="E46" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F46" s="3" t="n">
+      <x:c r="F46" s="3" t="str">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G46" s="3" t="n">
+      <x:c r="G46" s="3" t="str">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="H46" s="3" t="n">
+      <x:c r="H46" s="3" t="str">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="I46" s="3" t="n">
+      <x:c r="I46" s="3" t="str">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J46" s="3" t="n">
+      <x:c r="J46" s="3" t="str">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="K46" s="3" t="n">
+      <x:c r="K46" s="3" t="str">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L46" s="3" t="n">
+      <x:c r="L46" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M46" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N46" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="28" customHeight="1">
-      <x:c r="A47" s="3" t="n">
+      <x:c r="A47" s="3" t="str">
         <x:v>42</x:v>
       </x:c>
       <x:c r="B47" s="3" t="str">
@@ -2181,33 +2319,36 @@
       <x:c r="E47" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F47" s="3" t="n">
+      <x:c r="F47" s="3" t="str">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G47" s="3" t="n">
+      <x:c r="G47" s="3" t="str">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="H47" s="3" t="n">
+      <x:c r="H47" s="3" t="str">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="I47" s="3" t="n">
+      <x:c r="I47" s="3" t="str">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="J47" s="3" t="n">
+      <x:c r="J47" s="3" t="str">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="K47" s="3" t="n">
+      <x:c r="K47" s="3" t="str">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="L47" s="3" t="n">
+      <x:c r="L47" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M47" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N47" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="28" customHeight="1">
-      <x:c r="A48" s="3" t="n">
+      <x:c r="A48" s="3" t="str">
         <x:v>43</x:v>
       </x:c>
       <x:c r="B48" s="3" t="str">
@@ -2222,33 +2363,36 @@
       <x:c r="E48" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F48" s="3" t="n">
+      <x:c r="F48" s="3" t="str">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="G48" s="3" t="n">
+      <x:c r="G48" s="3" t="str">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H48" s="3" t="n">
+      <x:c r="H48" s="3" t="str">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="I48" s="3" t="n">
+      <x:c r="I48" s="3" t="str">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="J48" s="3" t="n">
+      <x:c r="J48" s="3" t="str">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K48" s="3" t="n">
+      <x:c r="K48" s="3" t="str">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L48" s="3" t="n">
+      <x:c r="L48" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M48" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N48" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="28" customHeight="1">
-      <x:c r="A49" s="3" t="n">
+      <x:c r="A49" s="3" t="str">
         <x:v>44</x:v>
       </x:c>
       <x:c r="B49" s="3" t="str">
@@ -2263,33 +2407,36 @@
       <x:c r="E49" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F49" s="3" t="n">
+      <x:c r="F49" s="3" t="str">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G49" s="3" t="n">
+      <x:c r="G49" s="3" t="str">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H49" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I49" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J49" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K49" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L49" s="3" t="n">
+      <x:c r="H49" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I49" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J49" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K49" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L49" s="3" t="str">
         <x:v>4</x:v>
       </x:c>
       <x:c r="M49" s="3" t="str">
         <x:v>Tooth0，原预制体 home.prefab</x:v>
       </x:c>
+      <x:c r="N49" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="28" customHeight="1">
-      <x:c r="A50" s="3" t="n">
+      <x:c r="A50" s="3" t="str">
         <x:v>45</x:v>
       </x:c>
       <x:c r="B50" s="3" t="str">
@@ -2304,33 +2451,36 @@
       <x:c r="E50" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F50" s="3" t="n">
+      <x:c r="F50" s="3" t="str">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G50" s="3" t="n">
+      <x:c r="G50" s="3" t="str">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H50" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I50" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J50" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K50" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L50" s="3" t="n">
+      <x:c r="H50" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I50" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J50" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K50" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L50" s="3" t="str">
         <x:v>4</x:v>
       </x:c>
       <x:c r="M50" s="3" t="str">
         <x:v>Tooth1，原预制体 home.prefab</x:v>
       </x:c>
+      <x:c r="N50" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="28" customHeight="1">
-      <x:c r="A51" s="3" t="n">
+      <x:c r="A51" s="3" t="str">
         <x:v>46</x:v>
       </x:c>
       <x:c r="B51" s="3" t="str">
@@ -2345,33 +2495,36 @@
       <x:c r="E51" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F51" s="3" t="n">
+      <x:c r="F51" s="3" t="str">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G51" s="3" t="n">
+      <x:c r="G51" s="3" t="str">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H51" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I51" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J51" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K51" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L51" s="3" t="n">
+      <x:c r="H51" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I51" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J51" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K51" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L51" s="3" t="str">
         <x:v>4</x:v>
       </x:c>
       <x:c r="M51" s="3" t="str">
         <x:v>Tooth2，原预制体 home.prefab</x:v>
       </x:c>
+      <x:c r="N51" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="28" customHeight="1">
-      <x:c r="A52" s="3" t="n">
+      <x:c r="A52" s="3" t="str">
         <x:v>47</x:v>
       </x:c>
       <x:c r="B52" s="3" t="str">
@@ -2386,33 +2539,36 @@
       <x:c r="E52" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F52" s="3" t="n">
+      <x:c r="F52" s="3" t="str">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G52" s="3" t="n">
+      <x:c r="G52" s="3" t="str">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H52" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I52" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J52" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K52" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L52" s="3" t="n">
+      <x:c r="H52" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I52" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J52" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K52" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L52" s="3" t="str">
         <x:v>4</x:v>
       </x:c>
       <x:c r="M52" s="3" t="str">
         <x:v>Tooth3，原预制体 home.prefab</x:v>
       </x:c>
+      <x:c r="N52" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="28" customHeight="1">
-      <x:c r="A53" s="3" t="n">
+      <x:c r="A53" s="3" t="str">
         <x:v>48</x:v>
       </x:c>
       <x:c r="B53" s="3" t="str">
@@ -2427,33 +2583,36 @@
       <x:c r="E53" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F53" s="3" t="n">
+      <x:c r="F53" s="3" t="str">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G53" s="3" t="n">
+      <x:c r="G53" s="3" t="str">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H53" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I53" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J53" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K53" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L53" s="3" t="n">
+      <x:c r="H53" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I53" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J53" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K53" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L53" s="3" t="str">
         <x:v>4</x:v>
       </x:c>
       <x:c r="M53" s="3" t="str">
         <x:v>Tooth4，原预制体 home.prefab</x:v>
       </x:c>
+      <x:c r="N53" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="28" customHeight="1">
-      <x:c r="A54" s="3" t="n">
+      <x:c r="A54" s="3" t="str">
         <x:v>49</x:v>
       </x:c>
       <x:c r="B54" s="3" t="str">
@@ -2468,33 +2627,36 @@
       <x:c r="E54" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F54" s="3" t="n">
+      <x:c r="F54" s="3" t="str">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G54" s="3" t="n">
+      <x:c r="G54" s="3" t="str">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H54" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I54" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J54" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K54" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L54" s="3" t="n">
+      <x:c r="H54" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I54" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J54" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K54" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L54" s="3" t="str">
         <x:v>4</x:v>
       </x:c>
       <x:c r="M54" s="3" t="str">
         <x:v>Tooth5，原预制体 home.prefab</x:v>
       </x:c>
+      <x:c r="N54" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="55" ht="28" customHeight="1">
-      <x:c r="A55" s="3" t="n">
+      <x:c r="A55" s="3" t="str">
         <x:v>50</x:v>
       </x:c>
       <x:c r="B55" s="3" t="str">
@@ -2509,33 +2671,36 @@
       <x:c r="E55" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F55" s="3" t="n">
+      <x:c r="F55" s="3" t="str">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G55" s="3" t="n">
+      <x:c r="G55" s="3" t="str">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H55" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I55" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J55" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K55" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L55" s="3" t="n">
+      <x:c r="H55" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I55" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J55" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K55" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L55" s="3" t="str">
         <x:v>4</x:v>
       </x:c>
       <x:c r="M55" s="3" t="str">
         <x:v>Tooth6，原预制体 home.prefab</x:v>
       </x:c>
+      <x:c r="N55" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="28" customHeight="1">
-      <x:c r="A56" s="3" t="n">
+      <x:c r="A56" s="3" t="str">
         <x:v>51</x:v>
       </x:c>
       <x:c r="B56" s="3" t="str">
@@ -2550,33 +2715,36 @@
       <x:c r="E56" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F56" s="3" t="n">
+      <x:c r="F56" s="3" t="str">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G56" s="3" t="n">
+      <x:c r="G56" s="3" t="str">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H56" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I56" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J56" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K56" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L56" s="3" t="n">
+      <x:c r="H56" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I56" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J56" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K56" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L56" s="3" t="str">
         <x:v>4</x:v>
       </x:c>
       <x:c r="M56" s="3" t="str">
         <x:v>Tooth7，原预制体 home.prefab</x:v>
       </x:c>
+      <x:c r="N56" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="57" ht="28" customHeight="1">
-      <x:c r="A57" s="3" t="n">
+      <x:c r="A57" s="3" t="str">
         <x:v>52</x:v>
       </x:c>
       <x:c r="B57" s="3" t="str">
@@ -2591,33 +2759,36 @@
       <x:c r="E57" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F57" s="3" t="n">
+      <x:c r="F57" s="3" t="str">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G57" s="3" t="n">
+      <x:c r="G57" s="3" t="str">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="H57" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I57" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J57" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K57" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L57" s="3" t="n">
+      <x:c r="H57" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I57" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J57" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K57" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L57" s="3" t="str">
         <x:v>4</x:v>
       </x:c>
       <x:c r="M57" s="3" t="str">
         <x:v>GearRing，原预制体 home.prefab</x:v>
       </x:c>
+      <x:c r="N57" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="58" ht="28" customHeight="1">
-      <x:c r="A58" s="3" t="n">
+      <x:c r="A58" s="3" t="str">
         <x:v>53</x:v>
       </x:c>
       <x:c r="B58" s="3" t="str">
@@ -2632,33 +2803,36 @@
       <x:c r="E58" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F58" s="3" t="n">
+      <x:c r="F58" s="3" t="str">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G58" s="3" t="n">
+      <x:c r="G58" s="3" t="str">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="H58" s="3" t="n">
+      <x:c r="H58" s="3" t="str">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="I58" s="3" t="n">
+      <x:c r="I58" s="3" t="str">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="J58" s="3" t="n">
+      <x:c r="J58" s="3" t="str">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="K58" s="3" t="n">
+      <x:c r="K58" s="3" t="str">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="L58" s="3" t="n">
+      <x:c r="L58" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M58" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N58" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="59" ht="28" customHeight="1">
-      <x:c r="A59" s="3" t="n">
+      <x:c r="A59" s="3" t="str">
         <x:v>54</x:v>
       </x:c>
       <x:c r="B59" s="3" t="str">
@@ -2673,33 +2847,36 @@
       <x:c r="E59" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F59" s="3" t="n">
+      <x:c r="F59" s="3" t="str">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G59" s="3" t="n">
+      <x:c r="G59" s="3" t="str">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="H59" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I59" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J59" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K59" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L59" s="3" t="n">
+      <x:c r="H59" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I59" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J59" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K59" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L59" s="3" t="str">
         <x:v>4</x:v>
       </x:c>
       <x:c r="M59" s="3" t="str">
         <x:v>Ring，原预制体 level_card.prefab</x:v>
       </x:c>
+      <x:c r="N59" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" ht="28" customHeight="1">
-      <x:c r="A60" s="3" t="n">
+      <x:c r="A60" s="3" t="str">
         <x:v>55</x:v>
       </x:c>
       <x:c r="B60" s="3" t="str">
@@ -2714,33 +2891,36 @@
       <x:c r="E60" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F60" s="3" t="n">
+      <x:c r="F60" s="3" t="str">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="G60" s="3" t="n">
+      <x:c r="G60" s="3" t="str">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="H60" s="3" t="n">
+      <x:c r="H60" s="3" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I60" s="3" t="n">
+      <x:c r="I60" s="3" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J60" s="3" t="n">
+      <x:c r="J60" s="3" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K60" s="3" t="n">
+      <x:c r="K60" s="3" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="L60" s="3" t="n">
+      <x:c r="L60" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M60" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N60" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="61" ht="28" customHeight="1">
-      <x:c r="A61" s="3" t="n">
+      <x:c r="A61" s="3" t="str">
         <x:v>56</x:v>
       </x:c>
       <x:c r="B61" s="3" t="str">
@@ -2755,33 +2935,36 @@
       <x:c r="E61" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F61" s="3" t="n">
+      <x:c r="F61" s="3" t="str">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G61" s="3" t="n">
+      <x:c r="G61" s="3" t="str">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="H61" s="3" t="n">
+      <x:c r="H61" s="3" t="str">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="I61" s="3" t="n">
+      <x:c r="I61" s="3" t="str">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="J61" s="3" t="n">
+      <x:c r="J61" s="3" t="str">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="K61" s="3" t="n">
+      <x:c r="K61" s="3" t="str">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L61" s="3" t="n">
+      <x:c r="L61" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M61" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N61" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="62" ht="28" customHeight="1">
-      <x:c r="A62" s="3" t="n">
+      <x:c r="A62" s="3" t="str">
         <x:v>57</x:v>
       </x:c>
       <x:c r="B62" s="3" t="str">
@@ -2796,33 +2979,36 @@
       <x:c r="E62" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F62" s="3" t="n">
+      <x:c r="F62" s="3" t="str">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G62" s="3" t="n">
+      <x:c r="G62" s="3" t="str">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="H62" s="3" t="n">
+      <x:c r="H62" s="3" t="str">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="I62" s="3" t="n">
+      <x:c r="I62" s="3" t="str">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="J62" s="3" t="n">
+      <x:c r="J62" s="3" t="str">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="K62" s="3" t="n">
+      <x:c r="K62" s="3" t="str">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="L62" s="3" t="n">
+      <x:c r="L62" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="M62" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N62" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="63" ht="28" customHeight="1">
-      <x:c r="A63" s="3" t="n">
+      <x:c r="A63" s="3" t="str">
         <x:v>58</x:v>
       </x:c>
       <x:c r="B63" s="3" t="str">
@@ -2837,33 +3023,36 @@
       <x:c r="E63" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F63" s="3" t="n">
+      <x:c r="F63" s="3" t="str">
         <x:v>544</x:v>
       </x:c>
-      <x:c r="G63" s="3" t="n">
+      <x:c r="G63" s="3" t="str">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H63" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I63" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J63" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K63" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L63" s="3" t="n">
+      <x:c r="H63" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I63" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J63" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K63" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L63" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
       <x:c r="M63" s="3" t="str">
         <x:v>Highlight，原预制体 lose.prefab</x:v>
       </x:c>
+      <x:c r="N63" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="64" ht="28" customHeight="1">
-      <x:c r="A64" s="3" t="n">
+      <x:c r="A64" s="3" t="str">
         <x:v>59</x:v>
       </x:c>
       <x:c r="B64" s="3" t="str">
@@ -2878,33 +3067,36 @@
       <x:c r="E64" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F64" s="3" t="n">
+      <x:c r="F64" s="3" t="str">
         <x:v>448</x:v>
       </x:c>
-      <x:c r="G64" s="3" t="n">
+      <x:c r="G64" s="3" t="str">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H64" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I64" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J64" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K64" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L64" s="3" t="n">
+      <x:c r="H64" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I64" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J64" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K64" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L64" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
       <x:c r="M64" s="3" t="str">
         <x:v>Highlight，原预制体 lose.prefab</x:v>
       </x:c>
+      <x:c r="N64" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="65" ht="28" customHeight="1">
-      <x:c r="A65" s="3" t="n">
+      <x:c r="A65" s="3" t="str">
         <x:v>60</x:v>
       </x:c>
       <x:c r="B65" s="3" t="str">
@@ -2919,33 +3111,36 @@
       <x:c r="E65" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F65" s="3" t="n">
+      <x:c r="F65" s="3" t="str">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G65" s="3" t="n">
+      <x:c r="G65" s="3" t="str">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="H65" s="3" t="n">
+      <x:c r="H65" s="3" t="str">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="I65" s="3" t="n">
+      <x:c r="I65" s="3" t="str">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="J65" s="3" t="n">
+      <x:c r="J65" s="3" t="str">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="K65" s="3" t="n">
+      <x:c r="K65" s="3" t="str">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L65" s="3" t="n">
+      <x:c r="L65" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="M65" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N65" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="66" ht="28" customHeight="1">
-      <x:c r="A66" s="3" t="n">
+      <x:c r="A66" s="3" t="str">
         <x:v>61</x:v>
       </x:c>
       <x:c r="B66" s="3" t="str">
@@ -2960,33 +3155,36 @@
       <x:c r="E66" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F66" s="3" t="n">
+      <x:c r="F66" s="3" t="str">
         <x:v>476</x:v>
       </x:c>
-      <x:c r="G66" s="3" t="n">
+      <x:c r="G66" s="3" t="str">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H66" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I66" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J66" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K66" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L66" s="3" t="n">
+      <x:c r="H66" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I66" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J66" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K66" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L66" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
       <x:c r="M66" s="3" t="str">
         <x:v>Highlight，原预制体 pause.prefab</x:v>
       </x:c>
+      <x:c r="N66" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="67" ht="28" customHeight="1">
-      <x:c r="A67" s="3" t="n">
+      <x:c r="A67" s="3" t="str">
         <x:v>62</x:v>
       </x:c>
       <x:c r="B67" s="3" t="str">
@@ -3001,33 +3199,36 @@
       <x:c r="E67" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F67" s="3" t="n">
+      <x:c r="F67" s="3" t="str">
         <x:v>448</x:v>
       </x:c>
-      <x:c r="G67" s="3" t="n">
+      <x:c r="G67" s="3" t="str">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H67" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I67" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J67" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K67" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L67" s="3" t="n">
+      <x:c r="H67" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I67" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J67" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K67" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L67" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
       <x:c r="M67" s="3" t="str">
         <x:v>Highlight，原预制体 pause.prefab</x:v>
       </x:c>
+      <x:c r="N67" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="68" ht="28" customHeight="1">
-      <x:c r="A68" s="3" t="n">
+      <x:c r="A68" s="3" t="str">
         <x:v>63</x:v>
       </x:c>
       <x:c r="B68" s="3" t="str">
@@ -3042,33 +3243,36 @@
       <x:c r="E68" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F68" s="3" t="n">
+      <x:c r="F68" s="3" t="str">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G68" s="3" t="n">
+      <x:c r="G68" s="3" t="str">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="H68" s="3" t="n">
+      <x:c r="H68" s="3" t="str">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="I68" s="3" t="n">
+      <x:c r="I68" s="3" t="str">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="J68" s="3" t="n">
+      <x:c r="J68" s="3" t="str">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K68" s="3" t="n">
+      <x:c r="K68" s="3" t="str">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="L68" s="3" t="n">
+      <x:c r="L68" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M68" s="3" t="str">
         <x:v>共享可替换皮肤</x:v>
       </x:c>
+      <x:c r="N68" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="69" ht="28" customHeight="1">
-      <x:c r="A69" s="3" t="n">
+      <x:c r="A69" s="3" t="str">
         <x:v>64</x:v>
       </x:c>
       <x:c r="B69" s="3" t="str">
@@ -3083,33 +3287,36 @@
       <x:c r="E69" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F69" s="3" t="n">
+      <x:c r="F69" s="3" t="str">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G69" s="3" t="n">
+      <x:c r="G69" s="3" t="str">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H69" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I69" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J69" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K69" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L69" s="3" t="n">
+      <x:c r="H69" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I69" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J69" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K69" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L69" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M69" s="3" t="str">
         <x:v>第1关，路线来自Map/MapPoint/Spot/Theme</x:v>
       </x:c>
+      <x:c r="N69" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="70" ht="28" customHeight="1">
-      <x:c r="A70" s="3" t="n">
+      <x:c r="A70" s="3" t="str">
         <x:v>65</x:v>
       </x:c>
       <x:c r="B70" s="3" t="str">
@@ -3124,33 +3331,36 @@
       <x:c r="E70" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F70" s="3" t="n">
+      <x:c r="F70" s="3" t="str">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G70" s="3" t="n">
+      <x:c r="G70" s="3" t="str">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H70" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I70" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J70" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K70" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L70" s="3" t="n">
+      <x:c r="H70" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I70" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J70" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K70" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L70" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M70" s="3" t="str">
         <x:v>第2关，路线来自Map/MapPoint/Spot/Theme</x:v>
       </x:c>
+      <x:c r="N70" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="71" ht="28" customHeight="1">
-      <x:c r="A71" s="3" t="n">
+      <x:c r="A71" s="3" t="str">
         <x:v>66</x:v>
       </x:c>
       <x:c r="B71" s="3" t="str">
@@ -3165,33 +3375,36 @@
       <x:c r="E71" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F71" s="3" t="n">
+      <x:c r="F71" s="3" t="str">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G71" s="3" t="n">
+      <x:c r="G71" s="3" t="str">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H71" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I71" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J71" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K71" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L71" s="3" t="n">
+      <x:c r="H71" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I71" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J71" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K71" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L71" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M71" s="3" t="str">
         <x:v>第3关，路线来自Map/MapPoint/Spot/Theme</x:v>
       </x:c>
+      <x:c r="N71" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="72" ht="28" customHeight="1">
-      <x:c r="A72" s="3" t="n">
+      <x:c r="A72" s="3" t="str">
         <x:v>67</x:v>
       </x:c>
       <x:c r="B72" s="3" t="str">
@@ -3206,33 +3419,36 @@
       <x:c r="E72" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F72" s="3" t="n">
+      <x:c r="F72" s="3" t="str">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G72" s="3" t="n">
+      <x:c r="G72" s="3" t="str">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H72" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I72" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J72" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K72" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L72" s="3" t="n">
+      <x:c r="H72" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I72" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J72" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K72" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L72" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M72" s="3" t="str">
         <x:v>第4关，路线来自Map/MapPoint/Spot/Theme</x:v>
       </x:c>
+      <x:c r="N72" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="73" ht="28" customHeight="1">
-      <x:c r="A73" s="3" t="n">
+      <x:c r="A73" s="3" t="str">
         <x:v>68</x:v>
       </x:c>
       <x:c r="B73" s="3" t="str">
@@ -3247,33 +3463,36 @@
       <x:c r="E73" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F73" s="3" t="n">
+      <x:c r="F73" s="3" t="str">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G73" s="3" t="n">
+      <x:c r="G73" s="3" t="str">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H73" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I73" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J73" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K73" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L73" s="3" t="n">
+      <x:c r="H73" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I73" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J73" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K73" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L73" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M73" s="3" t="str">
         <x:v>第5关，路线来自Map/MapPoint/Spot/Theme</x:v>
       </x:c>
+      <x:c r="N73" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="74" ht="28" customHeight="1">
-      <x:c r="A74" s="3" t="n">
+      <x:c r="A74" s="3" t="str">
         <x:v>69</x:v>
       </x:c>
       <x:c r="B74" s="3" t="str">
@@ -3288,33 +3507,36 @@
       <x:c r="E74" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F74" s="3" t="n">
+      <x:c r="F74" s="3" t="str">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G74" s="3" t="n">
+      <x:c r="G74" s="3" t="str">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H74" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I74" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J74" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K74" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L74" s="3" t="n">
+      <x:c r="H74" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I74" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J74" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K74" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L74" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M74" s="3" t="str">
         <x:v>第6关，路线来自Map/MapPoint/Spot/Theme</x:v>
       </x:c>
+      <x:c r="N74" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="75" ht="28" customHeight="1">
-      <x:c r="A75" s="3" t="n">
+      <x:c r="A75" s="3" t="str">
         <x:v>70</x:v>
       </x:c>
       <x:c r="B75" s="3" t="str">
@@ -3329,33 +3551,36 @@
       <x:c r="E75" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F75" s="3" t="n">
+      <x:c r="F75" s="3" t="str">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G75" s="3" t="n">
+      <x:c r="G75" s="3" t="str">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H75" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I75" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J75" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K75" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L75" s="3" t="n">
+      <x:c r="H75" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I75" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J75" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K75" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L75" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M75" s="3" t="str">
         <x:v>第7关，路线来自Map/MapPoint/Spot/Theme</x:v>
       </x:c>
+      <x:c r="N75" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="76" ht="28" customHeight="1">
-      <x:c r="A76" s="3" t="n">
+      <x:c r="A76" s="3" t="str">
         <x:v>71</x:v>
       </x:c>
       <x:c r="B76" s="3" t="str">
@@ -3370,33 +3595,36 @@
       <x:c r="E76" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F76" s="3" t="n">
+      <x:c r="F76" s="3" t="str">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G76" s="3" t="n">
+      <x:c r="G76" s="3" t="str">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H76" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I76" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J76" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K76" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L76" s="3" t="n">
+      <x:c r="H76" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I76" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J76" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K76" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L76" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M76" s="3" t="str">
         <x:v>第8关，路线来自Map/MapPoint/Spot/Theme</x:v>
       </x:c>
+      <x:c r="N76" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="77" ht="28" customHeight="1">
-      <x:c r="A77" s="3" t="n">
+      <x:c r="A77" s="3" t="str">
         <x:v>72</x:v>
       </x:c>
       <x:c r="B77" s="3" t="str">
@@ -3411,33 +3639,36 @@
       <x:c r="E77" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F77" s="3" t="n">
+      <x:c r="F77" s="3" t="str">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G77" s="3" t="n">
+      <x:c r="G77" s="3" t="str">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H77" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I77" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J77" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K77" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L77" s="3" t="n">
+      <x:c r="H77" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I77" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J77" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K77" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L77" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M77" s="3" t="str">
         <x:v>第9关，路线来自Map/MapPoint/Spot/Theme</x:v>
       </x:c>
+      <x:c r="N77" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="78" ht="28" customHeight="1">
-      <x:c r="A78" s="3" t="n">
+      <x:c r="A78" s="3" t="str">
         <x:v>73</x:v>
       </x:c>
       <x:c r="B78" s="3" t="str">
@@ -3452,33 +3683,36 @@
       <x:c r="E78" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F78" s="3" t="n">
+      <x:c r="F78" s="3" t="str">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G78" s="3" t="n">
+      <x:c r="G78" s="3" t="str">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H78" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I78" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J78" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K78" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L78" s="3" t="n">
+      <x:c r="H78" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I78" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J78" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K78" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L78" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M78" s="3" t="str">
         <x:v>第10关，路线来自Map/MapPoint/Spot/Theme</x:v>
       </x:c>
+      <x:c r="N78" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="79" ht="28" customHeight="1">
-      <x:c r="A79" s="3" t="n">
+      <x:c r="A79" s="3" t="str">
         <x:v>74</x:v>
       </x:c>
       <x:c r="B79" s="3" t="str">
@@ -3493,33 +3727,36 @@
       <x:c r="E79" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F79" s="3" t="n">
+      <x:c r="F79" s="3" t="str">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G79" s="3" t="n">
+      <x:c r="G79" s="3" t="str">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H79" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I79" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J79" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K79" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L79" s="3" t="n">
+      <x:c r="H79" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I79" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J79" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K79" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L79" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M79" s="3" t="str">
         <x:v>第11关，路线来自Map/MapPoint/Spot/Theme</x:v>
       </x:c>
+      <x:c r="N79" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="80" ht="28" customHeight="1">
-      <x:c r="A80" s="3" t="n">
+      <x:c r="A80" s="3" t="str">
         <x:v>75</x:v>
       </x:c>
       <x:c r="B80" s="3" t="str">
@@ -3534,33 +3771,36 @@
       <x:c r="E80" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F80" s="3" t="n">
+      <x:c r="F80" s="3" t="str">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G80" s="3" t="n">
+      <x:c r="G80" s="3" t="str">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H80" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I80" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J80" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K80" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L80" s="3" t="n">
+      <x:c r="H80" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I80" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J80" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K80" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L80" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M80" s="3" t="str">
         <x:v>第12关，路线来自Map/MapPoint/Spot/Theme</x:v>
       </x:c>
+      <x:c r="N80" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="81" ht="28" customHeight="1">
-      <x:c r="A81" s="3" t="n">
+      <x:c r="A81" s="3" t="str">
         <x:v>76</x:v>
       </x:c>
       <x:c r="B81" s="3" t="str">
@@ -3575,33 +3815,36 @@
       <x:c r="E81" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F81" s="3" t="n">
+      <x:c r="F81" s="3" t="str">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G81" s="3" t="n">
+      <x:c r="G81" s="3" t="str">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H81" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I81" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J81" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K81" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L81" s="3" t="n">
+      <x:c r="H81" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I81" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J81" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K81" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L81" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M81" s="3" t="str">
         <x:v>第13关，路线来自Map/MapPoint/Spot/Theme</x:v>
       </x:c>
+      <x:c r="N81" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="82" ht="28" customHeight="1">
-      <x:c r="A82" s="3" t="n">
+      <x:c r="A82" s="3" t="str">
         <x:v>77</x:v>
       </x:c>
       <x:c r="B82" s="3" t="str">
@@ -3616,33 +3859,36 @@
       <x:c r="E82" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F82" s="3" t="n">
+      <x:c r="F82" s="3" t="str">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G82" s="3" t="n">
+      <x:c r="G82" s="3" t="str">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H82" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I82" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J82" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K82" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L82" s="3" t="n">
+      <x:c r="H82" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I82" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J82" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K82" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L82" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M82" s="3" t="str">
         <x:v>第14关，路线来自Map/MapPoint/Spot/Theme</x:v>
       </x:c>
+      <x:c r="N82" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="83" ht="28" customHeight="1">
-      <x:c r="A83" s="3" t="n">
+      <x:c r="A83" s="3" t="str">
         <x:v>78</x:v>
       </x:c>
       <x:c r="B83" s="3" t="str">
@@ -3657,33 +3903,36 @@
       <x:c r="E83" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F83" s="3" t="n">
+      <x:c r="F83" s="3" t="str">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G83" s="3" t="n">
+      <x:c r="G83" s="3" t="str">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H83" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I83" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J83" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K83" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L83" s="3" t="n">
+      <x:c r="H83" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I83" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J83" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K83" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L83" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M83" s="3" t="str">
         <x:v>第15关，路线来自Map/MapPoint/Spot/Theme</x:v>
       </x:c>
+      <x:c r="N83" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="84" ht="28" customHeight="1">
-      <x:c r="A84" s="3" t="n">
+      <x:c r="A84" s="3" t="str">
         <x:v>79</x:v>
       </x:c>
       <x:c r="B84" s="3" t="str">
@@ -3698,33 +3947,36 @@
       <x:c r="E84" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F84" s="3" t="n">
+      <x:c r="F84" s="3" t="str">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G84" s="3" t="n">
+      <x:c r="G84" s="3" t="str">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H84" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I84" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J84" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K84" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L84" s="3" t="n">
+      <x:c r="H84" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I84" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J84" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K84" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L84" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M84" s="3" t="str">
         <x:v>第16关，路线来自Map/MapPoint/Spot/Theme</x:v>
       </x:c>
+      <x:c r="N84" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="85" ht="28" customHeight="1">
-      <x:c r="A85" s="3" t="n">
+      <x:c r="A85" s="3" t="str">
         <x:v>80</x:v>
       </x:c>
       <x:c r="B85" s="3" t="str">
@@ -3739,33 +3991,36 @@
       <x:c r="E85" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F85" s="3" t="n">
+      <x:c r="F85" s="3" t="str">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G85" s="3" t="n">
+      <x:c r="G85" s="3" t="str">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H85" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I85" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J85" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K85" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L85" s="3" t="n">
+      <x:c r="H85" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I85" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J85" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K85" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L85" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M85" s="3" t="str">
         <x:v>第17关，路线来自Map/MapPoint/Spot/Theme</x:v>
       </x:c>
+      <x:c r="N85" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="86" ht="28" customHeight="1">
-      <x:c r="A86" s="3" t="n">
+      <x:c r="A86" s="3" t="str">
         <x:v>81</x:v>
       </x:c>
       <x:c r="B86" s="3" t="str">
@@ -3780,33 +4035,36 @@
       <x:c r="E86" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F86" s="3" t="n">
+      <x:c r="F86" s="3" t="str">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G86" s="3" t="n">
+      <x:c r="G86" s="3" t="str">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H86" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I86" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J86" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K86" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L86" s="3" t="n">
+      <x:c r="H86" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I86" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J86" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K86" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L86" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M86" s="3" t="str">
         <x:v>第18关，路线来自Map/MapPoint/Spot/Theme</x:v>
       </x:c>
+      <x:c r="N86" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="87" ht="28" customHeight="1">
-      <x:c r="A87" s="3" t="n">
+      <x:c r="A87" s="3" t="str">
         <x:v>82</x:v>
       </x:c>
       <x:c r="B87" s="3" t="str">
@@ -3821,33 +4079,36 @@
       <x:c r="E87" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F87" s="3" t="n">
+      <x:c r="F87" s="3" t="str">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G87" s="3" t="n">
+      <x:c r="G87" s="3" t="str">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H87" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I87" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J87" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K87" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L87" s="3" t="n">
+      <x:c r="H87" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I87" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J87" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K87" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L87" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M87" s="3" t="str">
         <x:v>第19关，路线来自Map/MapPoint/Spot/Theme</x:v>
       </x:c>
+      <x:c r="N87" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="88" ht="28" customHeight="1">
-      <x:c r="A88" s="3" t="n">
+      <x:c r="A88" s="3" t="str">
         <x:v>83</x:v>
       </x:c>
       <x:c r="B88" s="3" t="str">
@@ -3862,33 +4123,36 @@
       <x:c r="E88" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F88" s="3" t="n">
+      <x:c r="F88" s="3" t="str">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G88" s="3" t="n">
+      <x:c r="G88" s="3" t="str">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H88" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I88" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J88" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K88" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L88" s="3" t="n">
+      <x:c r="H88" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I88" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J88" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K88" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L88" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M88" s="3" t="str">
         <x:v>第20关，路线来自Map/MapPoint/Spot/Theme</x:v>
       </x:c>
+      <x:c r="N88" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="89" ht="28" customHeight="1">
-      <x:c r="A89" s="3" t="n">
+      <x:c r="A89" s="3" t="str">
         <x:v>84</x:v>
       </x:c>
       <x:c r="B89" s="3" t="str">
@@ -3903,33 +4167,36 @@
       <x:c r="E89" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F89" s="3" t="n">
+      <x:c r="F89" s="3" t="str">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G89" s="3" t="n">
+      <x:c r="G89" s="3" t="str">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H89" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I89" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J89" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K89" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L89" s="3" t="n">
+      <x:c r="H89" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I89" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J89" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K89" s="3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L89" s="3" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M89" s="3" t="str">
         <x:v>第21关，路线来自Map/MapPoint/Spot/Theme</x:v>
       </x:c>
+      <x:c r="N89" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="90">
-      <x:c r="A90" t="n">
+      <x:c r="A90" t="str">
         <x:v>85</x:v>
       </x:c>
       <x:c r="B90" t="str">
@@ -3950,27 +4217,30 @@
       <x:c r="G90" t="n">
         <x:v>1672</x:v>
       </x:c>
-      <x:c r="H90" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I90" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J90" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K90" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L90" t="n">
+      <x:c r="H90" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I90" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J90" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K90" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L90" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M90" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N90" t="str">
+        <x:v>cover</x:v>
+      </x:c>
     </x:row>
     <x:row r="91">
-      <x:c r="A91" t="n">
+      <x:c r="A91" t="str">
         <x:v>86</x:v>
       </x:c>
       <x:c r="B91" t="str">
@@ -3991,27 +4261,30 @@
       <x:c r="G91" t="n">
         <x:v>1672</x:v>
       </x:c>
-      <x:c r="H91" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I91" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J91" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K91" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L91" t="n">
+      <x:c r="H91" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I91" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J91" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K91" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L91" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M91" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N91" t="str">
+        <x:v>cover</x:v>
+      </x:c>
     </x:row>
     <x:row r="92">
-      <x:c r="A92" t="n">
+      <x:c r="A92" t="str">
         <x:v>87</x:v>
       </x:c>
       <x:c r="B92" t="str">
@@ -4027,32 +4300,35 @@
         <x:v>sliced</x:v>
       </x:c>
       <x:c r="F92" t="n">
-        <x:v>112</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="G92" t="n">
-        <x:v>112</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="H92" t="n">
-        <x:v>20</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I92" t="n">
-        <x:v>20</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="J92" t="n">
-        <x:v>20</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K92" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="L92" t="n">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="L92" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M92" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N92" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="93">
-      <x:c r="A93" t="n">
+      <x:c r="A93" t="str">
         <x:v>88</x:v>
       </x:c>
       <x:c r="B93" t="str">
@@ -4068,32 +4344,35 @@
         <x:v>sliced</x:v>
       </x:c>
       <x:c r="F93" t="n">
-        <x:v>160</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="G93" t="n">
-        <x:v>48</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="H93" t="n">
-        <x:v>24</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I93" t="n">
-        <x:v>24</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J93" t="n">
-        <x:v>12</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K93" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="L93" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="L93" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M93" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N93" t="str">
+        <x:v>height</x:v>
+      </x:c>
     </x:row>
     <x:row r="94">
-      <x:c r="A94" t="n">
+      <x:c r="A94" t="str">
         <x:v>89</x:v>
       </x:c>
       <x:c r="B94" t="str">
@@ -4109,32 +4388,35 @@
         <x:v>sliced</x:v>
       </x:c>
       <x:c r="F94" t="n">
-        <x:v>160</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="G94" t="n">
-        <x:v>48</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="H94" t="n">
-        <x:v>24</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I94" t="n">
-        <x:v>24</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J94" t="n">
-        <x:v>12</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K94" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="L94" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="L94" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M94" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N94" t="str">
+        <x:v>height</x:v>
+      </x:c>
     </x:row>
     <x:row r="95">
-      <x:c r="A95" t="n">
+      <x:c r="A95" t="str">
         <x:v>90</x:v>
       </x:c>
       <x:c r="B95" t="str">
@@ -4150,32 +4432,35 @@
         <x:v>simple</x:v>
       </x:c>
       <x:c r="F95" t="n">
-        <x:v>299</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G95" t="n">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="H95" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I95" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J95" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K95" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L95" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H95" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I95" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J95" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K95" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L95" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M95" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N95" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="96">
-      <x:c r="A96" t="n">
+      <x:c r="A96" t="str">
         <x:v>91</x:v>
       </x:c>
       <x:c r="B96" t="str">
@@ -4191,32 +4476,35 @@
         <x:v>sliced</x:v>
       </x:c>
       <x:c r="F96" t="n">
-        <x:v>128</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="G96" t="n">
-        <x:v>44</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H96" t="n">
-        <x:v>14</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="I96" t="n">
-        <x:v>14</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="J96" t="n">
-        <x:v>12</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K96" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="L96" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="L96" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M96" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N96" t="str">
+        <x:v>height</x:v>
+      </x:c>
     </x:row>
     <x:row r="97">
-      <x:c r="A97" t="n">
+      <x:c r="A97" t="str">
         <x:v>92</x:v>
       </x:c>
       <x:c r="B97" t="str">
@@ -4232,32 +4520,35 @@
         <x:v>sliced</x:v>
       </x:c>
       <x:c r="F97" t="n">
-        <x:v>128</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="G97" t="n">
-        <x:v>44</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="H97" t="n">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="I97" t="n">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="J97" t="n">
-        <x:v>12</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="K97" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="L97" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L97" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M97" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N97" t="str">
+        <x:v>height</x:v>
+      </x:c>
     </x:row>
     <x:row r="98">
-      <x:c r="A98" t="n">
+      <x:c r="A98" t="str">
         <x:v>93</x:v>
       </x:c>
       <x:c r="B98" t="str">
@@ -4273,32 +4564,35 @@
         <x:v>simple</x:v>
       </x:c>
       <x:c r="F98" t="n">
-        <x:v>181</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G98" t="n">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="H98" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I98" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J98" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K98" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L98" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H98" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I98" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J98" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K98" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L98" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M98" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N98" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="99">
-      <x:c r="A99" t="n">
+      <x:c r="A99" t="str">
         <x:v>94</x:v>
       </x:c>
       <x:c r="B99" t="str">
@@ -4314,32 +4608,35 @@
         <x:v>sliced</x:v>
       </x:c>
       <x:c r="F99" t="n">
-        <x:v>128</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="G99" t="n">
-        <x:v>24</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H99" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I99" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J99" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="I99" t="n">
+      <x:c r="K99" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="J99" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="K99" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="L99" t="n">
+      <x:c r="L99" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M99" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N99" t="str">
+        <x:v>height</x:v>
+      </x:c>
     </x:row>
     <x:row r="100">
-      <x:c r="A100" t="n">
+      <x:c r="A100" t="str">
         <x:v>95</x:v>
       </x:c>
       <x:c r="B100" t="str">
@@ -4355,32 +4652,35 @@
         <x:v>sliced</x:v>
       </x:c>
       <x:c r="F100" t="n">
-        <x:v>112</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="G100" t="n">
-        <x:v>30</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="H100" t="n">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I100" t="n">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J100" t="n">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="K100" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="L100" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L100" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M100" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N100" t="str">
+        <x:v>height</x:v>
+      </x:c>
     </x:row>
     <x:row r="101">
-      <x:c r="A101" t="n">
+      <x:c r="A101" t="str">
         <x:v>96</x:v>
       </x:c>
       <x:c r="B101" t="str">
@@ -4396,32 +4696,35 @@
         <x:v>simple</x:v>
       </x:c>
       <x:c r="F101" t="n">
-        <x:v>488</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="G101" t="n">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="H101" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I101" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J101" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K101" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L101" t="n">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="H101" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I101" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J101" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K101" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L101" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M101" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N101" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="102">
-      <x:c r="A102" t="n">
+      <x:c r="A102" t="str">
         <x:v>97</x:v>
       </x:c>
       <x:c r="B102" t="str">
@@ -4437,32 +4740,35 @@
         <x:v>sliced</x:v>
       </x:c>
       <x:c r="F102" t="n">
-        <x:v>160</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="G102" t="n">
-        <x:v>48</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="H102" t="n">
-        <x:v>16</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="I102" t="n">
-        <x:v>16</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="J102" t="n">
-        <x:v>12</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="K102" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="L102" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="L102" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M102" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N102" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="103">
-      <x:c r="A103" t="n">
+      <x:c r="A103" t="str">
         <x:v>98</x:v>
       </x:c>
       <x:c r="B103" t="str">
@@ -4478,32 +4784,35 @@
         <x:v>sliced</x:v>
       </x:c>
       <x:c r="F103" t="n">
-        <x:v>160</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="G103" t="n">
-        <x:v>48</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="H103" t="n">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="I103" t="n">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="J103" t="n">
-        <x:v>12</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="K103" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="L103" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L103" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M103" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N103" t="str">
+        <x:v>height</x:v>
+      </x:c>
     </x:row>
     <x:row r="104">
-      <x:c r="A104" t="n">
+      <x:c r="A104" t="str">
         <x:v>99</x:v>
       </x:c>
       <x:c r="B104" t="str">
@@ -4519,32 +4828,35 @@
         <x:v>sliced</x:v>
       </x:c>
       <x:c r="F104" t="n">
-        <x:v>390</x:v>
+        <x:v>1086</x:v>
       </x:c>
       <x:c r="G104" t="n">
-        <x:v>540</x:v>
+        <x:v>1448</x:v>
       </x:c>
       <x:c r="H104" t="n">
-        <x:v>24</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="I104" t="n">
-        <x:v>24</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="J104" t="n">
-        <x:v>76</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="K104" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="L104" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="L104" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M104" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N104" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
     </x:row>
     <x:row r="105">
-      <x:c r="A105" t="n">
+      <x:c r="A105" t="str">
         <x:v>100</x:v>
       </x:c>
       <x:c r="B105" t="str">
@@ -4560,32 +4872,35 @@
         <x:v>simple</x:v>
       </x:c>
       <x:c r="F105" t="n">
-        <x:v>272</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G105" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="H105" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I105" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J105" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K105" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L105" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H105" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I105" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J105" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K105" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L105" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M105" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N105" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="106">
-      <x:c r="A106" t="n">
+      <x:c r="A106" t="str">
         <x:v>101</x:v>
       </x:c>
       <x:c r="B106" t="str">
@@ -4601,32 +4916,35 @@
         <x:v>simple</x:v>
       </x:c>
       <x:c r="F106" t="n">
-        <x:v>291</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G106" t="n">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="H106" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I106" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J106" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K106" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L106" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H106" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I106" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J106" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K106" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L106" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M106" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N106" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="107">
-      <x:c r="A107" t="n">
+      <x:c r="A107" t="str">
         <x:v>102</x:v>
       </x:c>
       <x:c r="B107" t="str">
@@ -4642,32 +4960,35 @@
         <x:v>simple</x:v>
       </x:c>
       <x:c r="F107" t="n">
-        <x:v>306</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G107" t="n">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="H107" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I107" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J107" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K107" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L107" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H107" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I107" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J107" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K107" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L107" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M107" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N107" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="108">
-      <x:c r="A108" t="n">
+      <x:c r="A108" t="str">
         <x:v>103</x:v>
       </x:c>
       <x:c r="B108" t="str">
@@ -4683,32 +5004,35 @@
         <x:v>simple</x:v>
       </x:c>
       <x:c r="F108" t="n">
-        <x:v>287</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G108" t="n">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="H108" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I108" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J108" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K108" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L108" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H108" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I108" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J108" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K108" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L108" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M108" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N108" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="109">
-      <x:c r="A109" t="n">
+      <x:c r="A109" t="str">
         <x:v>104</x:v>
       </x:c>
       <x:c r="B109" t="str">
@@ -4724,32 +5048,35 @@
         <x:v>simple</x:v>
       </x:c>
       <x:c r="F109" t="n">
-        <x:v>293</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G109" t="n">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="H109" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I109" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J109" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K109" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L109" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H109" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I109" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J109" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K109" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L109" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M109" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N109" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="110">
-      <x:c r="A110" t="n">
+      <x:c r="A110" t="str">
         <x:v>105</x:v>
       </x:c>
       <x:c r="B110" t="str">
@@ -4765,32 +5092,35 @@
         <x:v>simple</x:v>
       </x:c>
       <x:c r="F110" t="n">
-        <x:v>284</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G110" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="H110" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I110" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J110" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K110" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L110" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H110" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I110" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J110" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K110" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L110" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M110" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N110" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="111">
-      <x:c r="A111" t="n">
+      <x:c r="A111" t="str">
         <x:v>106</x:v>
       </x:c>
       <x:c r="B111" t="str">
@@ -4806,32 +5136,35 @@
         <x:v>simple</x:v>
       </x:c>
       <x:c r="F111" t="n">
-        <x:v>314</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G111" t="n">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="H111" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I111" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J111" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K111" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L111" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H111" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I111" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J111" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K111" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L111" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M111" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N111" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="112">
-      <x:c r="A112" t="n">
+      <x:c r="A112" t="str">
         <x:v>107</x:v>
       </x:c>
       <x:c r="B112" t="str">
@@ -4847,32 +5180,35 @@
         <x:v>simple</x:v>
       </x:c>
       <x:c r="F112" t="n">
-        <x:v>293</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G112" t="n">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="H112" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I112" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J112" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K112" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L112" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H112" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I112" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J112" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K112" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L112" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M112" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N112" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="113">
-      <x:c r="A113" t="n">
+      <x:c r="A113" t="str">
         <x:v>108</x:v>
       </x:c>
       <x:c r="B113" t="str">
@@ -4888,32 +5224,35 @@
         <x:v>simple</x:v>
       </x:c>
       <x:c r="F113" t="n">
-        <x:v>207</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G113" t="n">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="H113" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I113" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J113" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K113" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L113" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H113" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I113" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J113" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K113" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L113" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M113" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N113" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="114">
-      <x:c r="A114" t="n">
+      <x:c r="A114" t="str">
         <x:v>109</x:v>
       </x:c>
       <x:c r="B114" t="str">
@@ -4929,32 +5268,35 @@
         <x:v>simple</x:v>
       </x:c>
       <x:c r="F114" t="n">
-        <x:v>235</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G114" t="n">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="H114" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I114" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J114" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K114" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L114" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H114" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I114" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J114" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K114" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L114" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M114" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N114" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="115">
-      <x:c r="A115" t="n">
+      <x:c r="A115" t="str">
         <x:v>110</x:v>
       </x:c>
       <x:c r="B115" t="str">
@@ -4970,32 +5312,35 @@
         <x:v>simple</x:v>
       </x:c>
       <x:c r="F115" t="n">
-        <x:v>274</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G115" t="n">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="H115" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I115" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J115" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K115" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L115" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H115" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I115" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J115" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K115" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L115" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M115" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N115" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="116">
-      <x:c r="A116" t="n">
+      <x:c r="A116" t="str">
         <x:v>111</x:v>
       </x:c>
       <x:c r="B116" t="str">
@@ -5011,32 +5356,35 @@
         <x:v>simple</x:v>
       </x:c>
       <x:c r="F116" t="n">
-        <x:v>274</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G116" t="n">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="H116" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I116" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J116" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K116" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L116" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H116" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I116" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J116" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K116" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L116" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M116" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N116" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="117">
-      <x:c r="A117" t="n">
+      <x:c r="A117" t="str">
         <x:v>112</x:v>
       </x:c>
       <x:c r="B117" t="str">
@@ -5055,29 +5403,32 @@
         <x:v>256</x:v>
       </x:c>
       <x:c r="G117" t="n">
-        <x:v>353</x:v>
-      </x:c>
-      <x:c r="H117" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I117" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J117" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K117" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L117" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H117" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I117" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J117" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K117" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L117" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M117" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N117" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="118">
-      <x:c r="A118" t="n">
+      <x:c r="A118" t="str">
         <x:v>113</x:v>
       </x:c>
       <x:c r="B118" t="str">
@@ -5093,32 +5444,35 @@
         <x:v>simple</x:v>
       </x:c>
       <x:c r="F118" t="n">
-        <x:v>378</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G118" t="n">
-        <x:v>355</x:v>
-      </x:c>
-      <x:c r="H118" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I118" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J118" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K118" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L118" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H118" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I118" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J118" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K118" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L118" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M118" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N118" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="119">
-      <x:c r="A119" t="n">
+      <x:c r="A119" t="str">
         <x:v>114</x:v>
       </x:c>
       <x:c r="B119" t="str">
@@ -5134,32 +5488,35 @@
         <x:v>simple</x:v>
       </x:c>
       <x:c r="F119" t="n">
-        <x:v>345</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G119" t="n">
-        <x:v>332</x:v>
-      </x:c>
-      <x:c r="H119" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I119" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J119" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K119" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L119" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H119" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I119" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J119" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K119" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L119" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M119" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N119" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="120">
-      <x:c r="A120" t="n">
+      <x:c r="A120" t="str">
         <x:v>115</x:v>
       </x:c>
       <x:c r="B120" t="str">
@@ -5175,32 +5532,35 @@
         <x:v>simple</x:v>
       </x:c>
       <x:c r="F120" t="n">
-        <x:v>293</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G120" t="n">
-        <x:v>332</x:v>
-      </x:c>
-      <x:c r="H120" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I120" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J120" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K120" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L120" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H120" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I120" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J120" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K120" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L120" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M120" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N120" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="121">
-      <x:c r="A121" t="n">
+      <x:c r="A121" t="str">
         <x:v>116</x:v>
       </x:c>
       <x:c r="B121" t="str">
@@ -5216,32 +5576,35 @@
         <x:v>simple</x:v>
       </x:c>
       <x:c r="F121" t="n">
-        <x:v>343</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G121" t="n">
-        <x:v>392</x:v>
-      </x:c>
-      <x:c r="H121" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I121" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J121" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K121" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L121" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H121" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I121" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J121" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K121" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L121" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M121" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N121" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="122">
-      <x:c r="A122" t="n">
+      <x:c r="A122" t="str">
         <x:v>117</x:v>
       </x:c>
       <x:c r="B122" t="str">
@@ -5257,32 +5620,35 @@
         <x:v>simple</x:v>
       </x:c>
       <x:c r="F122" t="n">
-        <x:v>376</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G122" t="n">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="H122" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I122" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J122" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K122" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L122" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H122" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I122" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J122" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K122" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L122" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M122" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N122" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="123">
-      <x:c r="A123" t="n">
+      <x:c r="A123" t="str">
         <x:v>118</x:v>
       </x:c>
       <x:c r="B123" t="str">
@@ -5298,32 +5664,35 @@
         <x:v>simple</x:v>
       </x:c>
       <x:c r="F123" t="n">
-        <x:v>389</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G123" t="n">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="H123" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I123" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J123" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K123" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L123" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H123" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I123" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J123" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K123" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L123" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M123" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N123" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="124">
-      <x:c r="A124" t="n">
+      <x:c r="A124" t="str">
         <x:v>119</x:v>
       </x:c>
       <x:c r="B124" t="str">
@@ -5339,32 +5708,35 @@
         <x:v>simple</x:v>
       </x:c>
       <x:c r="F124" t="n">
-        <x:v>293</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G124" t="n">
-        <x:v>362</x:v>
-      </x:c>
-      <x:c r="H124" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I124" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J124" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K124" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L124" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H124" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I124" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J124" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K124" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L124" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M124" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N124" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="125">
-      <x:c r="A125" t="n">
+      <x:c r="A125" t="str">
         <x:v>120</x:v>
       </x:c>
       <x:c r="B125" t="str">
@@ -5380,32 +5752,35 @@
         <x:v>simple</x:v>
       </x:c>
       <x:c r="F125" t="n">
-        <x:v>366</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G125" t="n">
-        <x:v>317</x:v>
-      </x:c>
-      <x:c r="H125" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I125" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J125" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K125" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L125" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H125" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I125" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J125" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K125" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L125" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M125" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
       </x:c>
+      <x:c r="N125" t="str">
+        <x:v>contain</x:v>
+      </x:c>
     </x:row>
     <x:row r="126" ht="28" customHeight="1">
-      <x:c r="A126" t="n">
+      <x:c r="A126" t="str">
         <x:v>121</x:v>
       </x:c>
       <x:c r="B126" t="str">
@@ -5426,23 +5801,26 @@
       <x:c r="G126" t="n">
         <x:v>1254</x:v>
       </x:c>
-      <x:c r="H126" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I126" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J126" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K126" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L126" t="n">
+      <x:c r="H126" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I126" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J126" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K126" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L126" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M126" t="str">
         <x:v>2026-10-07用户UI参考；PNG可替换</x:v>
+      </x:c>
+      <x:c r="N126" t="str">
+        <x:v>cover</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/VisualSkin.xlsx
+++ b/design/tables/VisualSkin.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisualSkin" sheetId="1" r:id="R7a9478e3e2c847a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisualSkin" sheetId="1" r:id="R234a22d7a68c44d4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -500,7 +500,7 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="28" customHeight="1">
-      <x:c r="A6" s="3" t="str">
+      <x:c r="A6" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="3" t="str">
@@ -515,25 +515,25 @@
       <x:c r="E6" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F6" s="3" t="str">
+      <x:c r="F6" s="3" t="n">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="G6" s="3" t="str">
+      <x:c r="G6" s="3" t="n">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="H6" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I6" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J6" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K6" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L6" s="3" t="str">
+      <x:c r="H6" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I6" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J6" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K6" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L6" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M6" s="3" t="str">
@@ -544,7 +544,7 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="28" customHeight="1">
-      <x:c r="A7" s="3" t="str">
+      <x:c r="A7" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B7" s="3" t="str">
@@ -559,25 +559,25 @@
       <x:c r="E7" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F7" s="3" t="str">
+      <x:c r="F7" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G7" s="3" t="str">
+      <x:c r="G7" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H7" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I7" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J7" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K7" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L7" s="3" t="str">
+      <x:c r="H7" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I7" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J7" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K7" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L7" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M7" s="3" t="str">
@@ -588,7 +588,7 @@
       </x:c>
     </x:row>
     <x:row r="8" ht="28" customHeight="1">
-      <x:c r="A8" s="3" t="str">
+      <x:c r="A8" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B8" s="3" t="str">
@@ -603,25 +603,25 @@
       <x:c r="E8" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F8" s="3" t="str">
+      <x:c r="F8" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G8" s="3" t="str">
+      <x:c r="G8" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H8" s="3" t="str">
+      <x:c r="H8" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I8" s="3" t="str">
+      <x:c r="I8" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J8" s="3" t="str">
+      <x:c r="J8" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K8" s="3" t="str">
+      <x:c r="K8" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L8" s="3" t="str">
+      <x:c r="L8" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M8" s="3" t="str">
@@ -632,7 +632,7 @@
       </x:c>
     </x:row>
     <x:row r="9" ht="28" customHeight="1">
-      <x:c r="A9" s="3" t="str">
+      <x:c r="A9" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B9" s="3" t="str">
@@ -647,25 +647,25 @@
       <x:c r="E9" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F9" s="3" t="str">
+      <x:c r="F9" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G9" s="3" t="str">
+      <x:c r="G9" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H9" s="3" t="str">
+      <x:c r="H9" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I9" s="3" t="str">
+      <x:c r="I9" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J9" s="3" t="str">
+      <x:c r="J9" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K9" s="3" t="str">
+      <x:c r="K9" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L9" s="3" t="str">
+      <x:c r="L9" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M9" s="3" t="str">
@@ -676,7 +676,7 @@
       </x:c>
     </x:row>
     <x:row r="10" ht="28" customHeight="1">
-      <x:c r="A10" s="3" t="str">
+      <x:c r="A10" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B10" s="3" t="str">
@@ -691,25 +691,25 @@
       <x:c r="E10" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F10" s="3" t="str">
+      <x:c r="F10" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G10" s="3" t="str">
+      <x:c r="G10" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H10" s="3" t="str">
+      <x:c r="H10" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I10" s="3" t="str">
+      <x:c r="I10" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J10" s="3" t="str">
+      <x:c r="J10" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K10" s="3" t="str">
+      <x:c r="K10" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L10" s="3" t="str">
+      <x:c r="L10" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M10" s="3" t="str">
@@ -720,7 +720,7 @@
       </x:c>
     </x:row>
     <x:row r="11" ht="28" customHeight="1">
-      <x:c r="A11" s="3" t="str">
+      <x:c r="A11" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B11" s="3" t="str">
@@ -735,25 +735,25 @@
       <x:c r="E11" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F11" s="3" t="str">
+      <x:c r="F11" s="3" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G11" s="3" t="str">
+      <x:c r="G11" s="3" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H11" s="3" t="str">
+      <x:c r="H11" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I11" s="3" t="str">
+      <x:c r="I11" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J11" s="3" t="str">
+      <x:c r="J11" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K11" s="3" t="str">
+      <x:c r="K11" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L11" s="3" t="str">
+      <x:c r="L11" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M11" s="3" t="str">
@@ -764,7 +764,7 @@
       </x:c>
     </x:row>
     <x:row r="12" ht="28" customHeight="1">
-      <x:c r="A12" s="3" t="str">
+      <x:c r="A12" s="3" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B12" s="3" t="str">
@@ -779,25 +779,25 @@
       <x:c r="E12" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F12" s="3" t="str">
+      <x:c r="F12" s="3" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G12" s="3" t="str">
+      <x:c r="G12" s="3" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H12" s="3" t="str">
+      <x:c r="H12" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I12" s="3" t="str">
+      <x:c r="I12" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J12" s="3" t="str">
+      <x:c r="J12" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K12" s="3" t="str">
+      <x:c r="K12" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L12" s="3" t="str">
+      <x:c r="L12" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M12" s="3" t="str">
@@ -808,7 +808,7 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="28" customHeight="1">
-      <x:c r="A13" s="3" t="str">
+      <x:c r="A13" s="3" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B13" s="3" t="str">
@@ -823,25 +823,25 @@
       <x:c r="E13" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F13" s="3" t="str">
+      <x:c r="F13" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G13" s="3" t="str">
+      <x:c r="G13" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H13" s="3" t="str">
+      <x:c r="H13" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I13" s="3" t="str">
+      <x:c r="I13" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J13" s="3" t="str">
+      <x:c r="J13" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K13" s="3" t="str">
+      <x:c r="K13" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L13" s="3" t="str">
+      <x:c r="L13" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M13" s="3" t="str">
@@ -852,7 +852,7 @@
       </x:c>
     </x:row>
     <x:row r="14" ht="28" customHeight="1">
-      <x:c r="A14" s="3" t="str">
+      <x:c r="A14" s="3" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B14" s="3" t="str">
@@ -867,25 +867,25 @@
       <x:c r="E14" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F14" s="3" t="str">
+      <x:c r="F14" s="3" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="G14" s="3" t="str">
+      <x:c r="G14" s="3" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="H14" s="3" t="str">
+      <x:c r="H14" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I14" s="3" t="str">
+      <x:c r="I14" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J14" s="3" t="str">
+      <x:c r="J14" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K14" s="3" t="str">
+      <x:c r="K14" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="L14" s="3" t="str">
+      <x:c r="L14" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M14" s="3" t="str">
@@ -896,7 +896,7 @@
       </x:c>
     </x:row>
     <x:row r="15" ht="28" customHeight="1">
-      <x:c r="A15" s="3" t="str">
+      <x:c r="A15" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B15" s="3" t="str">
@@ -911,25 +911,25 @@
       <x:c r="E15" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F15" s="3" t="str">
+      <x:c r="F15" s="3" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="G15" s="3" t="str">
+      <x:c r="G15" s="3" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="H15" s="3" t="str">
+      <x:c r="H15" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I15" s="3" t="str">
+      <x:c r="I15" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J15" s="3" t="str">
+      <x:c r="J15" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K15" s="3" t="str">
+      <x:c r="K15" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L15" s="3" t="str">
+      <x:c r="L15" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M15" s="3" t="str">
@@ -940,7 +940,7 @@
       </x:c>
     </x:row>
     <x:row r="16" ht="28" customHeight="1">
-      <x:c r="A16" s="3" t="str">
+      <x:c r="A16" s="3" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B16" s="3" t="str">
@@ -955,25 +955,25 @@
       <x:c r="E16" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F16" s="3" t="str">
+      <x:c r="F16" s="3" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G16" s="3" t="str">
+      <x:c r="G16" s="3" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H16" s="3" t="str">
+      <x:c r="H16" s="3" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I16" s="3" t="str">
+      <x:c r="I16" s="3" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J16" s="3" t="str">
+      <x:c r="J16" s="3" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="K16" s="3" t="str">
+      <x:c r="K16" s="3" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="L16" s="3" t="str">
+      <x:c r="L16" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M16" s="3" t="str">
@@ -984,7 +984,7 @@
       </x:c>
     </x:row>
     <x:row r="17" ht="28" customHeight="1">
-      <x:c r="A17" s="3" t="str">
+      <x:c r="A17" s="3" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B17" s="3" t="str">
@@ -999,25 +999,25 @@
       <x:c r="E17" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F17" s="3" t="str">
+      <x:c r="F17" s="3" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G17" s="3" t="str">
+      <x:c r="G17" s="3" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H17" s="3" t="str">
+      <x:c r="H17" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I17" s="3" t="str">
+      <x:c r="I17" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J17" s="3" t="str">
+      <x:c r="J17" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K17" s="3" t="str">
+      <x:c r="K17" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L17" s="3" t="str">
+      <x:c r="L17" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M17" s="3" t="str">
@@ -1028,7 +1028,7 @@
       </x:c>
     </x:row>
     <x:row r="18" ht="28" customHeight="1">
-      <x:c r="A18" s="3" t="str">
+      <x:c r="A18" s="3" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B18" s="3" t="str">
@@ -1043,25 +1043,25 @@
       <x:c r="E18" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F18" s="3" t="str">
+      <x:c r="F18" s="3" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G18" s="3" t="str">
+      <x:c r="G18" s="3" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="H18" s="3" t="str">
+      <x:c r="H18" s="3" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="I18" s="3" t="str">
+      <x:c r="I18" s="3" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="J18" s="3" t="str">
+      <x:c r="J18" s="3" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="K18" s="3" t="str">
+      <x:c r="K18" s="3" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="L18" s="3" t="str">
+      <x:c r="L18" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M18" s="3" t="str">
@@ -1072,7 +1072,7 @@
       </x:c>
     </x:row>
     <x:row r="19" ht="28" customHeight="1">
-      <x:c r="A19" s="3" t="str">
+      <x:c r="A19" s="3" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B19" s="3" t="str">
@@ -1087,25 +1087,25 @@
       <x:c r="E19" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F19" s="3" t="str">
+      <x:c r="F19" s="3" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G19" s="3" t="str">
+      <x:c r="G19" s="3" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H19" s="3" t="str">
+      <x:c r="H19" s="3" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="I19" s="3" t="str">
+      <x:c r="I19" s="3" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="J19" s="3" t="str">
+      <x:c r="J19" s="3" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="K19" s="3" t="str">
+      <x:c r="K19" s="3" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="L19" s="3" t="str">
+      <x:c r="L19" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M19" s="3" t="str">
@@ -1116,7 +1116,7 @@
       </x:c>
     </x:row>
     <x:row r="20" ht="28" customHeight="1">
-      <x:c r="A20" s="3" t="str">
+      <x:c r="A20" s="3" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B20" s="3" t="str">
@@ -1131,25 +1131,25 @@
       <x:c r="E20" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F20" s="3" t="str">
+      <x:c r="F20" s="3" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="G20" s="3" t="str">
+      <x:c r="G20" s="3" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="H20" s="3" t="str">
+      <x:c r="H20" s="3" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="I20" s="3" t="str">
+      <x:c r="I20" s="3" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="J20" s="3" t="str">
+      <x:c r="J20" s="3" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="K20" s="3" t="str">
+      <x:c r="K20" s="3" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="L20" s="3" t="str">
+      <x:c r="L20" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M20" s="3" t="str">
@@ -1160,7 +1160,7 @@
       </x:c>
     </x:row>
     <x:row r="21" ht="28" customHeight="1">
-      <x:c r="A21" s="3" t="str">
+      <x:c r="A21" s="3" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B21" s="3" t="str">
@@ -1175,25 +1175,25 @@
       <x:c r="E21" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F21" s="3" t="str">
+      <x:c r="F21" s="3" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G21" s="3" t="str">
+      <x:c r="G21" s="3" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="H21" s="3" t="str">
+      <x:c r="H21" s="3" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I21" s="3" t="str">
+      <x:c r="I21" s="3" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="J21" s="3" t="str">
+      <x:c r="J21" s="3" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K21" s="3" t="str">
+      <x:c r="K21" s="3" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="L21" s="3" t="str">
+      <x:c r="L21" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M21" s="3" t="str">
@@ -1204,7 +1204,7 @@
       </x:c>
     </x:row>
     <x:row r="22" ht="28" customHeight="1">
-      <x:c r="A22" s="3" t="str">
+      <x:c r="A22" s="3" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B22" s="3" t="str">
@@ -1219,25 +1219,25 @@
       <x:c r="E22" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F22" s="3" t="str">
+      <x:c r="F22" s="3" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G22" s="3" t="str">
+      <x:c r="G22" s="3" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H22" s="3" t="str">
+      <x:c r="H22" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I22" s="3" t="str">
+      <x:c r="I22" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J22" s="3" t="str">
+      <x:c r="J22" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K22" s="3" t="str">
+      <x:c r="K22" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L22" s="3" t="str">
+      <x:c r="L22" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="M22" s="3" t="str">
@@ -1248,7 +1248,7 @@
       </x:c>
     </x:row>
     <x:row r="23" ht="28" customHeight="1">
-      <x:c r="A23" s="3" t="str">
+      <x:c r="A23" s="3" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B23" s="3" t="str">
@@ -1263,25 +1263,25 @@
       <x:c r="E23" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F23" s="3" t="str">
+      <x:c r="F23" s="3" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G23" s="3" t="str">
+      <x:c r="G23" s="3" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="H23" s="3" t="str">
+      <x:c r="H23" s="3" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="I23" s="3" t="str">
+      <x:c r="I23" s="3" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J23" s="3" t="str">
+      <x:c r="J23" s="3" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="K23" s="3" t="str">
+      <x:c r="K23" s="3" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L23" s="3" t="str">
+      <x:c r="L23" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="M23" s="3" t="str">
@@ -1292,7 +1292,7 @@
       </x:c>
     </x:row>
     <x:row r="24" ht="28" customHeight="1">
-      <x:c r="A24" s="3" t="str">
+      <x:c r="A24" s="3" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B24" s="3" t="str">
@@ -1307,25 +1307,25 @@
       <x:c r="E24" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F24" s="3" t="str">
+      <x:c r="F24" s="3" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G24" s="3" t="str">
+      <x:c r="G24" s="3" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="H24" s="3" t="str">
+      <x:c r="H24" s="3" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="I24" s="3" t="str">
+      <x:c r="I24" s="3" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="J24" s="3" t="str">
+      <x:c r="J24" s="3" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="K24" s="3" t="str">
+      <x:c r="K24" s="3" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="L24" s="3" t="str">
+      <x:c r="L24" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="M24" s="3" t="str">
@@ -1336,7 +1336,7 @@
       </x:c>
     </x:row>
     <x:row r="25" ht="28" customHeight="1">
-      <x:c r="A25" s="3" t="str">
+      <x:c r="A25" s="3" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B25" s="3" t="str">
@@ -1351,25 +1351,25 @@
       <x:c r="E25" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F25" s="3" t="str">
+      <x:c r="F25" s="3" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="G25" s="3" t="str">
+      <x:c r="G25" s="3" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H25" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I25" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J25" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K25" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L25" s="3" t="str">
+      <x:c r="H25" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I25" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J25" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K25" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L25" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M25" s="3" t="str">
@@ -1380,7 +1380,7 @@
       </x:c>
     </x:row>
     <x:row r="26" ht="28" customHeight="1">
-      <x:c r="A26" s="3" t="str">
+      <x:c r="A26" s="3" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B26" s="3" t="str">
@@ -1395,25 +1395,25 @@
       <x:c r="E26" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F26" s="3" t="str">
+      <x:c r="F26" s="3" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="G26" s="3" t="str">
+      <x:c r="G26" s="3" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H26" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I26" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J26" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K26" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L26" s="3" t="str">
+      <x:c r="H26" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I26" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J26" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K26" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L26" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M26" s="3" t="str">
@@ -1424,7 +1424,7 @@
       </x:c>
     </x:row>
     <x:row r="27" ht="28" customHeight="1">
-      <x:c r="A27" s="3" t="str">
+      <x:c r="A27" s="3" t="n">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B27" s="3" t="str">
@@ -1439,25 +1439,25 @@
       <x:c r="E27" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F27" s="3" t="str">
+      <x:c r="F27" s="3" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="G27" s="3" t="str">
+      <x:c r="G27" s="3" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H27" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I27" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J27" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K27" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L27" s="3" t="str">
+      <x:c r="H27" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I27" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J27" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K27" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L27" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M27" s="3" t="str">
@@ -1468,7 +1468,7 @@
       </x:c>
     </x:row>
     <x:row r="28" ht="28" customHeight="1">
-      <x:c r="A28" s="3" t="str">
+      <x:c r="A28" s="3" t="n">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B28" s="3" t="str">
@@ -1483,25 +1483,25 @@
       <x:c r="E28" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F28" s="3" t="str">
+      <x:c r="F28" s="3" t="n">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="G28" s="3" t="str">
+      <x:c r="G28" s="3" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="H28" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I28" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J28" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K28" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L28" s="3" t="str">
+      <x:c r="H28" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I28" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J28" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K28" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L28" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M28" s="3" t="str">
@@ -1512,7 +1512,7 @@
       </x:c>
     </x:row>
     <x:row r="29" ht="28" customHeight="1">
-      <x:c r="A29" s="3" t="str">
+      <x:c r="A29" s="3" t="n">
         <x:v>24</x:v>
       </x:c>
       <x:c r="B29" s="3" t="str">
@@ -1527,25 +1527,25 @@
       <x:c r="E29" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F29" s="3" t="str">
+      <x:c r="F29" s="3" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="G29" s="3" t="str">
+      <x:c r="G29" s="3" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="H29" s="3" t="str">
+      <x:c r="H29" s="3" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="I29" s="3" t="str">
+      <x:c r="I29" s="3" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="J29" s="3" t="str">
+      <x:c r="J29" s="3" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="K29" s="3" t="str">
+      <x:c r="K29" s="3" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="L29" s="3" t="str">
+      <x:c r="L29" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="M29" s="3" t="str">
@@ -1556,7 +1556,7 @@
       </x:c>
     </x:row>
     <x:row r="30" ht="28" customHeight="1">
-      <x:c r="A30" s="3" t="str">
+      <x:c r="A30" s="3" t="n">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B30" s="3" t="str">
@@ -1571,25 +1571,25 @@
       <x:c r="E30" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F30" s="3" t="str">
+      <x:c r="F30" s="3" t="n">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="G30" s="3" t="str">
+      <x:c r="G30" s="3" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H30" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I30" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J30" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K30" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L30" s="3" t="str">
+      <x:c r="H30" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I30" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J30" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K30" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L30" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="M30" s="3" t="str">
@@ -1600,7 +1600,7 @@
       </x:c>
     </x:row>
     <x:row r="31" ht="28" customHeight="1">
-      <x:c r="A31" s="3" t="str">
+      <x:c r="A31" s="3" t="n">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B31" s="3" t="str">
@@ -1615,25 +1615,25 @@
       <x:c r="E31" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F31" s="3" t="str">
+      <x:c r="F31" s="3" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G31" s="3" t="str">
+      <x:c r="G31" s="3" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H31" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I31" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J31" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K31" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L31" s="3" t="str">
+      <x:c r="H31" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I31" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J31" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K31" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L31" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="M31" s="3" t="str">
@@ -1644,7 +1644,7 @@
       </x:c>
     </x:row>
     <x:row r="32" ht="28" customHeight="1">
-      <x:c r="A32" s="3" t="str">
+      <x:c r="A32" s="3" t="n">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B32" s="3" t="str">
@@ -1659,25 +1659,25 @@
       <x:c r="E32" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F32" s="3" t="str">
+      <x:c r="F32" s="3" t="n">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G32" s="3" t="str">
+      <x:c r="G32" s="3" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H32" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I32" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J32" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K32" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L32" s="3" t="str">
+      <x:c r="H32" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I32" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J32" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K32" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L32" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="M32" s="3" t="str">
@@ -1688,7 +1688,7 @@
       </x:c>
     </x:row>
     <x:row r="33" ht="28" customHeight="1">
-      <x:c r="A33" s="3" t="str">
+      <x:c r="A33" s="3" t="n">
         <x:v>28</x:v>
       </x:c>
       <x:c r="B33" s="3" t="str">
@@ -1703,25 +1703,25 @@
       <x:c r="E33" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F33" s="3" t="str">
+      <x:c r="F33" s="3" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="G33" s="3" t="str">
+      <x:c r="G33" s="3" t="n">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="H33" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I33" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J33" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K33" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L33" s="3" t="str">
+      <x:c r="H33" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I33" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J33" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K33" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L33" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="M33" s="3" t="str">
@@ -1732,7 +1732,7 @@
       </x:c>
     </x:row>
     <x:row r="34" ht="28" customHeight="1">
-      <x:c r="A34" s="3" t="str">
+      <x:c r="A34" s="3" t="n">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B34" s="3" t="str">
@@ -1747,25 +1747,25 @@
       <x:c r="E34" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F34" s="3" t="str">
+      <x:c r="F34" s="3" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G34" s="3" t="str">
+      <x:c r="G34" s="3" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="H34" s="3" t="str">
+      <x:c r="H34" s="3" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="I34" s="3" t="str">
+      <x:c r="I34" s="3" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="J34" s="3" t="str">
+      <x:c r="J34" s="3" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="K34" s="3" t="str">
+      <x:c r="K34" s="3" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="L34" s="3" t="str">
+      <x:c r="L34" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M34" s="3" t="str">
@@ -1776,7 +1776,7 @@
       </x:c>
     </x:row>
     <x:row r="35" ht="28" customHeight="1">
-      <x:c r="A35" s="3" t="str">
+      <x:c r="A35" s="3" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="B35" s="3" t="str">
@@ -1791,25 +1791,25 @@
       <x:c r="E35" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F35" s="3" t="str">
+      <x:c r="F35" s="3" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G35" s="3" t="str">
+      <x:c r="G35" s="3" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H35" s="3" t="str">
+      <x:c r="H35" s="3" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="I35" s="3" t="str">
+      <x:c r="I35" s="3" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="J35" s="3" t="str">
+      <x:c r="J35" s="3" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="K35" s="3" t="str">
+      <x:c r="K35" s="3" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="L35" s="3" t="str">
+      <x:c r="L35" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M35" s="3" t="str">
@@ -1820,7 +1820,7 @@
       </x:c>
     </x:row>
     <x:row r="36" ht="28" customHeight="1">
-      <x:c r="A36" s="3" t="str">
+      <x:c r="A36" s="3" t="n">
         <x:v>31</x:v>
       </x:c>
       <x:c r="B36" s="3" t="str">
@@ -1835,25 +1835,25 @@
       <x:c r="E36" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F36" s="3" t="str">
+      <x:c r="F36" s="3" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G36" s="3" t="str">
+      <x:c r="G36" s="3" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H36" s="3" t="str">
+      <x:c r="H36" s="3" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I36" s="3" t="str">
+      <x:c r="I36" s="3" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="J36" s="3" t="str">
+      <x:c r="J36" s="3" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="K36" s="3" t="str">
+      <x:c r="K36" s="3" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="L36" s="3" t="str">
+      <x:c r="L36" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="M36" s="3" t="str">
@@ -1864,7 +1864,7 @@
       </x:c>
     </x:row>
     <x:row r="37" ht="28" customHeight="1">
-      <x:c r="A37" s="3" t="str">
+      <x:c r="A37" s="3" t="n">
         <x:v>32</x:v>
       </x:c>
       <x:c r="B37" s="3" t="str">
@@ -1879,25 +1879,25 @@
       <x:c r="E37" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F37" s="3" t="str">
+      <x:c r="F37" s="3" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G37" s="3" t="str">
+      <x:c r="G37" s="3" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H37" s="3" t="str">
+      <x:c r="H37" s="3" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="I37" s="3" t="str">
+      <x:c r="I37" s="3" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="J37" s="3" t="str">
+      <x:c r="J37" s="3" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="K37" s="3" t="str">
+      <x:c r="K37" s="3" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="L37" s="3" t="str">
+      <x:c r="L37" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="M37" s="3" t="str">
@@ -1908,7 +1908,7 @@
       </x:c>
     </x:row>
     <x:row r="38" ht="28" customHeight="1">
-      <x:c r="A38" s="3" t="str">
+      <x:c r="A38" s="3" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B38" s="3" t="str">
@@ -1923,25 +1923,25 @@
       <x:c r="E38" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F38" s="3" t="str">
+      <x:c r="F38" s="3" t="n">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="G38" s="3" t="str">
+      <x:c r="G38" s="3" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H38" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I38" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J38" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K38" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L38" s="3" t="str">
+      <x:c r="H38" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I38" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J38" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K38" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L38" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="M38" s="3" t="str">
@@ -1952,7 +1952,7 @@
       </x:c>
     </x:row>
     <x:row r="39" ht="28" customHeight="1">
-      <x:c r="A39" s="3" t="str">
+      <x:c r="A39" s="3" t="n">
         <x:v>34</x:v>
       </x:c>
       <x:c r="B39" s="3" t="str">
@@ -1967,25 +1967,25 @@
       <x:c r="E39" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F39" s="3" t="str">
+      <x:c r="F39" s="3" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G39" s="3" t="str">
+      <x:c r="G39" s="3" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H39" s="3" t="str">
+      <x:c r="H39" s="3" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I39" s="3" t="str">
+      <x:c r="I39" s="3" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J39" s="3" t="str">
+      <x:c r="J39" s="3" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K39" s="3" t="str">
+      <x:c r="K39" s="3" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="L39" s="3" t="str">
+      <x:c r="L39" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M39" s="3" t="str">
@@ -1996,7 +1996,7 @@
       </x:c>
     </x:row>
     <x:row r="40" ht="28" customHeight="1">
-      <x:c r="A40" s="3" t="str">
+      <x:c r="A40" s="3" t="n">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B40" s="3" t="str">
@@ -2011,25 +2011,25 @@
       <x:c r="E40" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F40" s="3" t="str">
+      <x:c r="F40" s="3" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G40" s="3" t="str">
+      <x:c r="G40" s="3" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="H40" s="3" t="str">
+      <x:c r="H40" s="3" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="I40" s="3" t="str">
+      <x:c r="I40" s="3" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="J40" s="3" t="str">
+      <x:c r="J40" s="3" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="K40" s="3" t="str">
+      <x:c r="K40" s="3" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="L40" s="3" t="str">
+      <x:c r="L40" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="M40" s="3" t="str">
@@ -2040,7 +2040,7 @@
       </x:c>
     </x:row>
     <x:row r="41" ht="28" customHeight="1">
-      <x:c r="A41" s="3" t="str">
+      <x:c r="A41" s="3" t="n">
         <x:v>36</x:v>
       </x:c>
       <x:c r="B41" s="3" t="str">
@@ -2055,25 +2055,25 @@
       <x:c r="E41" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F41" s="3" t="str">
+      <x:c r="F41" s="3" t="n">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="G41" s="3" t="str">
+      <x:c r="G41" s="3" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H41" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I41" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J41" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K41" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L41" s="3" t="str">
+      <x:c r="H41" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I41" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J41" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K41" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L41" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="M41" s="3" t="str">
@@ -2084,7 +2084,7 @@
       </x:c>
     </x:row>
     <x:row r="42" ht="28" customHeight="1">
-      <x:c r="A42" s="3" t="str">
+      <x:c r="A42" s="3" t="n">
         <x:v>37</x:v>
       </x:c>
       <x:c r="B42" s="3" t="str">
@@ -2099,25 +2099,25 @@
       <x:c r="E42" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F42" s="3" t="str">
+      <x:c r="F42" s="3" t="n">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="G42" s="3" t="str">
+      <x:c r="G42" s="3" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H42" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I42" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J42" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K42" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L42" s="3" t="str">
+      <x:c r="H42" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I42" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J42" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K42" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L42" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="M42" s="3" t="str">
@@ -2128,7 +2128,7 @@
       </x:c>
     </x:row>
     <x:row r="43" ht="28" customHeight="1">
-      <x:c r="A43" s="3" t="str">
+      <x:c r="A43" s="3" t="n">
         <x:v>38</x:v>
       </x:c>
       <x:c r="B43" s="3" t="str">
@@ -2143,25 +2143,25 @@
       <x:c r="E43" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F43" s="3" t="str">
+      <x:c r="F43" s="3" t="n">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G43" s="3" t="str">
+      <x:c r="G43" s="3" t="n">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="H43" s="3" t="str">
+      <x:c r="H43" s="3" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I43" s="3" t="str">
+      <x:c r="I43" s="3" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="J43" s="3" t="str">
+      <x:c r="J43" s="3" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="K43" s="3" t="str">
+      <x:c r="K43" s="3" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="L43" s="3" t="str">
+      <x:c r="L43" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M43" s="3" t="str">
@@ -2172,7 +2172,7 @@
       </x:c>
     </x:row>
     <x:row r="44" ht="28" customHeight="1">
-      <x:c r="A44" s="3" t="str">
+      <x:c r="A44" s="3" t="n">
         <x:v>39</x:v>
       </x:c>
       <x:c r="B44" s="3" t="str">
@@ -2187,25 +2187,25 @@
       <x:c r="E44" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F44" s="3" t="str">
+      <x:c r="F44" s="3" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G44" s="3" t="str">
+      <x:c r="G44" s="3" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="H44" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I44" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J44" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K44" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L44" s="3" t="str">
+      <x:c r="H44" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I44" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J44" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K44" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L44" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="M44" s="3" t="str">
@@ -2216,7 +2216,7 @@
       </x:c>
     </x:row>
     <x:row r="45" ht="28" customHeight="1">
-      <x:c r="A45" s="3" t="str">
+      <x:c r="A45" s="3" t="n">
         <x:v>40</x:v>
       </x:c>
       <x:c r="B45" s="3" t="str">
@@ -2231,25 +2231,25 @@
       <x:c r="E45" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F45" s="3" t="str">
+      <x:c r="F45" s="3" t="n">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G45" s="3" t="str">
+      <x:c r="G45" s="3" t="n">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="H45" s="3" t="str">
+      <x:c r="H45" s="3" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="I45" s="3" t="str">
+      <x:c r="I45" s="3" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="J45" s="3" t="str">
+      <x:c r="J45" s="3" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="K45" s="3" t="str">
+      <x:c r="K45" s="3" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="L45" s="3" t="str">
+      <x:c r="L45" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M45" s="3" t="str">
@@ -2260,7 +2260,7 @@
       </x:c>
     </x:row>
     <x:row r="46" ht="28" customHeight="1">
-      <x:c r="A46" s="3" t="str">
+      <x:c r="A46" s="3" t="n">
         <x:v>41</x:v>
       </x:c>
       <x:c r="B46" s="3" t="str">
@@ -2275,25 +2275,25 @@
       <x:c r="E46" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F46" s="3" t="str">
+      <x:c r="F46" s="3" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G46" s="3" t="str">
+      <x:c r="G46" s="3" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="H46" s="3" t="str">
+      <x:c r="H46" s="3" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="I46" s="3" t="str">
+      <x:c r="I46" s="3" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J46" s="3" t="str">
+      <x:c r="J46" s="3" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="K46" s="3" t="str">
+      <x:c r="K46" s="3" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L46" s="3" t="str">
+      <x:c r="L46" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M46" s="3" t="str">
@@ -2304,7 +2304,7 @@
       </x:c>
     </x:row>
     <x:row r="47" ht="28" customHeight="1">
-      <x:c r="A47" s="3" t="str">
+      <x:c r="A47" s="3" t="n">
         <x:v>42</x:v>
       </x:c>
       <x:c r="B47" s="3" t="str">
@@ -2319,25 +2319,25 @@
       <x:c r="E47" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F47" s="3" t="str">
+      <x:c r="F47" s="3" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G47" s="3" t="str">
+      <x:c r="G47" s="3" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="H47" s="3" t="str">
+      <x:c r="H47" s="3" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="I47" s="3" t="str">
+      <x:c r="I47" s="3" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="J47" s="3" t="str">
+      <x:c r="J47" s="3" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="K47" s="3" t="str">
+      <x:c r="K47" s="3" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="L47" s="3" t="str">
+      <x:c r="L47" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M47" s="3" t="str">
@@ -2348,7 +2348,7 @@
       </x:c>
     </x:row>
     <x:row r="48" ht="28" customHeight="1">
-      <x:c r="A48" s="3" t="str">
+      <x:c r="A48" s="3" t="n">
         <x:v>43</x:v>
       </x:c>
       <x:c r="B48" s="3" t="str">
@@ -2363,25 +2363,25 @@
       <x:c r="E48" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F48" s="3" t="str">
+      <x:c r="F48" s="3" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="G48" s="3" t="str">
+      <x:c r="G48" s="3" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H48" s="3" t="str">
+      <x:c r="H48" s="3" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="I48" s="3" t="str">
+      <x:c r="I48" s="3" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="J48" s="3" t="str">
+      <x:c r="J48" s="3" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K48" s="3" t="str">
+      <x:c r="K48" s="3" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L48" s="3" t="str">
+      <x:c r="L48" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M48" s="3" t="str">
@@ -2392,7 +2392,7 @@
       </x:c>
     </x:row>
     <x:row r="49" ht="28" customHeight="1">
-      <x:c r="A49" s="3" t="str">
+      <x:c r="A49" s="3" t="n">
         <x:v>44</x:v>
       </x:c>
       <x:c r="B49" s="3" t="str">
@@ -2407,25 +2407,25 @@
       <x:c r="E49" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F49" s="3" t="str">
+      <x:c r="F49" s="3" t="n">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G49" s="3" t="str">
+      <x:c r="G49" s="3" t="n">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H49" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I49" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J49" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K49" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L49" s="3" t="str">
+      <x:c r="H49" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I49" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J49" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K49" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L49" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="M49" s="3" t="str">
@@ -2436,7 +2436,7 @@
       </x:c>
     </x:row>
     <x:row r="50" ht="28" customHeight="1">
-      <x:c r="A50" s="3" t="str">
+      <x:c r="A50" s="3" t="n">
         <x:v>45</x:v>
       </x:c>
       <x:c r="B50" s="3" t="str">
@@ -2451,25 +2451,25 @@
       <x:c r="E50" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F50" s="3" t="str">
+      <x:c r="F50" s="3" t="n">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G50" s="3" t="str">
+      <x:c r="G50" s="3" t="n">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H50" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I50" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J50" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K50" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L50" s="3" t="str">
+      <x:c r="H50" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I50" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J50" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K50" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L50" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="M50" s="3" t="str">
@@ -2480,7 +2480,7 @@
       </x:c>
     </x:row>
     <x:row r="51" ht="28" customHeight="1">
-      <x:c r="A51" s="3" t="str">
+      <x:c r="A51" s="3" t="n">
         <x:v>46</x:v>
       </x:c>
       <x:c r="B51" s="3" t="str">
@@ -2495,25 +2495,25 @@
       <x:c r="E51" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F51" s="3" t="str">
+      <x:c r="F51" s="3" t="n">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G51" s="3" t="str">
+      <x:c r="G51" s="3" t="n">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H51" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I51" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J51" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K51" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L51" s="3" t="str">
+      <x:c r="H51" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I51" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J51" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K51" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L51" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="M51" s="3" t="str">
@@ -2524,7 +2524,7 @@
       </x:c>
     </x:row>
     <x:row r="52" ht="28" customHeight="1">
-      <x:c r="A52" s="3" t="str">
+      <x:c r="A52" s="3" t="n">
         <x:v>47</x:v>
       </x:c>
       <x:c r="B52" s="3" t="str">
@@ -2539,25 +2539,25 @@
       <x:c r="E52" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F52" s="3" t="str">
+      <x:c r="F52" s="3" t="n">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G52" s="3" t="str">
+      <x:c r="G52" s="3" t="n">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H52" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I52" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J52" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K52" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L52" s="3" t="str">
+      <x:c r="H52" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I52" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J52" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K52" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L52" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="M52" s="3" t="str">
@@ -2568,7 +2568,7 @@
       </x:c>
     </x:row>
     <x:row r="53" ht="28" customHeight="1">
-      <x:c r="A53" s="3" t="str">
+      <x:c r="A53" s="3" t="n">
         <x:v>48</x:v>
       </x:c>
       <x:c r="B53" s="3" t="str">
@@ -2583,25 +2583,25 @@
       <x:c r="E53" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F53" s="3" t="str">
+      <x:c r="F53" s="3" t="n">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G53" s="3" t="str">
+      <x:c r="G53" s="3" t="n">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H53" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I53" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J53" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K53" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L53" s="3" t="str">
+      <x:c r="H53" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I53" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J53" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K53" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L53" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="M53" s="3" t="str">
@@ -2612,7 +2612,7 @@
       </x:c>
     </x:row>
     <x:row r="54" ht="28" customHeight="1">
-      <x:c r="A54" s="3" t="str">
+      <x:c r="A54" s="3" t="n">
         <x:v>49</x:v>
       </x:c>
       <x:c r="B54" s="3" t="str">
@@ -2627,25 +2627,25 @@
       <x:c r="E54" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F54" s="3" t="str">
+      <x:c r="F54" s="3" t="n">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G54" s="3" t="str">
+      <x:c r="G54" s="3" t="n">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H54" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I54" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J54" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K54" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L54" s="3" t="str">
+      <x:c r="H54" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I54" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J54" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K54" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L54" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="M54" s="3" t="str">
@@ -2656,7 +2656,7 @@
       </x:c>
     </x:row>
     <x:row r="55" ht="28" customHeight="1">
-      <x:c r="A55" s="3" t="str">
+      <x:c r="A55" s="3" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="B55" s="3" t="str">
@@ -2671,25 +2671,25 @@
       <x:c r="E55" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F55" s="3" t="str">
+      <x:c r="F55" s="3" t="n">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G55" s="3" t="str">
+      <x:c r="G55" s="3" t="n">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H55" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I55" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J55" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K55" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L55" s="3" t="str">
+      <x:c r="H55" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I55" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J55" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K55" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L55" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="M55" s="3" t="str">
@@ -2700,7 +2700,7 @@
       </x:c>
     </x:row>
     <x:row r="56" ht="28" customHeight="1">
-      <x:c r="A56" s="3" t="str">
+      <x:c r="A56" s="3" t="n">
         <x:v>51</x:v>
       </x:c>
       <x:c r="B56" s="3" t="str">
@@ -2715,25 +2715,25 @@
       <x:c r="E56" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F56" s="3" t="str">
+      <x:c r="F56" s="3" t="n">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G56" s="3" t="str">
+      <x:c r="G56" s="3" t="n">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H56" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I56" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J56" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K56" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L56" s="3" t="str">
+      <x:c r="H56" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I56" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J56" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K56" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L56" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="M56" s="3" t="str">
@@ -2744,7 +2744,7 @@
       </x:c>
     </x:row>
     <x:row r="57" ht="28" customHeight="1">
-      <x:c r="A57" s="3" t="str">
+      <x:c r="A57" s="3" t="n">
         <x:v>52</x:v>
       </x:c>
       <x:c r="B57" s="3" t="str">
@@ -2759,25 +2759,25 @@
       <x:c r="E57" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F57" s="3" t="str">
+      <x:c r="F57" s="3" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G57" s="3" t="str">
+      <x:c r="G57" s="3" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="H57" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I57" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J57" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K57" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L57" s="3" t="str">
+      <x:c r="H57" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I57" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J57" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K57" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L57" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="M57" s="3" t="str">
@@ -2788,7 +2788,7 @@
       </x:c>
     </x:row>
     <x:row r="58" ht="28" customHeight="1">
-      <x:c r="A58" s="3" t="str">
+      <x:c r="A58" s="3" t="n">
         <x:v>53</x:v>
       </x:c>
       <x:c r="B58" s="3" t="str">
@@ -2803,25 +2803,25 @@
       <x:c r="E58" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F58" s="3" t="str">
+      <x:c r="F58" s="3" t="n">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G58" s="3" t="str">
+      <x:c r="G58" s="3" t="n">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="H58" s="3" t="str">
+      <x:c r="H58" s="3" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="I58" s="3" t="str">
+      <x:c r="I58" s="3" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="J58" s="3" t="str">
+      <x:c r="J58" s="3" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="K58" s="3" t="str">
+      <x:c r="K58" s="3" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="L58" s="3" t="str">
+      <x:c r="L58" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M58" s="3" t="str">
@@ -2832,7 +2832,7 @@
       </x:c>
     </x:row>
     <x:row r="59" ht="28" customHeight="1">
-      <x:c r="A59" s="3" t="str">
+      <x:c r="A59" s="3" t="n">
         <x:v>54</x:v>
       </x:c>
       <x:c r="B59" s="3" t="str">
@@ -2847,25 +2847,25 @@
       <x:c r="E59" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F59" s="3" t="str">
+      <x:c r="F59" s="3" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G59" s="3" t="str">
+      <x:c r="G59" s="3" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="H59" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I59" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J59" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K59" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L59" s="3" t="str">
+      <x:c r="H59" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I59" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J59" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K59" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L59" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="M59" s="3" t="str">
@@ -2876,7 +2876,7 @@
       </x:c>
     </x:row>
     <x:row r="60" ht="28" customHeight="1">
-      <x:c r="A60" s="3" t="str">
+      <x:c r="A60" s="3" t="n">
         <x:v>55</x:v>
       </x:c>
       <x:c r="B60" s="3" t="str">
@@ -2891,25 +2891,25 @@
       <x:c r="E60" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F60" s="3" t="str">
+      <x:c r="F60" s="3" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="G60" s="3" t="str">
+      <x:c r="G60" s="3" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="H60" s="3" t="str">
+      <x:c r="H60" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I60" s="3" t="str">
+      <x:c r="I60" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J60" s="3" t="str">
+      <x:c r="J60" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K60" s="3" t="str">
+      <x:c r="K60" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="L60" s="3" t="str">
+      <x:c r="L60" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M60" s="3" t="str">
@@ -2920,7 +2920,7 @@
       </x:c>
     </x:row>
     <x:row r="61" ht="28" customHeight="1">
-      <x:c r="A61" s="3" t="str">
+      <x:c r="A61" s="3" t="n">
         <x:v>56</x:v>
       </x:c>
       <x:c r="B61" s="3" t="str">
@@ -2935,25 +2935,25 @@
       <x:c r="E61" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F61" s="3" t="str">
+      <x:c r="F61" s="3" t="n">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G61" s="3" t="str">
+      <x:c r="G61" s="3" t="n">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="H61" s="3" t="str">
+      <x:c r="H61" s="3" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="I61" s="3" t="str">
+      <x:c r="I61" s="3" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="J61" s="3" t="str">
+      <x:c r="J61" s="3" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="K61" s="3" t="str">
+      <x:c r="K61" s="3" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L61" s="3" t="str">
+      <x:c r="L61" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M61" s="3" t="str">
@@ -2964,7 +2964,7 @@
       </x:c>
     </x:row>
     <x:row r="62" ht="28" customHeight="1">
-      <x:c r="A62" s="3" t="str">
+      <x:c r="A62" s="3" t="n">
         <x:v>57</x:v>
       </x:c>
       <x:c r="B62" s="3" t="str">
@@ -2979,25 +2979,25 @@
       <x:c r="E62" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F62" s="3" t="str">
+      <x:c r="F62" s="3" t="n">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G62" s="3" t="str">
+      <x:c r="G62" s="3" t="n">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="H62" s="3" t="str">
+      <x:c r="H62" s="3" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="I62" s="3" t="str">
+      <x:c r="I62" s="3" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="J62" s="3" t="str">
+      <x:c r="J62" s="3" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="K62" s="3" t="str">
+      <x:c r="K62" s="3" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="L62" s="3" t="str">
+      <x:c r="L62" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="M62" s="3" t="str">
@@ -3008,7 +3008,7 @@
       </x:c>
     </x:row>
     <x:row r="63" ht="28" customHeight="1">
-      <x:c r="A63" s="3" t="str">
+      <x:c r="A63" s="3" t="n">
         <x:v>58</x:v>
       </x:c>
       <x:c r="B63" s="3" t="str">
@@ -3023,25 +3023,25 @@
       <x:c r="E63" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F63" s="3" t="str">
+      <x:c r="F63" s="3" t="n">
         <x:v>544</x:v>
       </x:c>
-      <x:c r="G63" s="3" t="str">
+      <x:c r="G63" s="3" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H63" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I63" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J63" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K63" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L63" s="3" t="str">
+      <x:c r="H63" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I63" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J63" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K63" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L63" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="M63" s="3" t="str">
@@ -3052,7 +3052,7 @@
       </x:c>
     </x:row>
     <x:row r="64" ht="28" customHeight="1">
-      <x:c r="A64" s="3" t="str">
+      <x:c r="A64" s="3" t="n">
         <x:v>59</x:v>
       </x:c>
       <x:c r="B64" s="3" t="str">
@@ -3067,25 +3067,25 @@
       <x:c r="E64" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F64" s="3" t="str">
+      <x:c r="F64" s="3" t="n">
         <x:v>448</x:v>
       </x:c>
-      <x:c r="G64" s="3" t="str">
+      <x:c r="G64" s="3" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H64" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I64" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J64" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K64" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L64" s="3" t="str">
+      <x:c r="H64" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I64" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J64" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K64" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L64" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="M64" s="3" t="str">
@@ -3096,7 +3096,7 @@
       </x:c>
     </x:row>
     <x:row r="65" ht="28" customHeight="1">
-      <x:c r="A65" s="3" t="str">
+      <x:c r="A65" s="3" t="n">
         <x:v>60</x:v>
       </x:c>
       <x:c r="B65" s="3" t="str">
@@ -3111,25 +3111,25 @@
       <x:c r="E65" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F65" s="3" t="str">
+      <x:c r="F65" s="3" t="n">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G65" s="3" t="str">
+      <x:c r="G65" s="3" t="n">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="H65" s="3" t="str">
+      <x:c r="H65" s="3" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="I65" s="3" t="str">
+      <x:c r="I65" s="3" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="J65" s="3" t="str">
+      <x:c r="J65" s="3" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="K65" s="3" t="str">
+      <x:c r="K65" s="3" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L65" s="3" t="str">
+      <x:c r="L65" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="M65" s="3" t="str">
@@ -3140,7 +3140,7 @@
       </x:c>
     </x:row>
     <x:row r="66" ht="28" customHeight="1">
-      <x:c r="A66" s="3" t="str">
+      <x:c r="A66" s="3" t="n">
         <x:v>61</x:v>
       </x:c>
       <x:c r="B66" s="3" t="str">
@@ -3155,25 +3155,25 @@
       <x:c r="E66" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F66" s="3" t="str">
+      <x:c r="F66" s="3" t="n">
         <x:v>476</x:v>
       </x:c>
-      <x:c r="G66" s="3" t="str">
+      <x:c r="G66" s="3" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H66" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I66" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J66" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K66" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L66" s="3" t="str">
+      <x:c r="H66" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I66" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J66" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K66" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L66" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="M66" s="3" t="str">
@@ -3184,7 +3184,7 @@
       </x:c>
     </x:row>
     <x:row r="67" ht="28" customHeight="1">
-      <x:c r="A67" s="3" t="str">
+      <x:c r="A67" s="3" t="n">
         <x:v>62</x:v>
       </x:c>
       <x:c r="B67" s="3" t="str">
@@ -3199,25 +3199,25 @@
       <x:c r="E67" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F67" s="3" t="str">
+      <x:c r="F67" s="3" t="n">
         <x:v>448</x:v>
       </x:c>
-      <x:c r="G67" s="3" t="str">
+      <x:c r="G67" s="3" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H67" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I67" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J67" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K67" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L67" s="3" t="str">
+      <x:c r="H67" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I67" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J67" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K67" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L67" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="M67" s="3" t="str">
@@ -3228,7 +3228,7 @@
       </x:c>
     </x:row>
     <x:row r="68" ht="28" customHeight="1">
-      <x:c r="A68" s="3" t="str">
+      <x:c r="A68" s="3" t="n">
         <x:v>63</x:v>
       </x:c>
       <x:c r="B68" s="3" t="str">
@@ -3243,25 +3243,25 @@
       <x:c r="E68" s="3" t="str">
         <x:v>sliced</x:v>
       </x:c>
-      <x:c r="F68" s="3" t="str">
+      <x:c r="F68" s="3" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G68" s="3" t="str">
+      <x:c r="G68" s="3" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="H68" s="3" t="str">
+      <x:c r="H68" s="3" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="I68" s="3" t="str">
+      <x:c r="I68" s="3" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="J68" s="3" t="str">
+      <x:c r="J68" s="3" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K68" s="3" t="str">
+      <x:c r="K68" s="3" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="L68" s="3" t="str">
+      <x:c r="L68" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M68" s="3" t="str">
@@ -3272,7 +3272,7 @@
       </x:c>
     </x:row>
     <x:row r="69" ht="28" customHeight="1">
-      <x:c r="A69" s="3" t="str">
+      <x:c r="A69" s="3" t="n">
         <x:v>64</x:v>
       </x:c>
       <x:c r="B69" s="3" t="str">
@@ -3287,25 +3287,25 @@
       <x:c r="E69" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F69" s="3" t="str">
+      <x:c r="F69" s="3" t="n">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G69" s="3" t="str">
+      <x:c r="G69" s="3" t="n">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H69" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I69" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J69" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K69" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L69" s="3" t="str">
+      <x:c r="H69" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I69" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J69" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K69" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L69" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M69" s="3" t="str">
@@ -3316,7 +3316,7 @@
       </x:c>
     </x:row>
     <x:row r="70" ht="28" customHeight="1">
-      <x:c r="A70" s="3" t="str">
+      <x:c r="A70" s="3" t="n">
         <x:v>65</x:v>
       </x:c>
       <x:c r="B70" s="3" t="str">
@@ -3331,25 +3331,25 @@
       <x:c r="E70" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F70" s="3" t="str">
+      <x:c r="F70" s="3" t="n">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G70" s="3" t="str">
+      <x:c r="G70" s="3" t="n">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H70" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I70" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J70" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K70" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L70" s="3" t="str">
+      <x:c r="H70" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I70" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J70" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K70" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L70" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M70" s="3" t="str">
@@ -3360,7 +3360,7 @@
       </x:c>
     </x:row>
     <x:row r="71" ht="28" customHeight="1">
-      <x:c r="A71" s="3" t="str">
+      <x:c r="A71" s="3" t="n">
         <x:v>66</x:v>
       </x:c>
       <x:c r="B71" s="3" t="str">
@@ -3375,25 +3375,25 @@
       <x:c r="E71" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F71" s="3" t="str">
+      <x:c r="F71" s="3" t="n">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G71" s="3" t="str">
+      <x:c r="G71" s="3" t="n">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H71" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I71" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J71" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K71" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L71" s="3" t="str">
+      <x:c r="H71" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I71" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J71" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K71" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L71" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M71" s="3" t="str">
@@ -3404,7 +3404,7 @@
       </x:c>
     </x:row>
     <x:row r="72" ht="28" customHeight="1">
-      <x:c r="A72" s="3" t="str">
+      <x:c r="A72" s="3" t="n">
         <x:v>67</x:v>
       </x:c>
       <x:c r="B72" s="3" t="str">
@@ -3419,25 +3419,25 @@
       <x:c r="E72" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F72" s="3" t="str">
+      <x:c r="F72" s="3" t="n">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G72" s="3" t="str">
+      <x:c r="G72" s="3" t="n">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H72" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I72" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J72" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K72" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L72" s="3" t="str">
+      <x:c r="H72" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I72" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J72" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K72" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L72" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M72" s="3" t="str">
@@ -3448,7 +3448,7 @@
       </x:c>
     </x:row>
     <x:row r="73" ht="28" customHeight="1">
-      <x:c r="A73" s="3" t="str">
+      <x:c r="A73" s="3" t="n">
         <x:v>68</x:v>
       </x:c>
       <x:c r="B73" s="3" t="str">
@@ -3463,25 +3463,25 @@
       <x:c r="E73" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F73" s="3" t="str">
+      <x:c r="F73" s="3" t="n">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G73" s="3" t="str">
+      <x:c r="G73" s="3" t="n">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H73" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I73" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J73" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K73" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L73" s="3" t="str">
+      <x:c r="H73" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I73" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J73" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K73" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L73" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M73" s="3" t="str">
@@ -3492,7 +3492,7 @@
       </x:c>
     </x:row>
     <x:row r="74" ht="28" customHeight="1">
-      <x:c r="A74" s="3" t="str">
+      <x:c r="A74" s="3" t="n">
         <x:v>69</x:v>
       </x:c>
       <x:c r="B74" s="3" t="str">
@@ -3507,25 +3507,25 @@
       <x:c r="E74" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F74" s="3" t="str">
+      <x:c r="F74" s="3" t="n">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G74" s="3" t="str">
+      <x:c r="G74" s="3" t="n">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H74" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I74" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J74" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K74" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L74" s="3" t="str">
+      <x:c r="H74" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I74" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J74" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K74" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L74" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M74" s="3" t="str">
@@ -3536,7 +3536,7 @@
       </x:c>
     </x:row>
     <x:row r="75" ht="28" customHeight="1">
-      <x:c r="A75" s="3" t="str">
+      <x:c r="A75" s="3" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="B75" s="3" t="str">
@@ -3551,25 +3551,25 @@
       <x:c r="E75" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F75" s="3" t="str">
+      <x:c r="F75" s="3" t="n">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G75" s="3" t="str">
+      <x:c r="G75" s="3" t="n">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H75" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I75" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J75" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K75" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L75" s="3" t="str">
+      <x:c r="H75" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I75" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J75" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K75" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L75" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M75" s="3" t="str">
@@ -3580,7 +3580,7 @@
       </x:c>
     </x:row>
     <x:row r="76" ht="28" customHeight="1">
-      <x:c r="A76" s="3" t="str">
+      <x:c r="A76" s="3" t="n">
         <x:v>71</x:v>
       </x:c>
       <x:c r="B76" s="3" t="str">
@@ -3595,25 +3595,25 @@
       <x:c r="E76" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F76" s="3" t="str">
+      <x:c r="F76" s="3" t="n">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G76" s="3" t="str">
+      <x:c r="G76" s="3" t="n">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H76" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I76" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J76" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K76" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L76" s="3" t="str">
+      <x:c r="H76" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I76" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J76" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K76" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L76" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M76" s="3" t="str">
@@ -3624,7 +3624,7 @@
       </x:c>
     </x:row>
     <x:row r="77" ht="28" customHeight="1">
-      <x:c r="A77" s="3" t="str">
+      <x:c r="A77" s="3" t="n">
         <x:v>72</x:v>
       </x:c>
       <x:c r="B77" s="3" t="str">
@@ -3639,25 +3639,25 @@
       <x:c r="E77" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F77" s="3" t="str">
+      <x:c r="F77" s="3" t="n">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G77" s="3" t="str">
+      <x:c r="G77" s="3" t="n">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H77" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I77" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J77" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K77" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L77" s="3" t="str">
+      <x:c r="H77" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I77" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J77" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K77" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L77" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M77" s="3" t="str">
@@ -3668,7 +3668,7 @@
       </x:c>
     </x:row>
     <x:row r="78" ht="28" customHeight="1">
-      <x:c r="A78" s="3" t="str">
+      <x:c r="A78" s="3" t="n">
         <x:v>73</x:v>
       </x:c>
       <x:c r="B78" s="3" t="str">
@@ -3683,25 +3683,25 @@
       <x:c r="E78" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F78" s="3" t="str">
+      <x:c r="F78" s="3" t="n">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G78" s="3" t="str">
+      <x:c r="G78" s="3" t="n">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H78" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I78" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J78" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K78" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L78" s="3" t="str">
+      <x:c r="H78" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I78" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J78" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K78" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L78" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M78" s="3" t="str">
@@ -3712,7 +3712,7 @@
       </x:c>
     </x:row>
     <x:row r="79" ht="28" customHeight="1">
-      <x:c r="A79" s="3" t="str">
+      <x:c r="A79" s="3" t="n">
         <x:v>74</x:v>
       </x:c>
       <x:c r="B79" s="3" t="str">
@@ -3727,25 +3727,25 @@
       <x:c r="E79" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F79" s="3" t="str">
+      <x:c r="F79" s="3" t="n">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G79" s="3" t="str">
+      <x:c r="G79" s="3" t="n">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H79" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I79" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J79" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K79" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L79" s="3" t="str">
+      <x:c r="H79" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I79" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J79" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K79" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L79" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M79" s="3" t="str">
@@ -3756,7 +3756,7 @@
       </x:c>
     </x:row>
     <x:row r="80" ht="28" customHeight="1">
-      <x:c r="A80" s="3" t="str">
+      <x:c r="A80" s="3" t="n">
         <x:v>75</x:v>
       </x:c>
       <x:c r="B80" s="3" t="str">
@@ -3771,25 +3771,25 @@
       <x:c r="E80" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F80" s="3" t="str">
+      <x:c r="F80" s="3" t="n">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G80" s="3" t="str">
+      <x:c r="G80" s="3" t="n">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H80" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I80" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J80" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K80" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L80" s="3" t="str">
+      <x:c r="H80" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I80" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J80" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K80" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L80" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M80" s="3" t="str">
@@ -3800,7 +3800,7 @@
       </x:c>
     </x:row>
     <x:row r="81" ht="28" customHeight="1">
-      <x:c r="A81" s="3" t="str">
+      <x:c r="A81" s="3" t="n">
         <x:v>76</x:v>
       </x:c>
       <x:c r="B81" s="3" t="str">
@@ -3815,25 +3815,25 @@
       <x:c r="E81" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F81" s="3" t="str">
+      <x:c r="F81" s="3" t="n">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G81" s="3" t="str">
+      <x:c r="G81" s="3" t="n">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H81" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I81" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J81" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K81" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L81" s="3" t="str">
+      <x:c r="H81" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I81" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J81" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K81" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L81" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M81" s="3" t="str">
@@ -3844,7 +3844,7 @@
       </x:c>
     </x:row>
     <x:row r="82" ht="28" customHeight="1">
-      <x:c r="A82" s="3" t="str">
+      <x:c r="A82" s="3" t="n">
         <x:v>77</x:v>
       </x:c>
       <x:c r="B82" s="3" t="str">
@@ -3859,25 +3859,25 @@
       <x:c r="E82" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F82" s="3" t="str">
+      <x:c r="F82" s="3" t="n">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G82" s="3" t="str">
+      <x:c r="G82" s="3" t="n">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H82" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I82" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J82" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K82" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L82" s="3" t="str">
+      <x:c r="H82" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I82" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J82" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K82" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L82" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M82" s="3" t="str">
@@ -3888,7 +3888,7 @@
       </x:c>
     </x:row>
     <x:row r="83" ht="28" customHeight="1">
-      <x:c r="A83" s="3" t="str">
+      <x:c r="A83" s="3" t="n">
         <x:v>78</x:v>
       </x:c>
       <x:c r="B83" s="3" t="str">
@@ -3903,25 +3903,25 @@
       <x:c r="E83" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F83" s="3" t="str">
+      <x:c r="F83" s="3" t="n">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G83" s="3" t="str">
+      <x:c r="G83" s="3" t="n">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H83" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I83" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J83" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K83" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L83" s="3" t="str">
+      <x:c r="H83" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I83" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J83" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K83" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L83" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M83" s="3" t="str">
@@ -3932,7 +3932,7 @@
       </x:c>
     </x:row>
     <x:row r="84" ht="28" customHeight="1">
-      <x:c r="A84" s="3" t="str">
+      <x:c r="A84" s="3" t="n">
         <x:v>79</x:v>
       </x:c>
       <x:c r="B84" s="3" t="str">
@@ -3947,25 +3947,25 @@
       <x:c r="E84" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F84" s="3" t="str">
+      <x:c r="F84" s="3" t="n">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G84" s="3" t="str">
+      <x:c r="G84" s="3" t="n">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H84" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I84" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J84" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K84" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L84" s="3" t="str">
+      <x:c r="H84" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I84" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J84" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K84" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L84" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M84" s="3" t="str">
@@ -3976,7 +3976,7 @@
       </x:c>
     </x:row>
     <x:row r="85" ht="28" customHeight="1">
-      <x:c r="A85" s="3" t="str">
+      <x:c r="A85" s="3" t="n">
         <x:v>80</x:v>
       </x:c>
       <x:c r="B85" s="3" t="str">
@@ -3991,25 +3991,25 @@
       <x:c r="E85" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F85" s="3" t="str">
+      <x:c r="F85" s="3" t="n">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G85" s="3" t="str">
+      <x:c r="G85" s="3" t="n">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H85" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I85" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J85" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K85" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L85" s="3" t="str">
+      <x:c r="H85" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I85" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J85" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K85" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L85" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M85" s="3" t="str">
@@ -4020,7 +4020,7 @@
       </x:c>
     </x:row>
     <x:row r="86" ht="28" customHeight="1">
-      <x:c r="A86" s="3" t="str">
+      <x:c r="A86" s="3" t="n">
         <x:v>81</x:v>
       </x:c>
       <x:c r="B86" s="3" t="str">
@@ -4035,25 +4035,25 @@
       <x:c r="E86" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F86" s="3" t="str">
+      <x:c r="F86" s="3" t="n">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G86" s="3" t="str">
+      <x:c r="G86" s="3" t="n">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H86" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I86" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J86" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K86" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L86" s="3" t="str">
+      <x:c r="H86" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I86" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J86" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K86" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L86" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M86" s="3" t="str">
@@ -4064,7 +4064,7 @@
       </x:c>
     </x:row>
     <x:row r="87" ht="28" customHeight="1">
-      <x:c r="A87" s="3" t="str">
+      <x:c r="A87" s="3" t="n">
         <x:v>82</x:v>
       </x:c>
       <x:c r="B87" s="3" t="str">
@@ -4079,25 +4079,25 @@
       <x:c r="E87" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F87" s="3" t="str">
+      <x:c r="F87" s="3" t="n">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G87" s="3" t="str">
+      <x:c r="G87" s="3" t="n">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H87" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I87" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J87" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K87" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L87" s="3" t="str">
+      <x:c r="H87" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I87" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J87" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K87" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L87" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M87" s="3" t="str">
@@ -4108,7 +4108,7 @@
       </x:c>
     </x:row>
     <x:row r="88" ht="28" customHeight="1">
-      <x:c r="A88" s="3" t="str">
+      <x:c r="A88" s="3" t="n">
         <x:v>83</x:v>
       </x:c>
       <x:c r="B88" s="3" t="str">
@@ -4123,25 +4123,25 @@
       <x:c r="E88" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F88" s="3" t="str">
+      <x:c r="F88" s="3" t="n">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G88" s="3" t="str">
+      <x:c r="G88" s="3" t="n">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H88" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I88" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J88" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K88" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L88" s="3" t="str">
+      <x:c r="H88" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I88" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J88" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K88" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L88" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M88" s="3" t="str">
@@ -4152,7 +4152,7 @@
       </x:c>
     </x:row>
     <x:row r="89" ht="28" customHeight="1">
-      <x:c r="A89" s="3" t="str">
+      <x:c r="A89" s="3" t="n">
         <x:v>84</x:v>
       </x:c>
       <x:c r="B89" s="3" t="str">
@@ -4167,25 +4167,25 @@
       <x:c r="E89" s="3" t="str">
         <x:v>simple</x:v>
       </x:c>
-      <x:c r="F89" s="3" t="str">
+      <x:c r="F89" s="3" t="n">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="G89" s="3" t="str">
+      <x:c r="G89" s="3" t="n">
         <x:v>1388</x:v>
       </x:c>
-      <x:c r="H89" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I89" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J89" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K89" s="3" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L89" s="3" t="str">
+      <x:c r="H89" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I89" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J89" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K89" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L89" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M89" s="3" t="str">
@@ -4196,7 +4196,7 @@
       </x:c>
     </x:row>
     <x:row r="90">
-      <x:c r="A90" t="str">
+      <x:c r="A90" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="B90" t="str">
@@ -4217,19 +4217,19 @@
       <x:c r="G90" t="n">
         <x:v>1672</x:v>
       </x:c>
-      <x:c r="H90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L90" t="str">
+      <x:c r="H90" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I90" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J90" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K90" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L90" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M90" t="str">
@@ -4240,7 +4240,7 @@
       </x:c>
     </x:row>
     <x:row r="91">
-      <x:c r="A91" t="str">
+      <x:c r="A91" t="n">
         <x:v>86</x:v>
       </x:c>
       <x:c r="B91" t="str">
@@ -4261,19 +4261,19 @@
       <x:c r="G91" t="n">
         <x:v>1672</x:v>
       </x:c>
-      <x:c r="H91" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I91" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J91" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K91" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L91" t="str">
+      <x:c r="H91" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I91" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J91" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K91" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L91" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M91" t="str">
@@ -4284,7 +4284,7 @@
       </x:c>
     </x:row>
     <x:row r="92">
-      <x:c r="A92" t="str">
+      <x:c r="A92" t="n">
         <x:v>87</x:v>
       </x:c>
       <x:c r="B92" t="str">
@@ -4317,7 +4317,7 @@
       <x:c r="K92" t="n">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="L92" t="str">
+      <x:c r="L92" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M92" t="str">
@@ -4328,7 +4328,7 @@
       </x:c>
     </x:row>
     <x:row r="93">
-      <x:c r="A93" t="str">
+      <x:c r="A93" t="n">
         <x:v>88</x:v>
       </x:c>
       <x:c r="B93" t="str">
@@ -4361,7 +4361,7 @@
       <x:c r="K93" t="n">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="L93" t="str">
+      <x:c r="L93" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M93" t="str">
@@ -4372,7 +4372,7 @@
       </x:c>
     </x:row>
     <x:row r="94">
-      <x:c r="A94" t="str">
+      <x:c r="A94" t="n">
         <x:v>89</x:v>
       </x:c>
       <x:c r="B94" t="str">
@@ -4405,7 +4405,7 @@
       <x:c r="K94" t="n">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="L94" t="str">
+      <x:c r="L94" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M94" t="str">
@@ -4416,7 +4416,7 @@
       </x:c>
     </x:row>
     <x:row r="95">
-      <x:c r="A95" t="str">
+      <x:c r="A95" t="n">
         <x:v>90</x:v>
       </x:c>
       <x:c r="B95" t="str">
@@ -4437,19 +4437,19 @@
       <x:c r="G95" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H95" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I95" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J95" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K95" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L95" t="str">
+      <x:c r="H95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L95" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M95" t="str">
@@ -4460,7 +4460,7 @@
       </x:c>
     </x:row>
     <x:row r="96">
-      <x:c r="A96" t="str">
+      <x:c r="A96" t="n">
         <x:v>91</x:v>
       </x:c>
       <x:c r="B96" t="str">
@@ -4493,7 +4493,7 @@
       <x:c r="K96" t="n">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="L96" t="str">
+      <x:c r="L96" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M96" t="str">
@@ -4504,7 +4504,7 @@
       </x:c>
     </x:row>
     <x:row r="97">
-      <x:c r="A97" t="str">
+      <x:c r="A97" t="n">
         <x:v>92</x:v>
       </x:c>
       <x:c r="B97" t="str">
@@ -4537,7 +4537,7 @@
       <x:c r="K97" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="L97" t="str">
+      <x:c r="L97" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M97" t="str">
@@ -4548,7 +4548,7 @@
       </x:c>
     </x:row>
     <x:row r="98">
-      <x:c r="A98" t="str">
+      <x:c r="A98" t="n">
         <x:v>93</x:v>
       </x:c>
       <x:c r="B98" t="str">
@@ -4569,19 +4569,19 @@
       <x:c r="G98" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H98" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I98" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J98" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K98" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L98" t="str">
+      <x:c r="H98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L98" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M98" t="str">
@@ -4592,7 +4592,7 @@
       </x:c>
     </x:row>
     <x:row r="99">
-      <x:c r="A99" t="str">
+      <x:c r="A99" t="n">
         <x:v>94</x:v>
       </x:c>
       <x:c r="B99" t="str">
@@ -4625,7 +4625,7 @@
       <x:c r="K99" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="L99" t="str">
+      <x:c r="L99" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M99" t="str">
@@ -4636,7 +4636,7 @@
       </x:c>
     </x:row>
     <x:row r="100">
-      <x:c r="A100" t="str">
+      <x:c r="A100" t="n">
         <x:v>95</x:v>
       </x:c>
       <x:c r="B100" t="str">
@@ -4669,7 +4669,7 @@
       <x:c r="K100" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="L100" t="str">
+      <x:c r="L100" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M100" t="str">
@@ -4680,7 +4680,7 @@
       </x:c>
     </x:row>
     <x:row r="101">
-      <x:c r="A101" t="str">
+      <x:c r="A101" t="n">
         <x:v>96</x:v>
       </x:c>
       <x:c r="B101" t="str">
@@ -4701,19 +4701,19 @@
       <x:c r="G101" t="n">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="H101" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I101" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J101" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K101" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L101" t="str">
+      <x:c r="H101" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I101" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J101" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K101" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L101" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M101" t="str">
@@ -4724,7 +4724,7 @@
       </x:c>
     </x:row>
     <x:row r="102">
-      <x:c r="A102" t="str">
+      <x:c r="A102" t="n">
         <x:v>97</x:v>
       </x:c>
       <x:c r="B102" t="str">
@@ -4757,7 +4757,7 @@
       <x:c r="K102" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="L102" t="str">
+      <x:c r="L102" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M102" t="str">
@@ -4768,7 +4768,7 @@
       </x:c>
     </x:row>
     <x:row r="103">
-      <x:c r="A103" t="str">
+      <x:c r="A103" t="n">
         <x:v>98</x:v>
       </x:c>
       <x:c r="B103" t="str">
@@ -4801,7 +4801,7 @@
       <x:c r="K103" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="L103" t="str">
+      <x:c r="L103" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M103" t="str">
@@ -4812,7 +4812,7 @@
       </x:c>
     </x:row>
     <x:row r="104">
-      <x:c r="A104" t="str">
+      <x:c r="A104" t="n">
         <x:v>99</x:v>
       </x:c>
       <x:c r="B104" t="str">
@@ -4845,7 +4845,7 @@
       <x:c r="K104" t="n">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="L104" t="str">
+      <x:c r="L104" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M104" t="str">
@@ -4856,7 +4856,7 @@
       </x:c>
     </x:row>
     <x:row r="105">
-      <x:c r="A105" t="str">
+      <x:c r="A105" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="B105" t="str">
@@ -4877,19 +4877,19 @@
       <x:c r="G105" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H105" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I105" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J105" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K105" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L105" t="str">
+      <x:c r="H105" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I105" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J105" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K105" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L105" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M105" t="str">
@@ -4900,7 +4900,7 @@
       </x:c>
     </x:row>
     <x:row r="106">
-      <x:c r="A106" t="str">
+      <x:c r="A106" t="n">
         <x:v>101</x:v>
       </x:c>
       <x:c r="B106" t="str">
@@ -4921,19 +4921,19 @@
       <x:c r="G106" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H106" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I106" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J106" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K106" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L106" t="str">
+      <x:c r="H106" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I106" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J106" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K106" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L106" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M106" t="str">
@@ -4944,7 +4944,7 @@
       </x:c>
     </x:row>
     <x:row r="107">
-      <x:c r="A107" t="str">
+      <x:c r="A107" t="n">
         <x:v>102</x:v>
       </x:c>
       <x:c r="B107" t="str">
@@ -4965,19 +4965,19 @@
       <x:c r="G107" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H107" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I107" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J107" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K107" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L107" t="str">
+      <x:c r="H107" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I107" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J107" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K107" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L107" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M107" t="str">
@@ -4988,7 +4988,7 @@
       </x:c>
     </x:row>
     <x:row r="108">
-      <x:c r="A108" t="str">
+      <x:c r="A108" t="n">
         <x:v>103</x:v>
       </x:c>
       <x:c r="B108" t="str">
@@ -5009,19 +5009,19 @@
       <x:c r="G108" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H108" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I108" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J108" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K108" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L108" t="str">
+      <x:c r="H108" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I108" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J108" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K108" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L108" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M108" t="str">
@@ -5032,7 +5032,7 @@
       </x:c>
     </x:row>
     <x:row r="109">
-      <x:c r="A109" t="str">
+      <x:c r="A109" t="n">
         <x:v>104</x:v>
       </x:c>
       <x:c r="B109" t="str">
@@ -5053,19 +5053,19 @@
       <x:c r="G109" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H109" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I109" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J109" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K109" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L109" t="str">
+      <x:c r="H109" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I109" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J109" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K109" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L109" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M109" t="str">
@@ -5076,7 +5076,7 @@
       </x:c>
     </x:row>
     <x:row r="110">
-      <x:c r="A110" t="str">
+      <x:c r="A110" t="n">
         <x:v>105</x:v>
       </x:c>
       <x:c r="B110" t="str">
@@ -5097,19 +5097,19 @@
       <x:c r="G110" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H110" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I110" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J110" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K110" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L110" t="str">
+      <x:c r="H110" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I110" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J110" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K110" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L110" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M110" t="str">
@@ -5120,7 +5120,7 @@
       </x:c>
     </x:row>
     <x:row r="111">
-      <x:c r="A111" t="str">
+      <x:c r="A111" t="n">
         <x:v>106</x:v>
       </x:c>
       <x:c r="B111" t="str">
@@ -5141,19 +5141,19 @@
       <x:c r="G111" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H111" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I111" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J111" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K111" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L111" t="str">
+      <x:c r="H111" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I111" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J111" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K111" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M111" t="str">
@@ -5164,7 +5164,7 @@
       </x:c>
     </x:row>
     <x:row r="112">
-      <x:c r="A112" t="str">
+      <x:c r="A112" t="n">
         <x:v>107</x:v>
       </x:c>
       <x:c r="B112" t="str">
@@ -5185,19 +5185,19 @@
       <x:c r="G112" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H112" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I112" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J112" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K112" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L112" t="str">
+      <x:c r="H112" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I112" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J112" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K112" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L112" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M112" t="str">
@@ -5208,7 +5208,7 @@
       </x:c>
     </x:row>
     <x:row r="113">
-      <x:c r="A113" t="str">
+      <x:c r="A113" t="n">
         <x:v>108</x:v>
       </x:c>
       <x:c r="B113" t="str">
@@ -5229,19 +5229,19 @@
       <x:c r="G113" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H113" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I113" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J113" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K113" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L113" t="str">
+      <x:c r="H113" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I113" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J113" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K113" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L113" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M113" t="str">
@@ -5252,7 +5252,7 @@
       </x:c>
     </x:row>
     <x:row r="114">
-      <x:c r="A114" t="str">
+      <x:c r="A114" t="n">
         <x:v>109</x:v>
       </x:c>
       <x:c r="B114" t="str">
@@ -5273,19 +5273,19 @@
       <x:c r="G114" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H114" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I114" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J114" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K114" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L114" t="str">
+      <x:c r="H114" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I114" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J114" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K114" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L114" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M114" t="str">
@@ -5296,7 +5296,7 @@
       </x:c>
     </x:row>
     <x:row r="115">
-      <x:c r="A115" t="str">
+      <x:c r="A115" t="n">
         <x:v>110</x:v>
       </x:c>
       <x:c r="B115" t="str">
@@ -5317,19 +5317,19 @@
       <x:c r="G115" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H115" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I115" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J115" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K115" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L115" t="str">
+      <x:c r="H115" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I115" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J115" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K115" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L115" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M115" t="str">
@@ -5340,7 +5340,7 @@
       </x:c>
     </x:row>
     <x:row r="116">
-      <x:c r="A116" t="str">
+      <x:c r="A116" t="n">
         <x:v>111</x:v>
       </x:c>
       <x:c r="B116" t="str">
@@ -5361,19 +5361,19 @@
       <x:c r="G116" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H116" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I116" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J116" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K116" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L116" t="str">
+      <x:c r="H116" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I116" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J116" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K116" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L116" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M116" t="str">
@@ -5384,7 +5384,7 @@
       </x:c>
     </x:row>
     <x:row r="117">
-      <x:c r="A117" t="str">
+      <x:c r="A117" t="n">
         <x:v>112</x:v>
       </x:c>
       <x:c r="B117" t="str">
@@ -5405,19 +5405,19 @@
       <x:c r="G117" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H117" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I117" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J117" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K117" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L117" t="str">
+      <x:c r="H117" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I117" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J117" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K117" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L117" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M117" t="str">
@@ -5428,7 +5428,7 @@
       </x:c>
     </x:row>
     <x:row r="118">
-      <x:c r="A118" t="str">
+      <x:c r="A118" t="n">
         <x:v>113</x:v>
       </x:c>
       <x:c r="B118" t="str">
@@ -5449,19 +5449,19 @@
       <x:c r="G118" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H118" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I118" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J118" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K118" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L118" t="str">
+      <x:c r="H118" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I118" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J118" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K118" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L118" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M118" t="str">
@@ -5472,7 +5472,7 @@
       </x:c>
     </x:row>
     <x:row r="119">
-      <x:c r="A119" t="str">
+      <x:c r="A119" t="n">
         <x:v>114</x:v>
       </x:c>
       <x:c r="B119" t="str">
@@ -5493,19 +5493,19 @@
       <x:c r="G119" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H119" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I119" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J119" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K119" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L119" t="str">
+      <x:c r="H119" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I119" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J119" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K119" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L119" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M119" t="str">
@@ -5516,7 +5516,7 @@
       </x:c>
     </x:row>
     <x:row r="120">
-      <x:c r="A120" t="str">
+      <x:c r="A120" t="n">
         <x:v>115</x:v>
       </x:c>
       <x:c r="B120" t="str">
@@ -5537,19 +5537,19 @@
       <x:c r="G120" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H120" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I120" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J120" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K120" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L120" t="str">
+      <x:c r="H120" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I120" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J120" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K120" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L120" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M120" t="str">
@@ -5560,7 +5560,7 @@
       </x:c>
     </x:row>
     <x:row r="121">
-      <x:c r="A121" t="str">
+      <x:c r="A121" t="n">
         <x:v>116</x:v>
       </x:c>
       <x:c r="B121" t="str">
@@ -5581,19 +5581,19 @@
       <x:c r="G121" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H121" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I121" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J121" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K121" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L121" t="str">
+      <x:c r="H121" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I121" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J121" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K121" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L121" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M121" t="str">
@@ -5604,7 +5604,7 @@
       </x:c>
     </x:row>
     <x:row r="122">
-      <x:c r="A122" t="str">
+      <x:c r="A122" t="n">
         <x:v>117</x:v>
       </x:c>
       <x:c r="B122" t="str">
@@ -5625,19 +5625,19 @@
       <x:c r="G122" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H122" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I122" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J122" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K122" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L122" t="str">
+      <x:c r="H122" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I122" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J122" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K122" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L122" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M122" t="str">
@@ -5648,7 +5648,7 @@
       </x:c>
     </x:row>
     <x:row r="123">
-      <x:c r="A123" t="str">
+      <x:c r="A123" t="n">
         <x:v>118</x:v>
       </x:c>
       <x:c r="B123" t="str">
@@ -5669,19 +5669,19 @@
       <x:c r="G123" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H123" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I123" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J123" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K123" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L123" t="str">
+      <x:c r="H123" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I123" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J123" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K123" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L123" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M123" t="str">
@@ -5692,7 +5692,7 @@
       </x:c>
     </x:row>
     <x:row r="124">
-      <x:c r="A124" t="str">
+      <x:c r="A124" t="n">
         <x:v>119</x:v>
       </x:c>
       <x:c r="B124" t="str">
@@ -5713,19 +5713,19 @@
       <x:c r="G124" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H124" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I124" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J124" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K124" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L124" t="str">
+      <x:c r="H124" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I124" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J124" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K124" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L124" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M124" t="str">
@@ -5736,7 +5736,7 @@
       </x:c>
     </x:row>
     <x:row r="125">
-      <x:c r="A125" t="str">
+      <x:c r="A125" t="n">
         <x:v>120</x:v>
       </x:c>
       <x:c r="B125" t="str">
@@ -5757,19 +5757,19 @@
       <x:c r="G125" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H125" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I125" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J125" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K125" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L125" t="str">
+      <x:c r="H125" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I125" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J125" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K125" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L125" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M125" t="str">
@@ -5780,7 +5780,7 @@
       </x:c>
     </x:row>
     <x:row r="126" ht="28" customHeight="1">
-      <x:c r="A126" t="str">
+      <x:c r="A126" t="n">
         <x:v>121</x:v>
       </x:c>
       <x:c r="B126" t="str">
@@ -5801,19 +5801,19 @@
       <x:c r="G126" t="n">
         <x:v>1254</x:v>
       </x:c>
-      <x:c r="H126" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I126" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J126" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K126" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L126" t="str">
+      <x:c r="H126" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I126" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J126" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K126" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L126" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M126" t="str">
@@ -5821,6 +5821,578 @@
       </x:c>
       <x:c r="N126" t="str">
         <x:v>cover</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" t="n">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B127" t="str">
+        <x:v>home_adventure</x:v>
+      </x:c>
+      <x:c r="C127" t="str">
+        <x:v>ui/windows/home/home_adventure/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D127" t="str">
+        <x:v>ui/windows/home</x:v>
+      </x:c>
+      <x:c r="E127" t="str">
+        <x:v>sliced</x:v>
+      </x:c>
+      <x:c r="F127" t="n">
+        <x:v>685</x:v>
+      </x:c>
+      <x:c r="G127" t="n">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="H127" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I127" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J127" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="K127" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="L127" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M127" t="str">
+        <x:v>2026-10-07逐页参考还原；独立专用PNG</x:v>
+      </x:c>
+      <x:c r="N127" t="str">
+        <x:v>height</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" t="n">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B128" t="str">
+        <x:v>home_challenge</x:v>
+      </x:c>
+      <x:c r="C128" t="str">
+        <x:v>ui/windows/home/home_challenge/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D128" t="str">
+        <x:v>ui/windows/home</x:v>
+      </x:c>
+      <x:c r="E128" t="str">
+        <x:v>sliced</x:v>
+      </x:c>
+      <x:c r="F128" t="n">
+        <x:v>683</x:v>
+      </x:c>
+      <x:c r="G128" t="n">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="H128" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I128" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J128" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="K128" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="L128" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M128" t="str">
+        <x:v>2026-10-07逐页参考还原；独立专用PNG</x:v>
+      </x:c>
+      <x:c r="N128" t="str">
+        <x:v>height</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" t="n">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B129" t="str">
+        <x:v>loading_track</x:v>
+      </x:c>
+      <x:c r="C129" t="str">
+        <x:v>ui/hud/loading/loading_track/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D129" t="str">
+        <x:v>ui/hud/loading</x:v>
+      </x:c>
+      <x:c r="E129" t="str">
+        <x:v>sliced</x:v>
+      </x:c>
+      <x:c r="F129" t="n">
+        <x:v>702</x:v>
+      </x:c>
+      <x:c r="G129" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="H129" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I129" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="J129" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K129" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L129" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M129" t="str">
+        <x:v>2026-10-07逐页参考还原；独立专用PNG</x:v>
+      </x:c>
+      <x:c r="N129" t="str">
+        <x:v>height</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B130" t="str">
+        <x:v>loading_fill</x:v>
+      </x:c>
+      <x:c r="C130" t="str">
+        <x:v>ui/hud/loading/loading_fill/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D130" t="str">
+        <x:v>ui/hud/loading</x:v>
+      </x:c>
+      <x:c r="E130" t="str">
+        <x:v>sliced</x:v>
+      </x:c>
+      <x:c r="F130" t="n">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="G130" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H130" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="I130" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J130" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K130" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L130" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M130" t="str">
+        <x:v>2026-10-07逐页参考还原；独立专用PNG</x:v>
+      </x:c>
+      <x:c r="N130" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B131" t="str">
+        <x:v>loading_paw</x:v>
+      </x:c>
+      <x:c r="C131" t="str">
+        <x:v>ui/hud/loading/loading_paw/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D131" t="str">
+        <x:v>ui/hud/loading</x:v>
+      </x:c>
+      <x:c r="E131" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F131" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G131" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H131" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I131" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J131" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K131" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L131" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M131" t="str">
+        <x:v>2026-10-07逐页参考还原；独立专用PNG</x:v>
+      </x:c>
+      <x:c r="N131" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" t="n">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B132" t="str">
+        <x:v>loading_title_paw</x:v>
+      </x:c>
+      <x:c r="C132" t="str">
+        <x:v>ui/hud/loading/loading_title_paw/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D132" t="str">
+        <x:v>ui/hud/loading</x:v>
+      </x:c>
+      <x:c r="E132" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F132" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G132" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H132" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I132" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J132" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K132" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L132" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M132" t="str">
+        <x:v>2026-10-07逐页参考还原；独立专用PNG</x:v>
+      </x:c>
+      <x:c r="N132" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B133" t="str">
+        <x:v>counter_white</x:v>
+      </x:c>
+      <x:c r="C133" t="str">
+        <x:v>ui/hud/counters/counter_white/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D133" t="str">
+        <x:v>ui/hud/counters</x:v>
+      </x:c>
+      <x:c r="E133" t="str">
+        <x:v>sliced</x:v>
+      </x:c>
+      <x:c r="F133" t="n">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="G133" t="n">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="H133" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="I133" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="J133" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K133" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="L133" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M133" t="str">
+        <x:v>2026-10-07逐页参考还原；独立专用PNG</x:v>
+      </x:c>
+      <x:c r="N133" t="str">
+        <x:v>height</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" t="n">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B134" t="str">
+        <x:v>window_flat</x:v>
+      </x:c>
+      <x:c r="C134" t="str">
+        <x:v>ui/windows/common/window_flat/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D134" t="str">
+        <x:v>ui/windows/common</x:v>
+      </x:c>
+      <x:c r="E134" t="str">
+        <x:v>sliced</x:v>
+      </x:c>
+      <x:c r="F134" t="n">
+        <x:v>716</x:v>
+      </x:c>
+      <x:c r="G134" t="n">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="H134" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="I134" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="J134" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K134" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="L134" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M134" t="str">
+        <x:v>2026-10-07逐页参考还原；独立专用PNG</x:v>
+      </x:c>
+      <x:c r="N134" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B135" t="str">
+        <x:v>portrait_normal</x:v>
+      </x:c>
+      <x:c r="C135" t="str">
+        <x:v>ui/windows/loadout/portrait_normal/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D135" t="str">
+        <x:v>ui/windows/loadout</x:v>
+      </x:c>
+      <x:c r="E135" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F135" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G135" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H135" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I135" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J135" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K135" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L135" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M135" t="str">
+        <x:v>2026-10-07逐页参考还原；独立专用PNG</x:v>
+      </x:c>
+      <x:c r="N135" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" t="n">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B136" t="str">
+        <x:v>portrait_selected</x:v>
+      </x:c>
+      <x:c r="C136" t="str">
+        <x:v>ui/windows/loadout/portrait_selected/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D136" t="str">
+        <x:v>ui/windows/loadout</x:v>
+      </x:c>
+      <x:c r="E136" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F136" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G136" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H136" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I136" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J136" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K136" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L136" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M136" t="str">
+        <x:v>2026-10-07逐页参考还原；独立专用PNG</x:v>
+      </x:c>
+      <x:c r="N136" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" t="n">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B137" t="str">
+        <x:v>preview_ground</x:v>
+      </x:c>
+      <x:c r="C137" t="str">
+        <x:v>ui/windows/adventure/preview_ground/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D137" t="str">
+        <x:v>ui/windows/adventure</x:v>
+      </x:c>
+      <x:c r="E137" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F137" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G137" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H137" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I137" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J137" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K137" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L137" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M137" t="str">
+        <x:v>缩略图底纹仅在卡片内适配，不能cover溢出</x:v>
+      </x:c>
+      <x:c r="N137" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" t="n">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B138" t="str">
+        <x:v>mint_pill</x:v>
+      </x:c>
+      <x:c r="C138" t="str">
+        <x:v>ui/windows/common/mint_pill/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D138" t="str">
+        <x:v>ui/windows/common</x:v>
+      </x:c>
+      <x:c r="E138" t="str">
+        <x:v>sliced</x:v>
+      </x:c>
+      <x:c r="F138" t="n">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="G138" t="n">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="H138" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="I138" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="J138" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K138" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="L138" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M138" t="str">
+        <x:v>单独生成完整PNG；淡绿圆角按钮/选卡标题</x:v>
+      </x:c>
+      <x:c r="N138" t="str">
+        <x:v>height</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" t="n">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B139" t="str">
+        <x:v>counter_green</x:v>
+      </x:c>
+      <x:c r="C139" t="str">
+        <x:v>ui/hud/counters/counter_green/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D139" t="str">
+        <x:v>ui/hud/counters</x:v>
+      </x:c>
+      <x:c r="E139" t="str">
+        <x:v>sliced</x:v>
+      </x:c>
+      <x:c r="F139" t="n">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="G139" t="n">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="H139" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="I139" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="J139" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K139" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="L139" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M139" t="str">
+        <x:v>单独生成完整PNG；战斗白底绿边计数框</x:v>
+      </x:c>
+      <x:c r="N139" t="str">
+        <x:v>height</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/VisualSkin.xlsx
+++ b/design/tables/VisualSkin.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisualSkin" sheetId="1" r:id="R234a22d7a68c44d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisualSkin" sheetId="1" r:id="R5ee1908e903c4dc0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6395,6 +6395,50 @@
         <x:v>height</x:v>
       </x:c>
     </x:row>
+    <x:row r="140">
+      <x:c r="A140" t="n">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B140" t="str">
+        <x:v>rank_star</x:v>
+      </x:c>
+      <x:c r="C140" t="str">
+        <x:v>gameplay/effects/rank_star/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D140" t="str">
+        <x:v>gameplay/effects</x:v>
+      </x:c>
+      <x:c r="E140" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F140" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G140" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H140" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I140" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J140" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K140" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L140" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M140" t="str">
+        <x:v>单张透明等级星星PNG</x:v>
+      </x:c>
+      <x:c r="N140" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/VisualSkin.xlsx
+++ b/design/tables/VisualSkin.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisualSkin" sheetId="1" r:id="R5ee1908e903c4dc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisualSkin" sheetId="1" r:id="R39906ffa1a834861"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6439,6 +6439,50 @@
         <x:v>contain</x:v>
       </x:c>
     </x:row>
+    <x:row r="141">
+      <x:c r="A141" t="n">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B141" t="str">
+        <x:v>shop_interior</x:v>
+      </x:c>
+      <x:c r="C141" t="str">
+        <x:v>ui/windows/shop/shop_interior/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D141" t="str">
+        <x:v>ui/windows/shop</x:v>
+      </x:c>
+      <x:c r="E141" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F141" t="n">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="G141" t="n">
+        <x:v>1536</x:v>
+      </x:c>
+      <x:c r="H141" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I141" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J141" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K141" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L141" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M141" t="str">
+        <x:v>单张完整PNG，内置图像生成；固定便利店内景</x:v>
+      </x:c>
+      <x:c r="N141" t="str">
+        <x:v>cover</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/VisualSkin.xlsx
+++ b/design/tables/VisualSkin.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisualSkin" sheetId="1" r:id="R39906ffa1a834861"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisualSkin" sheetId="1" r:id="Rfb17e5654e3e4caf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6483,6 +6483,138 @@
         <x:v>cover</x:v>
       </x:c>
     </x:row>
+    <x:row r="142">
+      <x:c r="A142" t="n">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B142" t="str">
+        <x:v>shop_floor</x:v>
+      </x:c>
+      <x:c r="C142" t="str">
+        <x:v>ui/windows/shop/shop_floor/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D142" t="str">
+        <x:v>ui/windows/shop</x:v>
+      </x:c>
+      <x:c r="E142" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F142" t="n">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="G142" t="n">
+        <x:v>1536</x:v>
+      </x:c>
+      <x:c r="H142" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I142" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J142" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K142" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L142" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M142" t="str">
+        <x:v>独立PNG；统一俯视斜角便利店视角</x:v>
+      </x:c>
+      <x:c r="N142" t="str">
+        <x:v>cover</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" t="n">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B143" t="str">
+        <x:v>shop_shelf</x:v>
+      </x:c>
+      <x:c r="C143" t="str">
+        <x:v>ui/windows/shop/shop_shelf/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D143" t="str">
+        <x:v>ui/windows/shop</x:v>
+      </x:c>
+      <x:c r="E143" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F143" t="n">
+        <x:v>1254</x:v>
+      </x:c>
+      <x:c r="G143" t="n">
+        <x:v>1254</x:v>
+      </x:c>
+      <x:c r="H143" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I143" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J143" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K143" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L143" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M143" t="str">
+        <x:v>独立PNG；统一俯视斜角便利店视角</x:v>
+      </x:c>
+      <x:c r="N143" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" t="n">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B144" t="str">
+        <x:v>shop_checkout</x:v>
+      </x:c>
+      <x:c r="C144" t="str">
+        <x:v>ui/windows/shop/shop_checkout/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D144" t="str">
+        <x:v>ui/windows/shop</x:v>
+      </x:c>
+      <x:c r="E144" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F144" t="n">
+        <x:v>1254</x:v>
+      </x:c>
+      <x:c r="G144" t="n">
+        <x:v>1254</x:v>
+      </x:c>
+      <x:c r="H144" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I144" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J144" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K144" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L144" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M144" t="str">
+        <x:v>独立PNG；统一俯视斜角便利店视角</x:v>
+      </x:c>
+      <x:c r="N144" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/VisualSkin.xlsx
+++ b/design/tables/VisualSkin.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisualSkin" sheetId="1" r:id="Rfb17e5654e3e4caf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisualSkin" sheetId="1" r:id="R3792144b8c6f402c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6615,6 +6615,226 @@
         <x:v>contain</x:v>
       </x:c>
     </x:row>
+    <x:row r="145">
+      <x:c r="A145" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="B145" t="str">
+        <x:v>map_22</x:v>
+      </x:c>
+      <x:c r="C145" t="str">
+        <x:v>gameplay/maps/map_22/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D145" t="str">
+        <x:v>gameplay/maps</x:v>
+      </x:c>
+      <x:c r="E145" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F145" t="n">
+        <x:v>780</x:v>
+      </x:c>
+      <x:c r="G145" t="n">
+        <x:v>1388</x:v>
+      </x:c>
+      <x:c r="H145" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I145" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J145" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K145" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L145" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M145" t="str">
+        <x:v>挑战专题急件专场；复用成熟路线并烘焙独立PNG</x:v>
+      </x:c>
+      <x:c r="N145" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" t="n">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B146" t="str">
+        <x:v>map_23</x:v>
+      </x:c>
+      <x:c r="C146" t="str">
+        <x:v>gameplay/maps/map_23/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D146" t="str">
+        <x:v>gameplay/maps</x:v>
+      </x:c>
+      <x:c r="E146" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F146" t="n">
+        <x:v>780</x:v>
+      </x:c>
+      <x:c r="G146" t="n">
+        <x:v>1388</x:v>
+      </x:c>
+      <x:c r="H146" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I146" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J146" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K146" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L146" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M146" t="str">
+        <x:v>挑战专题仓库清点；复用成熟路线并烘焙独立PNG</x:v>
+      </x:c>
+      <x:c r="N146" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" t="n">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="B147" t="str">
+        <x:v>map_24</x:v>
+      </x:c>
+      <x:c r="C147" t="str">
+        <x:v>gameplay/maps/map_24/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D147" t="str">
+        <x:v>gameplay/maps</x:v>
+      </x:c>
+      <x:c r="E147" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F147" t="n">
+        <x:v>780</x:v>
+      </x:c>
+      <x:c r="G147" t="n">
+        <x:v>1388</x:v>
+      </x:c>
+      <x:c r="H147" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I147" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J147" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K147" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L147" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M147" t="str">
+        <x:v>挑战专题零钱狂欢；复用成熟路线并烘焙独立PNG</x:v>
+      </x:c>
+      <x:c r="N147" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" t="n">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="B148" t="str">
+        <x:v>map_25</x:v>
+      </x:c>
+      <x:c r="C148" t="str">
+        <x:v>gameplay/maps/map_25/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D148" t="str">
+        <x:v>gameplay/maps</x:v>
+      </x:c>
+      <x:c r="E148" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F148" t="n">
+        <x:v>780</x:v>
+      </x:c>
+      <x:c r="G148" t="n">
+        <x:v>1388</x:v>
+      </x:c>
+      <x:c r="H148" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I148" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J148" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K148" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L148" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M148" t="str">
+        <x:v>挑战专题迷你流水线；复用成熟路线并烘焙独立PNG</x:v>
+      </x:c>
+      <x:c r="N148" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" t="n">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="B149" t="str">
+        <x:v>map_26</x:v>
+      </x:c>
+      <x:c r="C149" t="str">
+        <x:v>gameplay/maps/map_26/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D149" t="str">
+        <x:v>gameplay/maps</x:v>
+      </x:c>
+      <x:c r="E149" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F149" t="n">
+        <x:v>780</x:v>
+      </x:c>
+      <x:c r="G149" t="n">
+        <x:v>1388</x:v>
+      </x:c>
+      <x:c r="H149" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I149" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J149" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K149" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L149" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M149" t="str">
+        <x:v>挑战专题午夜压轴；复用成熟路线并烘焙独立PNG</x:v>
+      </x:c>
+      <x:c r="N149" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/VisualSkin.xlsx
+++ b/design/tables/VisualSkin.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisualSkin" sheetId="1" r:id="R3792144b8c6f402c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisualSkin" sheetId="1" r:id="Rfd6713eb82664e37"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6835,6 +6835,138 @@
         <x:v>stretch</x:v>
       </x:c>
     </x:row>
+    <x:row r="150">
+      <x:c r="A150" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B150" t="str">
+        <x:v>shop_entrance</x:v>
+      </x:c>
+      <x:c r="C150" t="str">
+        <x:v>ui/windows/shop/shop_entrance/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D150" t="str">
+        <x:v>ui/windows/shop</x:v>
+      </x:c>
+      <x:c r="E150" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F150" t="n">
+        <x:v>1254</x:v>
+      </x:c>
+      <x:c r="G150" t="n">
+        <x:v>1254</x:v>
+      </x:c>
+      <x:c r="H150" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I150" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J150" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K150" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L150" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M150" t="str">
+        <x:v>商店表现独立PNG；完整透明画布，无图集切片</x:v>
+      </x:c>
+      <x:c r="N150" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" t="n">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B151" t="str">
+        <x:v>shop_bag</x:v>
+      </x:c>
+      <x:c r="C151" t="str">
+        <x:v>ui/windows/shop/shop_bag/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D151" t="str">
+        <x:v>ui/windows/shop</x:v>
+      </x:c>
+      <x:c r="E151" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F151" t="n">
+        <x:v>1254</x:v>
+      </x:c>
+      <x:c r="G151" t="n">
+        <x:v>1254</x:v>
+      </x:c>
+      <x:c r="H151" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I151" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J151" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K151" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L151" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M151" t="str">
+        <x:v>商店表现独立PNG；完整透明画布，无图集切片</x:v>
+      </x:c>
+      <x:c r="N151" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" t="n">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="B152" t="str">
+        <x:v>shop_crate</x:v>
+      </x:c>
+      <x:c r="C152" t="str">
+        <x:v>ui/windows/shop/shop_crate/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D152" t="str">
+        <x:v>ui/windows/shop</x:v>
+      </x:c>
+      <x:c r="E152" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F152" t="n">
+        <x:v>1254</x:v>
+      </x:c>
+      <x:c r="G152" t="n">
+        <x:v>1254</x:v>
+      </x:c>
+      <x:c r="H152" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I152" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J152" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K152" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L152" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M152" t="str">
+        <x:v>商店表现独立PNG；完整透明画布，无图集切片</x:v>
+      </x:c>
+      <x:c r="N152" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/VisualSkin.xlsx
+++ b/design/tables/VisualSkin.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisualSkin" sheetId="1" r:id="Rfd6713eb82664e37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisualSkin" sheetId="1" r:id="Rbade3606c7454d78"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6967,6 +6967,358 @@
         <x:v>contain</x:v>
       </x:c>
     </x:row>
+    <x:row r="153">
+      <x:c r="A153" t="n">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="B153" t="str">
+        <x:v>shop_uniform_sprout</x:v>
+      </x:c>
+      <x:c r="C153" t="str">
+        <x:v>ui/windows/shop/uniforms/sprout/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D153" t="str">
+        <x:v>ui/windows/shop/uniforms</x:v>
+      </x:c>
+      <x:c r="E153" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F153" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="G153" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="H153" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I153" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J153" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K153" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L153" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M153" t="str">
+        <x:v>独立制服PNG，统一透明画布与脚底，完整源图归档</x:v>
+      </x:c>
+      <x:c r="N153" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" t="n">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="B154" t="str">
+        <x:v>shop_uniform_frost</x:v>
+      </x:c>
+      <x:c r="C154" t="str">
+        <x:v>ui/windows/shop/uniforms/frost/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D154" t="str">
+        <x:v>ui/windows/shop/uniforms</x:v>
+      </x:c>
+      <x:c r="E154" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F154" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="G154" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="H154" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I154" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J154" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K154" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L154" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M154" t="str">
+        <x:v>独立制服PNG，统一透明画布与脚底，完整源图归档</x:v>
+      </x:c>
+      <x:c r="N154" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="B155" t="str">
+        <x:v>shop_uniform_bloom</x:v>
+      </x:c>
+      <x:c r="C155" t="str">
+        <x:v>ui/windows/shop/uniforms/bloom/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D155" t="str">
+        <x:v>ui/windows/shop/uniforms</x:v>
+      </x:c>
+      <x:c r="E155" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F155" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="G155" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="H155" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I155" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J155" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K155" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L155" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M155" t="str">
+        <x:v>独立制服PNG，统一透明画布与脚底，完整源图归档</x:v>
+      </x:c>
+      <x:c r="N155" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" t="n">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B156" t="str">
+        <x:v>shop_uniform_scope</x:v>
+      </x:c>
+      <x:c r="C156" t="str">
+        <x:v>ui/windows/shop/uniforms/scope/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D156" t="str">
+        <x:v>ui/windows/shop/uniforms</x:v>
+      </x:c>
+      <x:c r="E156" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F156" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="G156" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="H156" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I156" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J156" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K156" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L156" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M156" t="str">
+        <x:v>独立制服PNG，统一透明画布与脚底，完整源图归档</x:v>
+      </x:c>
+      <x:c r="N156" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" t="n">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="B157" t="str">
+        <x:v>shop_uniform_spark</x:v>
+      </x:c>
+      <x:c r="C157" t="str">
+        <x:v>ui/windows/shop/uniforms/spark/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D157" t="str">
+        <x:v>ui/windows/shop/uniforms</x:v>
+      </x:c>
+      <x:c r="E157" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F157" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="G157" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="H157" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I157" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J157" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K157" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L157" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M157" t="str">
+        <x:v>独立制服PNG，统一透明画布与脚底，完整源图归档</x:v>
+      </x:c>
+      <x:c r="N157" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" t="n">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="B158" t="str">
+        <x:v>shop_uniform_ember</x:v>
+      </x:c>
+      <x:c r="C158" t="str">
+        <x:v>ui/windows/shop/uniforms/ember/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D158" t="str">
+        <x:v>ui/windows/shop/uniforms</x:v>
+      </x:c>
+      <x:c r="E158" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F158" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="G158" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="H158" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I158" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J158" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K158" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L158" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M158" t="str">
+        <x:v>独立制服PNG，统一透明画布与脚底，完整源图归档</x:v>
+      </x:c>
+      <x:c r="N158" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="B159" t="str">
+        <x:v>shop_uniform_mint</x:v>
+      </x:c>
+      <x:c r="C159" t="str">
+        <x:v>ui/windows/shop/uniforms/mint/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D159" t="str">
+        <x:v>ui/windows/shop/uniforms</x:v>
+      </x:c>
+      <x:c r="E159" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F159" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="G159" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="H159" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I159" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J159" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K159" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L159" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M159" t="str">
+        <x:v>独立制服PNG，统一透明画布与脚底，完整源图归档</x:v>
+      </x:c>
+      <x:c r="N159" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" t="n">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="B160" t="str">
+        <x:v>shop_uniform_fan</x:v>
+      </x:c>
+      <x:c r="C160" t="str">
+        <x:v>ui/windows/shop/uniforms/fan/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D160" t="str">
+        <x:v>ui/windows/shop/uniforms</x:v>
+      </x:c>
+      <x:c r="E160" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F160" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="G160" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="H160" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I160" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J160" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K160" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L160" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M160" t="str">
+        <x:v>独立制服PNG，统一透明画布与脚底，完整源图归档</x:v>
+      </x:c>
+      <x:c r="N160" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/VisualSkin.xlsx
+++ b/design/tables/VisualSkin.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisualSkin" sheetId="1" r:id="Rbade3606c7454d78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisualSkin" sheetId="1" r:id="Rb581e969d7a74b8c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7319,6 +7319,798 @@
         <x:v>contain</x:v>
       </x:c>
     </x:row>
+    <x:row r="161">
+      <x:c r="A161" t="n">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="B161" t="str">
+        <x:v>shop_room_v2</x:v>
+      </x:c>
+      <x:c r="C161" t="str">
+        <x:v>ui/windows/shop/reference/room/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D161" t="str">
+        <x:v>ui/windows/shop/reference</x:v>
+      </x:c>
+      <x:c r="E161" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F161" t="n">
+        <x:v>941</x:v>
+      </x:c>
+      <x:c r="G161" t="n">
+        <x:v>1672</x:v>
+      </x:c>
+      <x:c r="H161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M161" t="str">
+        <x:v>用户效果图参考；内置imagegen独立PNG；完整源图保留</x:v>
+      </x:c>
+      <x:c r="N161" t="str">
+        <x:v>cover</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" t="n">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="B162" t="str">
+        <x:v>shop_shelf_v2</x:v>
+      </x:c>
+      <x:c r="C162" t="str">
+        <x:v>ui/windows/shop/reference/shelf/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D162" t="str">
+        <x:v>ui/windows/shop/reference</x:v>
+      </x:c>
+      <x:c r="E162" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F162" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="G162" t="n">
+        <x:v>576</x:v>
+      </x:c>
+      <x:c r="H162" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I162" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J162" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K162" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L162" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M162" t="str">
+        <x:v>用户效果图参考；内置imagegen独立PNG；完整源图保留</x:v>
+      </x:c>
+      <x:c r="N162" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" t="n">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="B163" t="str">
+        <x:v>shop_counter_v2</x:v>
+      </x:c>
+      <x:c r="C163" t="str">
+        <x:v>ui/windows/shop/reference/counter/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D163" t="str">
+        <x:v>ui/windows/shop/reference</x:v>
+      </x:c>
+      <x:c r="E163" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F163" t="n">
+        <x:v>768</x:v>
+      </x:c>
+      <x:c r="G163" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="H163" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I163" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J163" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K163" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L163" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M163" t="str">
+        <x:v>用户效果图参考；内置imagegen独立PNG；完整源图保留</x:v>
+      </x:c>
+      <x:c r="N163" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" t="n">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B164" t="str">
+        <x:v>shop_nav_staff</x:v>
+      </x:c>
+      <x:c r="C164" t="str">
+        <x:v>ui/windows/shop/reference/nav_staff/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D164" t="str">
+        <x:v>ui/windows/shop/reference</x:v>
+      </x:c>
+      <x:c r="E164" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F164" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="G164" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="H164" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I164" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J164" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K164" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L164" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M164" t="str">
+        <x:v>用户效果图参考；内置imagegen独立PNG；完整源图保留</x:v>
+      </x:c>
+      <x:c r="N164" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="B165" t="str">
+        <x:v>shop_nav_upgrade</x:v>
+      </x:c>
+      <x:c r="C165" t="str">
+        <x:v>ui/windows/shop/reference/nav_upgrade/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D165" t="str">
+        <x:v>ui/windows/shop/reference</x:v>
+      </x:c>
+      <x:c r="E165" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F165" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="G165" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="H165" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I165" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J165" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K165" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L165" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M165" t="str">
+        <x:v>用户效果图参考；内置imagegen独立PNG；完整源图保留</x:v>
+      </x:c>
+      <x:c r="N165" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" t="n">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="B166" t="str">
+        <x:v>shop_nav_goods</x:v>
+      </x:c>
+      <x:c r="C166" t="str">
+        <x:v>ui/windows/shop/reference/nav_goods/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D166" t="str">
+        <x:v>ui/windows/shop/reference</x:v>
+      </x:c>
+      <x:c r="E166" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F166" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="G166" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="H166" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I166" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J166" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K166" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L166" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M166" t="str">
+        <x:v>用户效果图参考；内置imagegen独立PNG；完整源图保留</x:v>
+      </x:c>
+      <x:c r="N166" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" t="n">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="B167" t="str">
+        <x:v>shop_nav_research</x:v>
+      </x:c>
+      <x:c r="C167" t="str">
+        <x:v>ui/windows/shop/reference/nav_research/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D167" t="str">
+        <x:v>ui/windows/shop/reference</x:v>
+      </x:c>
+      <x:c r="E167" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F167" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="G167" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="H167" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I167" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J167" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K167" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L167" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M167" t="str">
+        <x:v>用户效果图参考；内置imagegen独立PNG；完整源图保留</x:v>
+      </x:c>
+      <x:c r="N167" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" t="n">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="B168" t="str">
+        <x:v>shop_nav_uniform</x:v>
+      </x:c>
+      <x:c r="C168" t="str">
+        <x:v>ui/windows/shop/reference/nav_uniform/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D168" t="str">
+        <x:v>ui/windows/shop/reference</x:v>
+      </x:c>
+      <x:c r="E168" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F168" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="G168" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="H168" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I168" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J168" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K168" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L168" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M168" t="str">
+        <x:v>用户效果图参考；内置imagegen独立PNG；完整源图保留</x:v>
+      </x:c>
+      <x:c r="N168" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" t="n">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="B169" t="str">
+        <x:v>adventure_banner_v2</x:v>
+      </x:c>
+      <x:c r="C169" t="str">
+        <x:v>ui/windows/modes/adventure_banner/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D169" t="str">
+        <x:v>ui/windows/modes</x:v>
+      </x:c>
+      <x:c r="E169" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F169" t="n">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="G169" t="n">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="H169" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I169" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J169" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K169" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L169" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M169" t="str">
+        <x:v>用户模式效果图参考；内置imagegen独立PNG；不使用图集</x:v>
+      </x:c>
+      <x:c r="N169" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="B170" t="str">
+        <x:v>challenge_banner_v2</x:v>
+      </x:c>
+      <x:c r="C170" t="str">
+        <x:v>ui/windows/modes/challenge_banner/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D170" t="str">
+        <x:v>ui/windows/modes</x:v>
+      </x:c>
+      <x:c r="E170" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F170" t="n">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="G170" t="n">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="H170" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I170" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J170" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K170" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L170" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M170" t="str">
+        <x:v>用户模式效果图参考；内置imagegen独立PNG；不使用图集</x:v>
+      </x:c>
+      <x:c r="N170" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" t="n">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="B171" t="str">
+        <x:v>ranking_banner_v2</x:v>
+      </x:c>
+      <x:c r="C171" t="str">
+        <x:v>ui/windows/modes/ranking_banner/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D171" t="str">
+        <x:v>ui/windows/modes</x:v>
+      </x:c>
+      <x:c r="E171" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F171" t="n">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="G171" t="n">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="H171" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I171" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J171" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K171" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L171" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M171" t="str">
+        <x:v>用户模式效果图参考；内置imagegen独立PNG；不使用图集</x:v>
+      </x:c>
+      <x:c r="N171" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" t="n">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="B172" t="str">
+        <x:v>topic_opening</x:v>
+      </x:c>
+      <x:c r="C172" t="str">
+        <x:v>ui/windows/modes/topic_opening/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D172" t="str">
+        <x:v>ui/windows/modes</x:v>
+      </x:c>
+      <x:c r="E172" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F172" t="n">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="G172" t="n">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="H172" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I172" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J172" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K172" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L172" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M172" t="str">
+        <x:v>用户模式效果图参考；内置imagegen独立PNG；不使用图集</x:v>
+      </x:c>
+      <x:c r="N172" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173" t="n">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="B173" t="str">
+        <x:v>topic_express</x:v>
+      </x:c>
+      <x:c r="C173" t="str">
+        <x:v>ui/windows/modes/topic_express/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D173" t="str">
+        <x:v>ui/windows/modes</x:v>
+      </x:c>
+      <x:c r="E173" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F173" t="n">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="G173" t="n">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="H173" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I173" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J173" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K173" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L173" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M173" t="str">
+        <x:v>用户模式效果图参考；内置imagegen独立PNG；不使用图集</x:v>
+      </x:c>
+      <x:c r="N173" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174" t="n">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="B174" t="str">
+        <x:v>topic_warehouse</x:v>
+      </x:c>
+      <x:c r="C174" t="str">
+        <x:v>ui/windows/modes/topic_warehouse/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D174" t="str">
+        <x:v>ui/windows/modes</x:v>
+      </x:c>
+      <x:c r="E174" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F174" t="n">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="G174" t="n">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="H174" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I174" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J174" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K174" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L174" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M174" t="str">
+        <x:v>用户模式效果图参考；内置imagegen独立PNG；不使用图集</x:v>
+      </x:c>
+      <x:c r="N174" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="B175" t="str">
+        <x:v>topic_coins</x:v>
+      </x:c>
+      <x:c r="C175" t="str">
+        <x:v>ui/windows/modes/topic_coins/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D175" t="str">
+        <x:v>ui/windows/modes</x:v>
+      </x:c>
+      <x:c r="E175" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F175" t="n">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="G175" t="n">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="H175" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I175" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J175" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K175" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L175" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M175" t="str">
+        <x:v>用户模式效果图参考；内置imagegen独立PNG；不使用图集</x:v>
+      </x:c>
+      <x:c r="N175" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176" t="n">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="B176" t="str">
+        <x:v>topic_mini</x:v>
+      </x:c>
+      <x:c r="C176" t="str">
+        <x:v>ui/windows/modes/topic_mini/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D176" t="str">
+        <x:v>ui/windows/modes</x:v>
+      </x:c>
+      <x:c r="E176" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F176" t="n">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="G176" t="n">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="H176" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I176" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J176" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K176" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L176" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M176" t="str">
+        <x:v>用户模式效果图参考；内置imagegen独立PNG；不使用图集</x:v>
+      </x:c>
+      <x:c r="N176" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="B177" t="str">
+        <x:v>topic_midnight</x:v>
+      </x:c>
+      <x:c r="C177" t="str">
+        <x:v>ui/windows/modes/topic_midnight/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D177" t="str">
+        <x:v>ui/windows/modes</x:v>
+      </x:c>
+      <x:c r="E177" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F177" t="n">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="G177" t="n">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="H177" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I177" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J177" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K177" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L177" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M177" t="str">
+        <x:v>用户模式效果图参考；内置imagegen独立PNG；不使用图集</x:v>
+      </x:c>
+      <x:c r="N177" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" t="n">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="B178" t="str">
+        <x:v>shop_goods_card_v2</x:v>
+      </x:c>
+      <x:c r="C178" t="str">
+        <x:v>ui/windows/shop/reference/goods_card/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D178" t="str">
+        <x:v>ui/windows/shop/reference</x:v>
+      </x:c>
+      <x:c r="E178" t="str">
+        <x:v>sliced</x:v>
+      </x:c>
+      <x:c r="F178" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="G178" t="n">
+        <x:v>640</x:v>
+      </x:c>
+      <x:c r="H178" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="I178" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="J178" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="K178" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="L178" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M178" t="str">
+        <x:v>独立淡绿圆角竖卡；内部不透明；九宫保持圆角</x:v>
+      </x:c>
+      <x:c r="N178" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/VisualSkin.xlsx
+++ b/design/tables/VisualSkin.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisualSkin" sheetId="1" r:id="Rb581e969d7a74b8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisualSkin" sheetId="1" r:id="Rbd3aa7d5374c4683"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8111,6 +8111,798 @@
         <x:v>stretch</x:v>
       </x:c>
     </x:row>
+    <x:row r="179">
+      <x:c r="A179" s="3" t="n">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="B179" s="3" t="str">
+        <x:v>topic_freezer</x:v>
+      </x:c>
+      <x:c r="C179" s="3" t="str">
+        <x:v>gameplay/enemies/characters/enemy_freezer/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D179" s="3" t="str">
+        <x:v>gameplay/enemies</x:v>
+      </x:c>
+      <x:c r="E179" s="3" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F179" s="3" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G179" s="3" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H179" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I179" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J179" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K179" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L179" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M179" s="3" t="str">
+        <x:v>独立新角色PNG复用于专题缩略图，保持比例</x:v>
+      </x:c>
+      <x:c r="N179" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180" s="3" t="n">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="B180" s="3" t="str">
+        <x:v>topic_gifts</x:v>
+      </x:c>
+      <x:c r="C180" s="3" t="str">
+        <x:v>gameplay/enemies/characters/enemy_popcorn/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D180" s="3" t="str">
+        <x:v>gameplay/enemies</x:v>
+      </x:c>
+      <x:c r="E180" s="3" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F180" s="3" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G180" s="3" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H180" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I180" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J180" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K180" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L180" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M180" s="3" t="str">
+        <x:v>独立新角色PNG复用于专题缩略图，保持比例</x:v>
+      </x:c>
+      <x:c r="N180" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181" s="3" t="n">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="B181" s="3" t="str">
+        <x:v>topic_storm</x:v>
+      </x:c>
+      <x:c r="C181" s="3" t="str">
+        <x:v>gameplay/enemies/characters/enemy_frostdonut/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D181" s="3" t="str">
+        <x:v>gameplay/enemies</x:v>
+      </x:c>
+      <x:c r="E181" s="3" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F181" s="3" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G181" s="3" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H181" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I181" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J181" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K181" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L181" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M181" s="3" t="str">
+        <x:v>独立新角色PNG复用于专题缩略图，保持比例</x:v>
+      </x:c>
+      <x:c r="N181" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" s="3" t="n">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="B182" s="3" t="str">
+        <x:v>topic_dawn</x:v>
+      </x:c>
+      <x:c r="C182" s="3" t="str">
+        <x:v>gameplay/enemies/characters/enemy_vending/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D182" s="3" t="str">
+        <x:v>gameplay/enemies</x:v>
+      </x:c>
+      <x:c r="E182" s="3" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F182" s="3" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G182" s="3" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H182" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I182" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J182" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K182" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L182" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M182" s="3" t="str">
+        <x:v>独立新角色PNG复用于专题缩略图，保持比例</x:v>
+      </x:c>
+      <x:c r="N182" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" s="3" t="n">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="B183" s="3" t="str">
+        <x:v>map_27</x:v>
+      </x:c>
+      <x:c r="C183" s="3" t="str">
+        <x:v>gameplay/maps/map_27/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D183" s="3" t="str">
+        <x:v>gameplay/maps</x:v>
+      </x:c>
+      <x:c r="E183" s="3" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F183" s="3" t="n">
+        <x:v>780</x:v>
+      </x:c>
+      <x:c r="G183" s="3" t="n">
+        <x:v>1388</x:v>
+      </x:c>
+      <x:c r="H183" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I183" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J183" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K183" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L183" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M183" s="3" t="str">
+        <x:v>第27关，路线来自原始地图表</x:v>
+      </x:c>
+      <x:c r="N183" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" s="3" t="n">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B184" s="3" t="str">
+        <x:v>map_28</x:v>
+      </x:c>
+      <x:c r="C184" s="3" t="str">
+        <x:v>gameplay/maps/map_28/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D184" s="3" t="str">
+        <x:v>gameplay/maps</x:v>
+      </x:c>
+      <x:c r="E184" s="3" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F184" s="3" t="n">
+        <x:v>780</x:v>
+      </x:c>
+      <x:c r="G184" s="3" t="n">
+        <x:v>1388</x:v>
+      </x:c>
+      <x:c r="H184" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I184" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J184" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K184" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L184" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M184" s="3" t="str">
+        <x:v>第28关，路线来自原始地图表</x:v>
+      </x:c>
+      <x:c r="N184" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" s="3" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="B185" s="3" t="str">
+        <x:v>map_29</x:v>
+      </x:c>
+      <x:c r="C185" s="3" t="str">
+        <x:v>gameplay/maps/map_29/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D185" s="3" t="str">
+        <x:v>gameplay/maps</x:v>
+      </x:c>
+      <x:c r="E185" s="3" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F185" s="3" t="n">
+        <x:v>780</x:v>
+      </x:c>
+      <x:c r="G185" s="3" t="n">
+        <x:v>1388</x:v>
+      </x:c>
+      <x:c r="H185" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I185" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J185" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K185" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L185" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M185" s="3" t="str">
+        <x:v>第29关，路线来自原始地图表</x:v>
+      </x:c>
+      <x:c r="N185" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186" s="3" t="n">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="B186" s="3" t="str">
+        <x:v>map_30</x:v>
+      </x:c>
+      <x:c r="C186" s="3" t="str">
+        <x:v>gameplay/maps/map_30/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D186" s="3" t="str">
+        <x:v>gameplay/maps</x:v>
+      </x:c>
+      <x:c r="E186" s="3" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F186" s="3" t="n">
+        <x:v>780</x:v>
+      </x:c>
+      <x:c r="G186" s="3" t="n">
+        <x:v>1388</x:v>
+      </x:c>
+      <x:c r="H186" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I186" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J186" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K186" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L186" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M186" s="3" t="str">
+        <x:v>第30关，路线来自原始地图表</x:v>
+      </x:c>
+      <x:c r="N186" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" s="3" t="n">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="B187" s="3" t="str">
+        <x:v>map_31</x:v>
+      </x:c>
+      <x:c r="C187" s="3" t="str">
+        <x:v>gameplay/maps/map_31/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D187" s="3" t="str">
+        <x:v>gameplay/maps</x:v>
+      </x:c>
+      <x:c r="E187" s="3" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F187" s="3" t="n">
+        <x:v>780</x:v>
+      </x:c>
+      <x:c r="G187" s="3" t="n">
+        <x:v>1388</x:v>
+      </x:c>
+      <x:c r="H187" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I187" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J187" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K187" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L187" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M187" s="3" t="str">
+        <x:v>第31关，路线来自原始地图表</x:v>
+      </x:c>
+      <x:c r="N187" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" s="3" t="n">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="B188" s="3" t="str">
+        <x:v>map_32</x:v>
+      </x:c>
+      <x:c r="C188" s="3" t="str">
+        <x:v>gameplay/maps/map_32/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D188" s="3" t="str">
+        <x:v>gameplay/maps</x:v>
+      </x:c>
+      <x:c r="E188" s="3" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F188" s="3" t="n">
+        <x:v>780</x:v>
+      </x:c>
+      <x:c r="G188" s="3" t="n">
+        <x:v>1388</x:v>
+      </x:c>
+      <x:c r="H188" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I188" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J188" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K188" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L188" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M188" s="3" t="str">
+        <x:v>第32关，路线来自原始地图表</x:v>
+      </x:c>
+      <x:c r="N188" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" s="3" t="n">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="B189" s="3" t="str">
+        <x:v>map_33</x:v>
+      </x:c>
+      <x:c r="C189" s="3" t="str">
+        <x:v>gameplay/maps/map_33/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D189" s="3" t="str">
+        <x:v>gameplay/maps</x:v>
+      </x:c>
+      <x:c r="E189" s="3" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F189" s="3" t="n">
+        <x:v>780</x:v>
+      </x:c>
+      <x:c r="G189" s="3" t="n">
+        <x:v>1388</x:v>
+      </x:c>
+      <x:c r="H189" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I189" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J189" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K189" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L189" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M189" s="3" t="str">
+        <x:v>第33关，路线来自原始地图表</x:v>
+      </x:c>
+      <x:c r="N189" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" s="3" t="n">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="B190" s="3" t="str">
+        <x:v>map_34</x:v>
+      </x:c>
+      <x:c r="C190" s="3" t="str">
+        <x:v>gameplay/maps/map_34/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D190" s="3" t="str">
+        <x:v>gameplay/maps</x:v>
+      </x:c>
+      <x:c r="E190" s="3" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F190" s="3" t="n">
+        <x:v>780</x:v>
+      </x:c>
+      <x:c r="G190" s="3" t="n">
+        <x:v>1388</x:v>
+      </x:c>
+      <x:c r="H190" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I190" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J190" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K190" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L190" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M190" s="3" t="str">
+        <x:v>第34关，路线来自原始地图表</x:v>
+      </x:c>
+      <x:c r="N190" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A191" s="3" t="n">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="B191" s="3" t="str">
+        <x:v>map_35</x:v>
+      </x:c>
+      <x:c r="C191" s="3" t="str">
+        <x:v>gameplay/maps/map_35/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D191" s="3" t="str">
+        <x:v>gameplay/maps</x:v>
+      </x:c>
+      <x:c r="E191" s="3" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F191" s="3" t="n">
+        <x:v>780</x:v>
+      </x:c>
+      <x:c r="G191" s="3" t="n">
+        <x:v>1388</x:v>
+      </x:c>
+      <x:c r="H191" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I191" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J191" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K191" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L191" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M191" s="3" t="str">
+        <x:v>第35关，路线来自原始地图表</x:v>
+      </x:c>
+      <x:c r="N191" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" s="3" t="n">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="B192" s="3" t="str">
+        <x:v>map_36</x:v>
+      </x:c>
+      <x:c r="C192" s="3" t="str">
+        <x:v>gameplay/maps/map_36/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D192" s="3" t="str">
+        <x:v>gameplay/maps</x:v>
+      </x:c>
+      <x:c r="E192" s="3" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F192" s="3" t="n">
+        <x:v>780</x:v>
+      </x:c>
+      <x:c r="G192" s="3" t="n">
+        <x:v>1388</x:v>
+      </x:c>
+      <x:c r="H192" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I192" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J192" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K192" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L192" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M192" s="3" t="str">
+        <x:v>第36关，路线来自原始地图表</x:v>
+      </x:c>
+      <x:c r="N192" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" s="3" t="n">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="B193" s="3" t="str">
+        <x:v>map_37</x:v>
+      </x:c>
+      <x:c r="C193" s="3" t="str">
+        <x:v>gameplay/maps/map_37/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D193" s="3" t="str">
+        <x:v>gameplay/maps</x:v>
+      </x:c>
+      <x:c r="E193" s="3" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F193" s="3" t="n">
+        <x:v>780</x:v>
+      </x:c>
+      <x:c r="G193" s="3" t="n">
+        <x:v>1388</x:v>
+      </x:c>
+      <x:c r="H193" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I193" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J193" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K193" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L193" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M193" s="3" t="str">
+        <x:v>第37关，路线来自原始地图表</x:v>
+      </x:c>
+      <x:c r="N193" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" s="3" t="n">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="B194" s="3" t="str">
+        <x:v>map_38</x:v>
+      </x:c>
+      <x:c r="C194" s="3" t="str">
+        <x:v>gameplay/maps/map_38/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D194" s="3" t="str">
+        <x:v>gameplay/maps</x:v>
+      </x:c>
+      <x:c r="E194" s="3" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F194" s="3" t="n">
+        <x:v>780</x:v>
+      </x:c>
+      <x:c r="G194" s="3" t="n">
+        <x:v>1388</x:v>
+      </x:c>
+      <x:c r="H194" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I194" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J194" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K194" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L194" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M194" s="3" t="str">
+        <x:v>第38关，路线来自原始地图表</x:v>
+      </x:c>
+      <x:c r="N194" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" s="3" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="B195" s="3" t="str">
+        <x:v>map_39</x:v>
+      </x:c>
+      <x:c r="C195" s="3" t="str">
+        <x:v>gameplay/maps/map_39/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D195" s="3" t="str">
+        <x:v>gameplay/maps</x:v>
+      </x:c>
+      <x:c r="E195" s="3" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F195" s="3" t="n">
+        <x:v>780</x:v>
+      </x:c>
+      <x:c r="G195" s="3" t="n">
+        <x:v>1388</x:v>
+      </x:c>
+      <x:c r="H195" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I195" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J195" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K195" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L195" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M195" s="3" t="str">
+        <x:v>第39关，路线来自原始地图表</x:v>
+      </x:c>
+      <x:c r="N195" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196" s="3" t="n">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="B196" s="3" t="str">
+        <x:v>map_40</x:v>
+      </x:c>
+      <x:c r="C196" s="3" t="str">
+        <x:v>gameplay/maps/map_40/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D196" s="3" t="str">
+        <x:v>gameplay/maps</x:v>
+      </x:c>
+      <x:c r="E196" s="3" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F196" s="3" t="n">
+        <x:v>780</x:v>
+      </x:c>
+      <x:c r="G196" s="3" t="n">
+        <x:v>1388</x:v>
+      </x:c>
+      <x:c r="H196" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I196" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J196" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K196" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L196" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M196" s="3" t="str">
+        <x:v>第40关，路线来自原始地图表</x:v>
+      </x:c>
+      <x:c r="N196" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/VisualSkin.xlsx
+++ b/design/tables/VisualSkin.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisualSkin" sheetId="1" r:id="Rbd3aa7d5374c4683"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisualSkin" sheetId="1" r:id="Rf189b1b1e13e4734"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8903,6 +8903,138 @@
         <x:v>stretch</x:v>
       </x:c>
     </x:row>
+    <x:row r="197">
+      <x:c r="A197" s="3" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="B197" s="3" t="str">
+        <x:v>tech_banner</x:v>
+      </x:c>
+      <x:c r="C197" s="3" t="str">
+        <x:v>ui/windows/technology/tech_banner/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D197" s="3" t="str">
+        <x:v>ui/windows/technology</x:v>
+      </x:c>
+      <x:c r="E197" s="3" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F197" s="3" t="n">
+        <x:v>640</x:v>
+      </x:c>
+      <x:c r="G197" s="3" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="H197" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I197" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J197" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K197" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L197" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M197" s="3" t="str">
+        <x:v>内置image_gen独立制作；科技重设计</x:v>
+      </x:c>
+      <x:c r="N197" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198" s="3" t="n">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="B198" s="3" t="str">
+        <x:v>tech_card</x:v>
+      </x:c>
+      <x:c r="C198" s="3" t="str">
+        <x:v>ui/windows/technology/tech_card/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D198" s="3" t="str">
+        <x:v>ui/windows/technology</x:v>
+      </x:c>
+      <x:c r="E198" s="3" t="str">
+        <x:v>sliced</x:v>
+      </x:c>
+      <x:c r="F198" s="3" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="G198" s="3" t="n">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="H198" s="3" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="I198" s="3" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="J198" s="3" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K198" s="3" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="L198" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M198" s="3" t="str">
+        <x:v>内置image_gen独立制作；科技重设计</x:v>
+      </x:c>
+      <x:c r="N198" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199" s="3" t="n">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="B199" s="3" t="str">
+        <x:v>tech_badge</x:v>
+      </x:c>
+      <x:c r="C199" s="3" t="str">
+        <x:v>ui/windows/technology/tech_badge/spriteFrame</x:v>
+      </x:c>
+      <x:c r="D199" s="3" t="str">
+        <x:v>ui/windows/technology</x:v>
+      </x:c>
+      <x:c r="E199" s="3" t="str">
+        <x:v>simple</x:v>
+      </x:c>
+      <x:c r="F199" s="3" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G199" s="3" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H199" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I199" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J199" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K199" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L199" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M199" s="3" t="str">
+        <x:v>内置image_gen独立制作；科技重设计</x:v>
+      </x:c>
+      <x:c r="N199" t="str">
+        <x:v>contain</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/VisualSkin.xlsx
+++ b/design/tables/VisualSkin.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisualSkin" sheetId="1" r:id="Rf189b1b1e13e4734"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VisualSkin" sheetId="1" r:id="R99c305fd546648af"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -27,8 +27,18 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -40,6 +50,11 @@
         <x:fgColor rgb="FF264C42"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF315B4A"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -47,7 +62,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="9">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -62,6 +77,9 @@
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -277,6 +295,11 @@
     <x:col min="11" max="11" width="15" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="46" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="18" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="18" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="18" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
@@ -322,6 +345,18 @@
       <x:c r="N1" t="str">
         <x:v>适配方式</x:v>
       </x:c>
+      <x:c r="O1" s="8" t="str">
+        <x:v>可见左</x:v>
+      </x:c>
+      <x:c r="P1" s="8" t="str">
+        <x:v>可见上</x:v>
+      </x:c>
+      <x:c r="Q1" s="8" t="str">
+        <x:v>可见宽</x:v>
+      </x:c>
+      <x:c r="R1" s="8" t="str">
+        <x:v>可见高</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="5" t="str">
@@ -366,6 +401,18 @@
       <x:c r="N2" t="str">
         <x:v>client</x:v>
       </x:c>
+      <x:c r="O2" s="8" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="P2" s="8" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="Q2" s="8" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="R2" s="8" t="str">
+        <x:v>client</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="36" customHeight="1">
       <x:c r="A3" s="5" t="str">
@@ -410,6 +457,18 @@
       <x:c r="N3" t="str">
         <x:v>string</x:v>
       </x:c>
+      <x:c r="O3" s="8" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="P3" s="8" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="Q3" s="8" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="R3" s="8" t="str">
+        <x:v>int</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="36" customHeight="1">
       <x:c r="A4" s="5" t="str">
@@ -454,6 +513,18 @@
       <x:c r="N4" t="str">
         <x:v>适配方式</x:v>
       </x:c>
+      <x:c r="O4" s="8" t="str">
+        <x:v>可见左</x:v>
+      </x:c>
+      <x:c r="P4" s="8" t="str">
+        <x:v>可见上</x:v>
+      </x:c>
+      <x:c r="Q4" s="8" t="str">
+        <x:v>可见宽</x:v>
+      </x:c>
+      <x:c r="R4" s="8" t="str">
+        <x:v>可见高</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="36" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -498,6 +569,18 @@
       <x:c r="N5" t="str">
         <x:v>resizeMode</x:v>
       </x:c>
+      <x:c r="O5" s="8" t="str">
+        <x:v>contentX</x:v>
+      </x:c>
+      <x:c r="P5" s="8" t="str">
+        <x:v>contentY</x:v>
+      </x:c>
+      <x:c r="Q5" s="8" t="str">
+        <x:v>contentWidth</x:v>
+      </x:c>
+      <x:c r="R5" s="8" t="str">
+        <x:v>contentHeight</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="28" customHeight="1">
       <x:c r="A6" s="3" t="n">
@@ -542,6 +625,18 @@
       <x:c r="N6" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O6" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P6" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q6" s="6" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="R6" s="6" t="n">
+        <x:v>126</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="28" customHeight="1">
       <x:c r="A7" s="3" t="n">
@@ -586,6 +681,18 @@
       <x:c r="N7" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O7" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P7" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q7" s="6" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="R7" s="6" t="n">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="28" customHeight="1">
       <x:c r="A8" s="3" t="n">
@@ -630,6 +737,18 @@
       <x:c r="N8" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O8" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P8" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q8" s="6" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="R8" s="6" t="n">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="28" customHeight="1">
       <x:c r="A9" s="3" t="n">
@@ -674,6 +793,18 @@
       <x:c r="N9" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O9" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P9" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q9" s="6" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="R9" s="6" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="28" customHeight="1">
       <x:c r="A10" s="3" t="n">
@@ -718,6 +849,18 @@
       <x:c r="N10" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O10" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P10" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q10" s="6" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="R10" s="6" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="28" customHeight="1">
       <x:c r="A11" s="3" t="n">
@@ -762,6 +905,18 @@
       <x:c r="N11" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O11" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P11" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q11" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="R11" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="28" customHeight="1">
       <x:c r="A12" s="3" t="n">
@@ -806,6 +961,18 @@
       <x:c r="N12" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O12" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P12" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q12" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="R12" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="28" customHeight="1">
       <x:c r="A13" s="3" t="n">
@@ -850,6 +1017,18 @@
       <x:c r="N13" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O13" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P13" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q13" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="R13" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="28" customHeight="1">
       <x:c r="A14" s="3" t="n">
@@ -894,6 +1073,18 @@
       <x:c r="N14" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O14" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P14" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q14" s="6" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="R14" s="6" t="n">
+        <x:v>12</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="28" customHeight="1">
       <x:c r="A15" s="3" t="n">
@@ -938,6 +1129,18 @@
       <x:c r="N15" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O15" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P15" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q15" s="6" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="R15" s="6" t="n">
+        <x:v>14</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="28" customHeight="1">
       <x:c r="A16" s="3" t="n">
@@ -982,6 +1185,18 @@
       <x:c r="N16" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O16" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P16" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q16" s="6" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="R16" s="6" t="n">
+        <x:v>18</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="28" customHeight="1">
       <x:c r="A17" s="3" t="n">
@@ -1026,6 +1241,18 @@
       <x:c r="N17" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O17" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P17" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q17" s="6" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="R17" s="6" t="n">
+        <x:v>22</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="28" customHeight="1">
       <x:c r="A18" s="3" t="n">
@@ -1070,6 +1297,18 @@
       <x:c r="N18" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O18" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P18" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q18" s="6" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="R18" s="6" t="n">
+        <x:v>28</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="28" customHeight="1">
       <x:c r="A19" s="3" t="n">
@@ -1114,6 +1353,18 @@
       <x:c r="N19" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O19" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P19" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q19" s="6" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R19" s="6" t="n">
+        <x:v>30</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="28" customHeight="1">
       <x:c r="A20" s="3" t="n">
@@ -1158,6 +1409,18 @@
       <x:c r="N20" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O20" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P20" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q20" s="6" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="R20" s="6" t="n">
+        <x:v>34</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="28" customHeight="1">
       <x:c r="A21" s="3" t="n">
@@ -1202,6 +1465,18 @@
       <x:c r="N21" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O21" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P21" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q21" s="6" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="R21" s="6" t="n">
+        <x:v>42</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="28" customHeight="1">
       <x:c r="A22" s="3" t="n">
@@ -1246,6 +1521,18 @@
       <x:c r="N22" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O22" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P22" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q22" s="6" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="R22" s="6" t="n">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="28" customHeight="1">
       <x:c r="A23" s="3" t="n">
@@ -1290,6 +1577,18 @@
       <x:c r="N23" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O23" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P23" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q23" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="R23" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="28" customHeight="1">
       <x:c r="A24" s="3" t="n">
@@ -1334,6 +1633,18 @@
       <x:c r="N24" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O24" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P24" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q24" s="6" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="R24" s="6" t="n">
+        <x:v>36</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="28" customHeight="1">
       <x:c r="A25" s="3" t="n">
@@ -1378,6 +1689,18 @@
       <x:c r="N25" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O25" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P25" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q25" s="6" t="n">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="R25" s="6" t="n">
+        <x:v>254</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="28" customHeight="1">
       <x:c r="A26" s="3" t="n">
@@ -1422,6 +1745,18 @@
       <x:c r="N26" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O26" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P26" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q26" s="6" t="n">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="R26" s="6" t="n">
+        <x:v>254</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="28" customHeight="1">
       <x:c r="A27" s="3" t="n">
@@ -1466,6 +1801,18 @@
       <x:c r="N27" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O27" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P27" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q27" s="6" t="n">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="R27" s="6" t="n">
+        <x:v>254</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="28" customHeight="1">
       <x:c r="A28" s="3" t="n">
@@ -1510,6 +1857,18 @@
       <x:c r="N28" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O28" s="6" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="P28" s="6" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="Q28" s="6" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="R28" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="28" customHeight="1">
       <x:c r="A29" s="3" t="n">
@@ -1554,6 +1913,18 @@
       <x:c r="N29" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O29" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P29" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q29" s="6" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="R29" s="6" t="n">
+        <x:v>32</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="28" customHeight="1">
       <x:c r="A30" s="3" t="n">
@@ -1598,6 +1969,18 @@
       <x:c r="N30" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O30" s="6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="P30" s="6" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="Q30" s="6" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="R30" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="28" customHeight="1">
       <x:c r="A31" s="3" t="n">
@@ -1642,6 +2025,18 @@
       <x:c r="N31" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O31" s="6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="P31" s="6" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="Q31" s="6" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="R31" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="28" customHeight="1">
       <x:c r="A32" s="3" t="n">
@@ -1686,6 +2081,18 @@
       <x:c r="N32" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O32" s="6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="P32" s="6" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="Q32" s="6" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="R32" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="28" customHeight="1">
       <x:c r="A33" s="3" t="n">
@@ -1730,6 +2137,18 @@
       <x:c r="N33" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O33" s="6" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="P33" s="6" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q33" s="6" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="R33" s="6" t="n">
+        <x:v>35</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="28" customHeight="1">
       <x:c r="A34" s="3" t="n">
@@ -1774,6 +2193,18 @@
       <x:c r="N34" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O34" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P34" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q34" s="6" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="R34" s="6" t="n">
+        <x:v>38</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="28" customHeight="1">
       <x:c r="A35" s="3" t="n">
@@ -1818,6 +2249,18 @@
       <x:c r="N35" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O35" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P35" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q35" s="6" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="R35" s="6" t="n">
+        <x:v>32</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="28" customHeight="1">
       <x:c r="A36" s="3" t="n">
@@ -1862,6 +2305,18 @@
       <x:c r="N36" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O36" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P36" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q36" s="6" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="R36" s="6" t="n">
+        <x:v>14</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="28" customHeight="1">
       <x:c r="A37" s="3" t="n">
@@ -1906,6 +2361,18 @@
       <x:c r="N37" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O37" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P37" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q37" s="6" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R37" s="6" t="n">
+        <x:v>30</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="28" customHeight="1">
       <x:c r="A38" s="3" t="n">
@@ -1950,6 +2417,18 @@
       <x:c r="N38" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O38" s="6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="P38" s="6" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="Q38" s="6" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="R38" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="28" customHeight="1">
       <x:c r="A39" s="3" t="n">
@@ -1994,6 +2473,18 @@
       <x:c r="N39" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O39" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P39" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q39" s="6" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="R39" s="6" t="n">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="28" customHeight="1">
       <x:c r="A40" s="3" t="n">
@@ -2038,6 +2529,18 @@
       <x:c r="N40" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O40" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P40" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q40" s="6" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="R40" s="6" t="n">
+        <x:v>36</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="28" customHeight="1">
       <x:c r="A41" s="3" t="n">
@@ -2082,6 +2585,18 @@
       <x:c r="N41" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O41" s="6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="P41" s="6" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="Q41" s="6" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="R41" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="28" customHeight="1">
       <x:c r="A42" s="3" t="n">
@@ -2126,6 +2641,18 @@
       <x:c r="N42" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O42" s="6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="P42" s="6" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="Q42" s="6" t="n">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="R42" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="28" customHeight="1">
       <x:c r="A43" s="3" t="n">
@@ -2170,6 +2697,18 @@
       <x:c r="N43" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O43" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P43" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q43" s="6" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="R43" s="6" t="n">
+        <x:v>82</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="28" customHeight="1">
       <x:c r="A44" s="3" t="n">
@@ -2214,6 +2753,18 @@
       <x:c r="N44" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O44" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="P44" s="6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="Q44" s="6" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="R44" s="6" t="n">
+        <x:v>32</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="28" customHeight="1">
       <x:c r="A45" s="3" t="n">
@@ -2258,6 +2809,18 @@
       <x:c r="N45" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O45" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P45" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q45" s="6" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="R45" s="6" t="n">
+        <x:v>52</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="28" customHeight="1">
       <x:c r="A46" s="3" t="n">
@@ -2302,6 +2865,18 @@
       <x:c r="N46" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O46" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P46" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q46" s="6" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="R46" s="6" t="n">
+        <x:v>26</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="28" customHeight="1">
       <x:c r="A47" s="3" t="n">
@@ -2346,6 +2921,18 @@
       <x:c r="N47" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O47" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P47" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q47" s="6" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="R47" s="6" t="n">
+        <x:v>50</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="28" customHeight="1">
       <x:c r="A48" s="3" t="n">
@@ -2390,6 +2977,18 @@
       <x:c r="N48" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O48" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P48" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q48" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="R48" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="28" customHeight="1">
       <x:c r="A49" s="3" t="n">
@@ -2434,6 +3033,18 @@
       <x:c r="N49" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O49" s="6" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="P49" s="6" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="Q49" s="6" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="R49" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="28" customHeight="1">
       <x:c r="A50" s="3" t="n">
@@ -2478,6 +3089,18 @@
       <x:c r="N50" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O50" s="6" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="P50" s="6" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="Q50" s="6" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="R50" s="6" t="n">
+        <x:v>16</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="28" customHeight="1">
       <x:c r="A51" s="3" t="n">
@@ -2522,6 +3145,18 @@
       <x:c r="N51" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O51" s="6" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="P51" s="6" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="Q51" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="R51" s="6" t="n">
+        <x:v>18</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="28" customHeight="1">
       <x:c r="A52" s="3" t="n">
@@ -2566,6 +3201,18 @@
       <x:c r="N52" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O52" s="6" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="P52" s="6" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="Q52" s="6" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="R52" s="6" t="n">
+        <x:v>16</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="28" customHeight="1">
       <x:c r="A53" s="3" t="n">
@@ -2610,6 +3257,18 @@
       <x:c r="N53" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O53" s="6" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="P53" s="6" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="Q53" s="6" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="R53" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="28" customHeight="1">
       <x:c r="A54" s="3" t="n">
@@ -2654,6 +3313,18 @@
       <x:c r="N54" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O54" s="6" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="P54" s="6" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="Q54" s="6" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="R54" s="6" t="n">
+        <x:v>16</x:v>
+      </x:c>
     </x:row>
     <x:row r="55" ht="28" customHeight="1">
       <x:c r="A55" s="3" t="n">
@@ -2698,6 +3369,18 @@
       <x:c r="N55" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O55" s="6" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="P55" s="6" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="Q55" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="R55" s="6" t="n">
+        <x:v>18</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="28" customHeight="1">
       <x:c r="A56" s="3" t="n">
@@ -2742,6 +3425,18 @@
       <x:c r="N56" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O56" s="6" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="P56" s="6" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="Q56" s="6" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="R56" s="6" t="n">
+        <x:v>16</x:v>
+      </x:c>
     </x:row>
     <x:row r="57" ht="28" customHeight="1">
       <x:c r="A57" s="3" t="n">
@@ -2786,6 +3481,18 @@
       <x:c r="N57" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O57" s="6" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="P57" s="6" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="Q57" s="6" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="R57" s="6" t="n">
+        <x:v>40</x:v>
+      </x:c>
     </x:row>
     <x:row r="58" ht="28" customHeight="1">
       <x:c r="A58" s="3" t="n">
@@ -2830,6 +3537,18 @@
       <x:c r="N58" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O58" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P58" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q58" s="6" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="R58" s="6" t="n">
+        <x:v>52</x:v>
+      </x:c>
     </x:row>
     <x:row r="59" ht="28" customHeight="1">
       <x:c r="A59" s="3" t="n">
@@ -2874,6 +3593,18 @@
       <x:c r="N59" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O59" s="6" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="P59" s="6" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="Q59" s="6" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="R59" s="6" t="n">
+        <x:v>40</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" ht="28" customHeight="1">
       <x:c r="A60" s="3" t="n">
@@ -2918,6 +3649,18 @@
       <x:c r="N60" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O60" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P60" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q60" s="6" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="R60" s="6" t="n">
+        <x:v>12</x:v>
+      </x:c>
     </x:row>
     <x:row r="61" ht="28" customHeight="1">
       <x:c r="A61" s="3" t="n">
@@ -2962,6 +3705,18 @@
       <x:c r="N61" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O61" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P61" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q61" s="6" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="R61" s="6" t="n">
+        <x:v>54</x:v>
+      </x:c>
     </x:row>
     <x:row r="62" ht="28" customHeight="1">
       <x:c r="A62" s="3" t="n">
@@ -3006,6 +3761,18 @@
       <x:c r="N62" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O62" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P62" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q62" s="6" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="R62" s="6" t="n">
+        <x:v>56</x:v>
+      </x:c>
     </x:row>
     <x:row r="63" ht="28" customHeight="1">
       <x:c r="A63" s="3" t="n">
@@ -3050,6 +3817,18 @@
       <x:c r="N63" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O63" s="6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="P63" s="6" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="Q63" s="6" t="n">
+        <x:v>534</x:v>
+      </x:c>
+      <x:c r="R63" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="64" ht="28" customHeight="1">
       <x:c r="A64" s="3" t="n">
@@ -3094,6 +3873,18 @@
       <x:c r="N64" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O64" s="6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="P64" s="6" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="Q64" s="6" t="n">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="R64" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="65" ht="28" customHeight="1">
       <x:c r="A65" s="3" t="n">
@@ -3138,6 +3929,18 @@
       <x:c r="N65" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O65" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P65" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q65" s="6" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="R65" s="6" t="n">
+        <x:v>52</x:v>
+      </x:c>
     </x:row>
     <x:row r="66" ht="28" customHeight="1">
       <x:c r="A66" s="3" t="n">
@@ -3182,6 +3985,18 @@
       <x:c r="N66" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O66" s="6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="P66" s="6" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="Q66" s="6" t="n">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="R66" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="67" ht="28" customHeight="1">
       <x:c r="A67" s="3" t="n">
@@ -3226,6 +4041,18 @@
       <x:c r="N67" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O67" s="6" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="P67" s="6" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="Q67" s="6" t="n">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="R67" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="68" ht="28" customHeight="1">
       <x:c r="A68" s="3" t="n">
@@ -3270,6 +4097,18 @@
       <x:c r="N68" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O68" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P68" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q68" s="6" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="R68" s="6" t="n">
+        <x:v>48</x:v>
+      </x:c>
     </x:row>
     <x:row r="69" ht="28" customHeight="1">
       <x:c r="A69" s="3" t="n">
@@ -3314,6 +4153,18 @@
       <x:c r="N69" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O69" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P69" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q69" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R69" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="70" ht="28" customHeight="1">
       <x:c r="A70" s="3" t="n">
@@ -3358,6 +4209,18 @@
       <x:c r="N70" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O70" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P70" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q70" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R70" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="71" ht="28" customHeight="1">
       <x:c r="A71" s="3" t="n">
@@ -3402,6 +4265,18 @@
       <x:c r="N71" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O71" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P71" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q71" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R71" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="72" ht="28" customHeight="1">
       <x:c r="A72" s="3" t="n">
@@ -3446,6 +4321,18 @@
       <x:c r="N72" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O72" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P72" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q72" s="6" t="n">
+        <x:v>728</x:v>
+      </x:c>
+      <x:c r="R72" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="73" ht="28" customHeight="1">
       <x:c r="A73" s="3" t="n">
@@ -3490,6 +4377,18 @@
       <x:c r="N73" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O73" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P73" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q73" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R73" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="74" ht="28" customHeight="1">
       <x:c r="A74" s="3" t="n">
@@ -3534,6 +4433,18 @@
       <x:c r="N74" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O74" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P74" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q74" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R74" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="75" ht="28" customHeight="1">
       <x:c r="A75" s="3" t="n">
@@ -3578,6 +4489,18 @@
       <x:c r="N75" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O75" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P75" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q75" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R75" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="76" ht="28" customHeight="1">
       <x:c r="A76" s="3" t="n">
@@ -3622,6 +4545,18 @@
       <x:c r="N76" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O76" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P76" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q76" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R76" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="77" ht="28" customHeight="1">
       <x:c r="A77" s="3" t="n">
@@ -3666,6 +4601,18 @@
       <x:c r="N77" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O77" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P77" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q77" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R77" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="78" ht="28" customHeight="1">
       <x:c r="A78" s="3" t="n">
@@ -3710,6 +4657,18 @@
       <x:c r="N78" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O78" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P78" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q78" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R78" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="79" ht="28" customHeight="1">
       <x:c r="A79" s="3" t="n">
@@ -3754,6 +4713,18 @@
       <x:c r="N79" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O79" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P79" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q79" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R79" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="80" ht="28" customHeight="1">
       <x:c r="A80" s="3" t="n">
@@ -3798,6 +4769,18 @@
       <x:c r="N80" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O80" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P80" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q80" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R80" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="81" ht="28" customHeight="1">
       <x:c r="A81" s="3" t="n">
@@ -3842,6 +4825,18 @@
       <x:c r="N81" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O81" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P81" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q81" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R81" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="82" ht="28" customHeight="1">
       <x:c r="A82" s="3" t="n">
@@ -3886,6 +4881,18 @@
       <x:c r="N82" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O82" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P82" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q82" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R82" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="83" ht="28" customHeight="1">
       <x:c r="A83" s="3" t="n">
@@ -3930,6 +4937,18 @@
       <x:c r="N83" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O83" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P83" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q83" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R83" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="84" ht="28" customHeight="1">
       <x:c r="A84" s="3" t="n">
@@ -3974,6 +4993,18 @@
       <x:c r="N84" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O84" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P84" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q84" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R84" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="85" ht="28" customHeight="1">
       <x:c r="A85" s="3" t="n">
@@ -4018,6 +5049,18 @@
       <x:c r="N85" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O85" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P85" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q85" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R85" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="86" ht="28" customHeight="1">
       <x:c r="A86" s="3" t="n">
@@ -4062,6 +5105,18 @@
       <x:c r="N86" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O86" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P86" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q86" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R86" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="87" ht="28" customHeight="1">
       <x:c r="A87" s="3" t="n">
@@ -4106,6 +5161,18 @@
       <x:c r="N87" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O87" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P87" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q87" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R87" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="88" ht="28" customHeight="1">
       <x:c r="A88" s="3" t="n">
@@ -4150,6 +5217,18 @@
       <x:c r="N88" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O88" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P88" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q88" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R88" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="89" ht="28" customHeight="1">
       <x:c r="A89" s="3" t="n">
@@ -4194,6 +5273,18 @@
       <x:c r="N89" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O89" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P89" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q89" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R89" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" t="n">
@@ -4238,6 +5329,18 @@
       <x:c r="N90" t="str">
         <x:v>cover</x:v>
       </x:c>
+      <x:c r="O90" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P90" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q90" s="6" t="n">
+        <x:v>941</x:v>
+      </x:c>
+      <x:c r="R90" s="6" t="n">
+        <x:v>1672</x:v>
+      </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" t="n">
@@ -4282,6 +5385,18 @@
       <x:c r="N91" t="str">
         <x:v>cover</x:v>
       </x:c>
+      <x:c r="O91" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P91" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q91" s="6" t="n">
+        <x:v>941</x:v>
+      </x:c>
+      <x:c r="R91" s="6" t="n">
+        <x:v>1672</x:v>
+      </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" t="n">
@@ -4326,6 +5441,18 @@
       <x:c r="N92" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O92" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P92" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="Q92" s="6" t="n">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="R92" s="6" t="n">
+        <x:v>303</x:v>
+      </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" t="n">
@@ -4370,6 +5497,18 @@
       <x:c r="N93" t="str">
         <x:v>height</x:v>
       </x:c>
+      <x:c r="O93" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="P93" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Q93" s="6" t="n">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="R93" s="6" t="n">
+        <x:v>126</x:v>
+      </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" t="n">
@@ -4414,6 +5553,18 @@
       <x:c r="N94" t="str">
         <x:v>height</x:v>
       </x:c>
+      <x:c r="O94" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="P94" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Q94" s="6" t="n">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="R94" s="6" t="n">
+        <x:v>126</x:v>
+      </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" t="n">
@@ -4458,6 +5609,18 @@
       <x:c r="N95" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O95" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="P95" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q95" s="6" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="R95" s="6" t="n">
+        <x:v>236</x:v>
+      </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" t="n">
@@ -4502,6 +5665,18 @@
       <x:c r="N96" t="str">
         <x:v>height</x:v>
       </x:c>
+      <x:c r="O96" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="P96" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Q96" s="6" t="n">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="R96" s="6" t="n">
+        <x:v>117</x:v>
+      </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" t="n">
@@ -4546,6 +5721,18 @@
       <x:c r="N97" t="str">
         <x:v>height</x:v>
       </x:c>
+      <x:c r="O97" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P97" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Q97" s="6" t="n">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="R97" s="6" t="n">
+        <x:v>112</x:v>
+      </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" t="n">
@@ -4590,6 +5777,18 @@
       <x:c r="N98" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O98" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P98" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Q98" s="6" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="R98" s="6" t="n">
+        <x:v>239</x:v>
+      </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" t="n">
@@ -4634,6 +5833,18 @@
       <x:c r="N99" t="str">
         <x:v>height</x:v>
       </x:c>
+      <x:c r="O99" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="P99" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Q99" s="6" t="n">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="R99" s="6" t="n">
+        <x:v>74</x:v>
+      </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" t="n">
@@ -4678,6 +5889,18 @@
       <x:c r="N100" t="str">
         <x:v>height</x:v>
       </x:c>
+      <x:c r="O100" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="P100" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Q100" s="6" t="n">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="R100" s="6" t="n">
+        <x:v>107</x:v>
+      </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101" t="n">
@@ -4722,6 +5945,18 @@
       <x:c r="N101" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O101" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="P101" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Q101" s="6" t="n">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="R101" s="6" t="n">
+        <x:v>169</x:v>
+      </x:c>
     </x:row>
     <x:row r="102">
       <x:c r="A102" t="n">
@@ -4766,6 +6001,18 @@
       <x:c r="N102" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O102" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="P102" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Q102" s="6" t="n">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="R102" s="6" t="n">
+        <x:v>226</x:v>
+      </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" t="n">
@@ -4810,6 +6057,18 @@
       <x:c r="N103" t="str">
         <x:v>height</x:v>
       </x:c>
+      <x:c r="O103" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="P103" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Q103" s="6" t="n">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="R103" s="6" t="n">
+        <x:v>114</x:v>
+      </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" t="n">
@@ -4854,6 +6113,18 @@
       <x:c r="N104" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O104" s="6" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="P104" s="6" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q104" s="6" t="n">
+        <x:v>1025</x:v>
+      </x:c>
+      <x:c r="R104" s="6" t="n">
+        <x:v>1392</x:v>
+      </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" t="n">
@@ -4898,6 +6169,18 @@
       <x:c r="N105" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O105" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="P105" s="6" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q105" s="6" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="R105" s="6" t="n">
+        <x:v>210</x:v>
+      </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106" t="n">
@@ -4942,6 +6225,18 @@
       <x:c r="N106" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O106" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="P106" s="6" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="Q106" s="6" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="R106" s="6" t="n">
+        <x:v>202</x:v>
+      </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" t="n">
@@ -4986,6 +6281,18 @@
       <x:c r="N107" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O107" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="P107" s="6" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="Q107" s="6" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="R107" s="6" t="n">
+        <x:v>173</x:v>
+      </x:c>
     </x:row>
     <x:row r="108">
       <x:c r="A108" t="n">
@@ -5030,6 +6337,18 @@
       <x:c r="N108" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O108" s="6" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="P108" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Q108" s="6" t="n">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="R108" s="6" t="n">
+        <x:v>238</x:v>
+      </x:c>
     </x:row>
     <x:row r="109">
       <x:c r="A109" t="n">
@@ -5074,6 +6393,18 @@
       <x:c r="N109" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O109" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P109" s="6" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="Q109" s="6" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="R109" s="6" t="n">
+        <x:v>224</x:v>
+      </x:c>
     </x:row>
     <x:row r="110">
       <x:c r="A110" t="n">
@@ -5118,6 +6449,18 @@
       <x:c r="N110" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O110" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="P110" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Q110" s="6" t="n">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="R110" s="6" t="n">
+        <x:v>238</x:v>
+      </x:c>
     </x:row>
     <x:row r="111">
       <x:c r="A111" t="n">
@@ -5162,6 +6505,18 @@
       <x:c r="N111" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O111" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P111" s="6" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="Q111" s="6" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="R111" s="6" t="n">
+        <x:v>200</x:v>
+      </x:c>
     </x:row>
     <x:row r="112">
       <x:c r="A112" t="n">
@@ -5206,6 +6561,18 @@
       <x:c r="N112" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O112" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="P112" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Q112" s="6" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="R112" s="6" t="n">
+        <x:v>237</x:v>
+      </x:c>
     </x:row>
     <x:row r="113">
       <x:c r="A113" t="n">
@@ -5250,6 +6617,18 @@
       <x:c r="N113" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O113" s="6" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="P113" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Q113" s="6" t="n">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="R113" s="6" t="n">
+        <x:v>238</x:v>
+      </x:c>
     </x:row>
     <x:row r="114">
       <x:c r="A114" t="n">
@@ -5294,6 +6673,18 @@
       <x:c r="N114" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O114" s="6" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="P114" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Q114" s="6" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="R114" s="6" t="n">
+        <x:v>238</x:v>
+      </x:c>
     </x:row>
     <x:row r="115">
       <x:c r="A115" t="n">
@@ -5338,6 +6729,18 @@
       <x:c r="N115" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O115" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="P115" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Q115" s="6" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="R115" s="6" t="n">
+        <x:v>237</x:v>
+      </x:c>
     </x:row>
     <x:row r="116">
       <x:c r="A116" t="n">
@@ -5382,6 +6785,18 @@
       <x:c r="N116" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O116" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="P116" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Q116" s="6" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="R116" s="6" t="n">
+        <x:v>238</x:v>
+      </x:c>
     </x:row>
     <x:row r="117">
       <x:c r="A117" t="n">
@@ -5426,6 +6841,18 @@
       <x:c r="N117" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O117" s="6" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="P117" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="Q117" s="6" t="n">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="R117" s="6" t="n">
+        <x:v>240</x:v>
+      </x:c>
     </x:row>
     <x:row r="118">
       <x:c r="A118" t="n">
@@ -5470,6 +6897,18 @@
       <x:c r="N118" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O118" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P118" s="6" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="Q118" s="6" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="R118" s="6" t="n">
+        <x:v>224</x:v>
+      </x:c>
     </x:row>
     <x:row r="119">
       <x:c r="A119" t="n">
@@ -5514,6 +6953,18 @@
       <x:c r="N119" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O119" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="P119" s="6" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="Q119" s="6" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="R119" s="6" t="n">
+        <x:v>230</x:v>
+      </x:c>
     </x:row>
     <x:row r="120">
       <x:c r="A120" t="n">
@@ -5558,6 +7009,18 @@
       <x:c r="N120" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O120" s="6" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P120" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Q120" s="6" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="R120" s="6" t="n">
+        <x:v>238</x:v>
+      </x:c>
     </x:row>
     <x:row r="121">
       <x:c r="A121" t="n">
@@ -5602,6 +7065,18 @@
       <x:c r="N121" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O121" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="P121" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Q121" s="6" t="n">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="R121" s="6" t="n">
+        <x:v>238</x:v>
+      </x:c>
     </x:row>
     <x:row r="122">
       <x:c r="A122" t="n">
@@ -5646,6 +7121,18 @@
       <x:c r="N122" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O122" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="P122" s="6" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="Q122" s="6" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="R122" s="6" t="n">
+        <x:v>192</x:v>
+      </x:c>
     </x:row>
     <x:row r="123">
       <x:c r="A123" t="n">
@@ -5690,6 +7177,18 @@
       <x:c r="N123" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O123" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="P123" s="6" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="Q123" s="6" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="R123" s="6" t="n">
+        <x:v>142</x:v>
+      </x:c>
     </x:row>
     <x:row r="124">
       <x:c r="A124" t="n">
@@ -5734,6 +7233,18 @@
       <x:c r="N124" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O124" s="6" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="P124" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Q124" s="6" t="n">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="R124" s="6" t="n">
+        <x:v>238</x:v>
+      </x:c>
     </x:row>
     <x:row r="125">
       <x:c r="A125" t="n">
@@ -5778,6 +7289,18 @@
       <x:c r="N125" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O125" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="P125" s="6" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="Q125" s="6" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="R125" s="6" t="n">
+        <x:v>206</x:v>
+      </x:c>
     </x:row>
     <x:row r="126" ht="28" customHeight="1">
       <x:c r="A126" t="n">
@@ -5822,6 +7345,18 @@
       <x:c r="N126" t="str">
         <x:v>cover</x:v>
       </x:c>
+      <x:c r="O126" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P126" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q126" s="6" t="n">
+        <x:v>1254</x:v>
+      </x:c>
+      <x:c r="R126" s="6" t="n">
+        <x:v>1254</x:v>
+      </x:c>
     </x:row>
     <x:row r="127">
       <x:c r="A127" t="n">
@@ -5866,6 +7401,18 @@
       <x:c r="N127" t="str">
         <x:v>height</x:v>
       </x:c>
+      <x:c r="O127" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P127" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="Q127" s="6" t="n">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="R127" s="6" t="n">
+        <x:v>196</x:v>
+      </x:c>
     </x:row>
     <x:row r="128">
       <x:c r="A128" t="n">
@@ -5910,6 +7457,18 @@
       <x:c r="N128" t="str">
         <x:v>height</x:v>
       </x:c>
+      <x:c r="O128" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P128" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="Q128" s="6" t="n">
+        <x:v>667</x:v>
+      </x:c>
+      <x:c r="R128" s="6" t="n">
+        <x:v>196</x:v>
+      </x:c>
     </x:row>
     <x:row r="129">
       <x:c r="A129" t="n">
@@ -5954,6 +7513,18 @@
       <x:c r="N129" t="str">
         <x:v>height</x:v>
       </x:c>
+      <x:c r="O129" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P129" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="Q129" s="6" t="n">
+        <x:v>686</x:v>
+      </x:c>
+      <x:c r="R129" s="6" t="n">
+        <x:v>65</x:v>
+      </x:c>
     </x:row>
     <x:row r="130">
       <x:c r="A130" t="n">
@@ -5998,6 +7569,18 @@
       <x:c r="N130" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O130" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P130" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="Q130" s="6" t="n">
+        <x:v>688</x:v>
+      </x:c>
+      <x:c r="R130" s="6" t="n">
+        <x:v>63</x:v>
+      </x:c>
     </x:row>
     <x:row r="131">
       <x:c r="A131" t="n">
@@ -6042,6 +7625,18 @@
       <x:c r="N131" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O131" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P131" s="6" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="Q131" s="6" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="R131" s="6" t="n">
+        <x:v>216</x:v>
+      </x:c>
     </x:row>
     <x:row r="132">
       <x:c r="A132" t="n">
@@ -6086,6 +7681,18 @@
       <x:c r="N132" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O132" s="6" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="P132" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="Q132" s="6" t="n">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="R132" s="6" t="n">
+        <x:v>240</x:v>
+      </x:c>
     </x:row>
     <x:row r="133">
       <x:c r="A133" t="n">
@@ -6130,6 +7737,18 @@
       <x:c r="N133" t="str">
         <x:v>height</x:v>
       </x:c>
+      <x:c r="O133" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P133" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="Q133" s="6" t="n">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="R133" s="6" t="n">
+        <x:v>119</x:v>
+      </x:c>
     </x:row>
     <x:row r="134">
       <x:c r="A134" t="n">
@@ -6174,6 +7793,18 @@
       <x:c r="N134" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O134" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P134" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="Q134" s="6" t="n">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="R134" s="6" t="n">
+        <x:v>310</x:v>
+      </x:c>
     </x:row>
     <x:row r="135">
       <x:c r="A135" t="n">
@@ -6218,6 +7849,18 @@
       <x:c r="N135" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O135" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P135" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q135" s="6" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="R135" s="6" t="n">
+        <x:v>235</x:v>
+      </x:c>
     </x:row>
     <x:row r="136">
       <x:c r="A136" t="n">
@@ -6262,6 +7905,18 @@
       <x:c r="N136" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O136" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P136" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Q136" s="6" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="R136" s="6" t="n">
+        <x:v>238</x:v>
+      </x:c>
     </x:row>
     <x:row r="137">
       <x:c r="A137" t="n">
@@ -6306,6 +7961,18 @@
       <x:c r="N137" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O137" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P137" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q137" s="6" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="R137" s="6" t="n">
+        <x:v>256</x:v>
+      </x:c>
     </x:row>
     <x:row r="138">
       <x:c r="A138" t="n">
@@ -6350,6 +8017,18 @@
       <x:c r="N138" t="str">
         <x:v>height</x:v>
       </x:c>
+      <x:c r="O138" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P138" s="6" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="Q138" s="6" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="R138" s="6" t="n">
+        <x:v>127</x:v>
+      </x:c>
     </x:row>
     <x:row r="139">
       <x:c r="A139" t="n">
@@ -6394,6 +8073,18 @@
       <x:c r="N139" t="str">
         <x:v>height</x:v>
       </x:c>
+      <x:c r="O139" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P139" s="6" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q139" s="6" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="R139" s="6" t="n">
+        <x:v>132</x:v>
+      </x:c>
     </x:row>
     <x:row r="140">
       <x:c r="A140" t="n">
@@ -6438,6 +8129,18 @@
       <x:c r="N140" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O140" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="P140" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="Q140" s="6" t="n">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="R140" s="6" t="n">
+        <x:v>231</x:v>
+      </x:c>
     </x:row>
     <x:row r="141">
       <x:c r="A141" t="n">
@@ -6482,6 +8185,18 @@
       <x:c r="N141" t="str">
         <x:v>cover</x:v>
       </x:c>
+      <x:c r="O141" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P141" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q141" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="R141" s="6" t="n">
+        <x:v>1536</x:v>
+      </x:c>
     </x:row>
     <x:row r="142">
       <x:c r="A142" t="n">
@@ -6526,6 +8241,18 @@
       <x:c r="N142" t="str">
         <x:v>cover</x:v>
       </x:c>
+      <x:c r="O142" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P142" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q142" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="R142" s="6" t="n">
+        <x:v>1536</x:v>
+      </x:c>
     </x:row>
     <x:row r="143">
       <x:c r="A143" t="n">
@@ -6570,6 +8297,18 @@
       <x:c r="N143" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O143" s="6" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="P143" s="6" t="n">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="Q143" s="6" t="n">
+        <x:v>1131</x:v>
+      </x:c>
+      <x:c r="R143" s="6" t="n">
+        <x:v>836</x:v>
+      </x:c>
     </x:row>
     <x:row r="144">
       <x:c r="A144" t="n">
@@ -6614,6 +8353,18 @@
       <x:c r="N144" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O144" s="6" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="P144" s="6" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="Q144" s="6" t="n">
+        <x:v>1124</x:v>
+      </x:c>
+      <x:c r="R144" s="6" t="n">
+        <x:v>687</x:v>
+      </x:c>
     </x:row>
     <x:row r="145">
       <x:c r="A145" t="n">
@@ -6658,6 +8409,18 @@
       <x:c r="N145" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O145" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P145" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q145" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R145" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="146">
       <x:c r="A146" t="n">
@@ -6702,6 +8465,18 @@
       <x:c r="N146" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O146" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P146" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q146" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R146" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="147">
       <x:c r="A147" t="n">
@@ -6746,6 +8521,18 @@
       <x:c r="N147" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O147" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P147" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q147" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R147" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="148">
       <x:c r="A148" t="n">
@@ -6790,6 +8577,18 @@
       <x:c r="N148" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O148" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P148" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q148" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R148" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="149">
       <x:c r="A149" t="n">
@@ -6834,6 +8633,18 @@
       <x:c r="N149" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O149" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P149" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q149" s="6" t="n">
+        <x:v>728</x:v>
+      </x:c>
+      <x:c r="R149" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="150">
       <x:c r="A150" t="n">
@@ -6878,6 +8689,18 @@
       <x:c r="N150" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O150" s="6" t="n">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="P150" s="6" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="Q150" s="6" t="n">
+        <x:v>691</x:v>
+      </x:c>
+      <x:c r="R150" s="6" t="n">
+        <x:v>1059</x:v>
+      </x:c>
     </x:row>
     <x:row r="151">
       <x:c r="A151" t="n">
@@ -6922,6 +8745,18 @@
       <x:c r="N151" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O151" s="6" t="n">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="P151" s="6" t="n">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="Q151" s="6" t="n">
+        <x:v>687</x:v>
+      </x:c>
+      <x:c r="R151" s="6" t="n">
+        <x:v>826</x:v>
+      </x:c>
     </x:row>
     <x:row r="152">
       <x:c r="A152" t="n">
@@ -6966,6 +8801,18 @@
       <x:c r="N152" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O152" s="6" t="n">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="P152" s="6" t="n">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="Q152" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="R152" s="6" t="n">
+        <x:v>802</x:v>
+      </x:c>
     </x:row>
     <x:row r="153">
       <x:c r="A153" t="n">
@@ -7010,6 +8857,18 @@
       <x:c r="N153" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O153" s="6" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="P153" s="6" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="Q153" s="6" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="R153" s="6" t="n">
+        <x:v>393</x:v>
+      </x:c>
     </x:row>
     <x:row r="154">
       <x:c r="A154" t="n">
@@ -7054,6 +8913,18 @@
       <x:c r="N154" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O154" s="6" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="P154" s="6" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="Q154" s="6" t="n">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="R154" s="6" t="n">
+        <x:v>423</x:v>
+      </x:c>
     </x:row>
     <x:row r="155">
       <x:c r="A155" t="n">
@@ -7098,6 +8969,18 @@
       <x:c r="N155" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O155" s="6" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="P155" s="6" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="Q155" s="6" t="n">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="R155" s="6" t="n">
+        <x:v>444</x:v>
+      </x:c>
     </x:row>
     <x:row r="156">
       <x:c r="A156" t="n">
@@ -7142,6 +9025,18 @@
       <x:c r="N156" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O156" s="6" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="P156" s="6" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="Q156" s="6" t="n">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="R156" s="6" t="n">
+        <x:v>405</x:v>
+      </x:c>
     </x:row>
     <x:row r="157">
       <x:c r="A157" t="n">
@@ -7186,6 +9081,18 @@
       <x:c r="N157" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O157" s="6" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="P157" s="6" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="Q157" s="6" t="n">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="R157" s="6" t="n">
+        <x:v>372</x:v>
+      </x:c>
     </x:row>
     <x:row r="158">
       <x:c r="A158" t="n">
@@ -7230,6 +9137,18 @@
       <x:c r="N158" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O158" s="6" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="P158" s="6" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="Q158" s="6" t="n">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="R158" s="6" t="n">
+        <x:v>440</x:v>
+      </x:c>
     </x:row>
     <x:row r="159">
       <x:c r="A159" t="n">
@@ -7274,6 +9193,18 @@
       <x:c r="N159" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O159" s="6" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="P159" s="6" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="Q159" s="6" t="n">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="R159" s="6" t="n">
+        <x:v>438</x:v>
+      </x:c>
     </x:row>
     <x:row r="160">
       <x:c r="A160" t="n">
@@ -7318,6 +9249,18 @@
       <x:c r="N160" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O160" s="6" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="P160" s="6" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="Q160" s="6" t="n">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="R160" s="6" t="n">
+        <x:v>428</x:v>
+      </x:c>
     </x:row>
     <x:row r="161">
       <x:c r="A161" t="n">
@@ -7362,6 +9305,18 @@
       <x:c r="N161" t="str">
         <x:v>cover</x:v>
       </x:c>
+      <x:c r="O161" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P161" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q161" s="6" t="n">
+        <x:v>941</x:v>
+      </x:c>
+      <x:c r="R161" s="6" t="n">
+        <x:v>1672</x:v>
+      </x:c>
     </x:row>
     <x:row r="162">
       <x:c r="A162" t="n">
@@ -7406,6 +9361,18 @@
       <x:c r="N162" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O162" s="6" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="P162" s="6" t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="Q162" s="6" t="n">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="R162" s="6" t="n">
+        <x:v>401</x:v>
+      </x:c>
     </x:row>
     <x:row r="163">
       <x:c r="A163" t="n">
@@ -7450,6 +9417,18 @@
       <x:c r="N163" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O163" s="6" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="P163" s="6" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="Q163" s="6" t="n">
+        <x:v>695</x:v>
+      </x:c>
+      <x:c r="R163" s="6" t="n">
+        <x:v>370</x:v>
+      </x:c>
     </x:row>
     <x:row r="164">
       <x:c r="A164" t="n">
@@ -7494,6 +9473,18 @@
       <x:c r="N164" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O164" s="6" t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="P164" s="6" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="Q164" s="6" t="n">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="R164" s="6" t="n">
+        <x:v>348</x:v>
+      </x:c>
     </x:row>
     <x:row r="165">
       <x:c r="A165" t="n">
@@ -7538,6 +9529,18 @@
       <x:c r="N165" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O165" s="6" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="P165" s="6" t="n">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="Q165" s="6" t="n">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="R165" s="6" t="n">
+        <x:v>296</x:v>
+      </x:c>
     </x:row>
     <x:row r="166">
       <x:c r="A166" t="n">
@@ -7582,6 +9585,18 @@
       <x:c r="N166" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O166" s="6" t="n">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="P166" s="6" t="n">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="Q166" s="6" t="n">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="R166" s="6" t="n">
+        <x:v>314</x:v>
+      </x:c>
     </x:row>
     <x:row r="167">
       <x:c r="A167" t="n">
@@ -7626,6 +9641,18 @@
       <x:c r="N167" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O167" s="6" t="n">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="P167" s="6" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="Q167" s="6" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="R167" s="6" t="n">
+        <x:v>336</x:v>
+      </x:c>
     </x:row>
     <x:row r="168">
       <x:c r="A168" t="n">
@@ -7670,6 +9697,18 @@
       <x:c r="N168" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O168" s="6" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="P168" s="6" t="n">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="Q168" s="6" t="n">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="R168" s="6" t="n">
+        <x:v>319</x:v>
+      </x:c>
     </x:row>
     <x:row r="169">
       <x:c r="A169" t="n">
@@ -7714,6 +9753,18 @@
       <x:c r="N169" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O169" s="6" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="P169" s="6" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="Q169" s="6" t="n">
+        <x:v>894</x:v>
+      </x:c>
+      <x:c r="R169" s="6" t="n">
+        <x:v>211</x:v>
+      </x:c>
     </x:row>
     <x:row r="170">
       <x:c r="A170" t="n">
@@ -7758,6 +9809,18 @@
       <x:c r="N170" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O170" s="6" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="P170" s="6" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="Q170" s="6" t="n">
+        <x:v>890</x:v>
+      </x:c>
+      <x:c r="R170" s="6" t="n">
+        <x:v>233</x:v>
+      </x:c>
     </x:row>
     <x:row r="171">
       <x:c r="A171" t="n">
@@ -7802,6 +9865,18 @@
       <x:c r="N171" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O171" s="6" t="n">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="P171" s="6" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="Q171" s="6" t="n">
+        <x:v>828</x:v>
+      </x:c>
+      <x:c r="R171" s="6" t="n">
+        <x:v>211</x:v>
+      </x:c>
     </x:row>
     <x:row r="172">
       <x:c r="A172" t="n">
@@ -7846,6 +9921,18 @@
       <x:c r="N172" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O172" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P172" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q172" s="6" t="n">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="R172" s="6" t="n">
+        <x:v>384</x:v>
+      </x:c>
     </x:row>
     <x:row r="173">
       <x:c r="A173" t="n">
@@ -7890,6 +9977,18 @@
       <x:c r="N173" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O173" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P173" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q173" s="6" t="n">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="R173" s="6" t="n">
+        <x:v>384</x:v>
+      </x:c>
     </x:row>
     <x:row r="174">
       <x:c r="A174" t="n">
@@ -7934,6 +10033,18 @@
       <x:c r="N174" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O174" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P174" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q174" s="6" t="n">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="R174" s="6" t="n">
+        <x:v>384</x:v>
+      </x:c>
     </x:row>
     <x:row r="175">
       <x:c r="A175" t="n">
@@ -7978,6 +10089,18 @@
       <x:c r="N175" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O175" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P175" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q175" s="6" t="n">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="R175" s="6" t="n">
+        <x:v>384</x:v>
+      </x:c>
     </x:row>
     <x:row r="176">
       <x:c r="A176" t="n">
@@ -8022,6 +10145,18 @@
       <x:c r="N176" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O176" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P176" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q176" s="6" t="n">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="R176" s="6" t="n">
+        <x:v>384</x:v>
+      </x:c>
     </x:row>
     <x:row r="177">
       <x:c r="A177" t="n">
@@ -8066,6 +10201,18 @@
       <x:c r="N177" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O177" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P177" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q177" s="6" t="n">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="R177" s="6" t="n">
+        <x:v>384</x:v>
+      </x:c>
     </x:row>
     <x:row r="178">
       <x:c r="A178" t="n">
@@ -8110,6 +10257,18 @@
       <x:c r="N178" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O178" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P178" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q178" s="6" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="R178" s="6" t="n">
+        <x:v>640</x:v>
+      </x:c>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="3" t="n">
@@ -8154,6 +10313,18 @@
       <x:c r="N179" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O179" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P179" s="6" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="Q179" s="6" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="R179" s="6" t="n">
+        <x:v>235</x:v>
+      </x:c>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="3" t="n">
@@ -8198,6 +10369,18 @@
       <x:c r="N180" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O180" s="6" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P180" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="Q180" s="6" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="R180" s="6" t="n">
+        <x:v>240</x:v>
+      </x:c>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="3" t="n">
@@ -8242,6 +10425,18 @@
       <x:c r="N181" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O181" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P181" s="6" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q181" s="6" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="R181" s="6" t="n">
+        <x:v>231</x:v>
+      </x:c>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="3" t="n">
@@ -8286,6 +10481,18 @@
       <x:c r="N182" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O182" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="P182" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="Q182" s="6" t="n">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="R182" s="6" t="n">
+        <x:v>240</x:v>
+      </x:c>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="3" t="n">
@@ -8330,6 +10537,18 @@
       <x:c r="N183" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O183" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P183" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q183" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R183" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="3" t="n">
@@ -8374,6 +10593,18 @@
       <x:c r="N184" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O184" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P184" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q184" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R184" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="3" t="n">
@@ -8418,6 +10649,18 @@
       <x:c r="N185" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O185" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P185" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q185" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R185" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="3" t="n">
@@ -8462,6 +10705,18 @@
       <x:c r="N186" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O186" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P186" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q186" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R186" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="3" t="n">
@@ -8506,6 +10761,18 @@
       <x:c r="N187" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O187" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P187" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q187" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R187" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="3" t="n">
@@ -8550,6 +10817,18 @@
       <x:c r="N188" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O188" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P188" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q188" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R188" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="3" t="n">
@@ -8594,6 +10873,18 @@
       <x:c r="N189" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O189" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P189" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q189" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R189" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="3" t="n">
@@ -8638,6 +10929,18 @@
       <x:c r="N190" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O190" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P190" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q190" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R190" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="3" t="n">
@@ -8682,6 +10985,18 @@
       <x:c r="N191" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O191" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P191" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q191" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R191" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="3" t="n">
@@ -8726,6 +11041,18 @@
       <x:c r="N192" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O192" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P192" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q192" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R192" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="3" t="n">
@@ -8770,6 +11097,18 @@
       <x:c r="N193" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O193" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P193" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q193" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R193" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="3" t="n">
@@ -8814,6 +11153,18 @@
       <x:c r="N194" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O194" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P194" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q194" s="6" t="n">
+        <x:v>728</x:v>
+      </x:c>
+      <x:c r="R194" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="3" t="n">
@@ -8858,6 +11209,18 @@
       <x:c r="N195" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O195" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P195" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q195" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R195" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="3" t="n">
@@ -8902,6 +11265,18 @@
       <x:c r="N196" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O196" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P196" s="6" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="Q196" s="6" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="R196" s="6" t="n">
+        <x:v>1024</x:v>
+      </x:c>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="3" t="n">
@@ -8946,6 +11321,18 @@
       <x:c r="N197" t="str">
         <x:v>contain</x:v>
       </x:c>
+      <x:c r="O197" s="6" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="P197" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="Q197" s="6" t="n">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="R197" s="6" t="n">
+        <x:v>144</x:v>
+      </x:c>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="3" t="n">
@@ -8990,6 +11377,18 @@
       <x:c r="N198" t="str">
         <x:v>stretch</x:v>
       </x:c>
+      <x:c r="O198" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="P198" s="6" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="Q198" s="6" t="n">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="R198" s="6" t="n">
+        <x:v>382</x:v>
+      </x:c>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="3" t="n">
@@ -9033,6 +11432,18 @@
       </x:c>
       <x:c r="N199" t="str">
         <x:v>contain</x:v>
+      </x:c>
+      <x:c r="O199" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P199" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="Q199" s="6" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="R199" s="6" t="n">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
